--- a/Ostalo/DIGITALNI CERTIFIKATI.xlsx
+++ b/Ostalo/DIGITALNI CERTIFIKATI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3A98488-20DF-4881-9DB8-052B52B7BE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9248E4C6-FADD-4BD7-9E05-8800B30BB89D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dgc" sheetId="1" r:id="rId1"/>
@@ -133,6 +133,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="Q86" authorId="0" shapeId="0" xr:uid="{2F3ACAAB-2B6B-49FB-95DE-521916F4FEF3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Lenovo:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+TREBA DOSTAVITI PRIJEVOD IZVADTKA
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -250,7 +275,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="909" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="381">
   <si>
     <t>RB</t>
   </si>
@@ -1174,9 +1199,6 @@
     <t>SCANRIB26</t>
   </si>
   <si>
-    <t>da, čekamo novu osobnu, ističe</t>
-  </si>
-  <si>
     <t>Adriafencing03</t>
   </si>
   <si>
@@ -1319,13 +1341,103 @@
   </si>
   <si>
     <t>ZsuZsamama18</t>
+  </si>
+  <si>
+    <t>Rusko Invest</t>
+  </si>
+  <si>
+    <t>ANDOR GY0RGY FARKAS</t>
+  </si>
+  <si>
+    <t>&lt;baumhakl@gmail.com&gt;</t>
+  </si>
+  <si>
+    <t>BAUMHAKL1984</t>
+  </si>
+  <si>
+    <t>0036 30 520 0980</t>
+  </si>
+  <si>
+    <t>kažu da su aktivirali</t>
+  </si>
+  <si>
+    <t>baumhakl@gmail.com</t>
+  </si>
+  <si>
+    <t>+36302263662</t>
+  </si>
+  <si>
+    <t>andor.farkas975@gmail.com</t>
+  </si>
+  <si>
+    <t>Farkas1975</t>
+  </si>
+  <si>
+    <t>Emi-BM</t>
+  </si>
+  <si>
+    <t>ruskoinvest@gmail.com</t>
+  </si>
+  <si>
+    <t>+36703383480</t>
+  </si>
+  <si>
+    <t>Rusko1980</t>
+  </si>
+  <si>
+    <t>070429</t>
+  </si>
+  <si>
+    <t>171180</t>
+  </si>
+  <si>
+    <t>VivaPalazzo Zrt.</t>
+  </si>
+  <si>
+    <t>Kapitány Zoltán &lt;kapitany.zoltan@vivapalazzo.hu&gt;</t>
+  </si>
+  <si>
+    <t>+36303518181</t>
+  </si>
+  <si>
+    <t>Kapitany1974</t>
+  </si>
+  <si>
+    <t>kapitany.zoltan@vivapalazzo.hu</t>
+  </si>
+  <si>
+    <t>traviczky@gmail.com</t>
+  </si>
+  <si>
+    <t>DA</t>
+  </si>
+  <si>
+    <t>+36204822008</t>
+  </si>
+  <si>
+    <t>SKYPHONE</t>
+  </si>
+  <si>
+    <t>CELLMAXPHONE KFT</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>IMA</t>
+  </si>
+  <si>
+    <t>nemam osobne ni od Nemes Zoltana i Kristof Nobilis</t>
+  </si>
+  <si>
+    <t>Cassiopeia doo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1504,8 +1616,33 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1532,12 +1669,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1556,13 +1687,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF6815C"/>
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor rgb="FFF6815C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1702,7 +1833,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="195">
+  <cellXfs count="210">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1748,8 +1879,7 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="8" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1761,14 +1891,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1777,13 +1907,13 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1792,13 +1922,13 @@
     <xf numFmtId="49" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1813,7 +1943,7 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="13" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="13" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1860,7 +1990,7 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1870,7 +2000,7 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1956,74 +2086,100 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="23" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="5" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="15" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperveza" xfId="1" builtinId="8"/>
@@ -3029,8 +3185,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:U85" totalsRowShown="0" headerRowDxfId="50" headerRowBorderDxfId="49" tableBorderDxfId="48" totalsRowBorderDxfId="47">
-  <autoFilter ref="A1:U85" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:U91" totalsRowShown="0" headerRowDxfId="50" headerRowBorderDxfId="49" tableBorderDxfId="48" totalsRowBorderDxfId="47">
+  <autoFilter ref="A1:U91" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U70">
     <sortCondition ref="A1:A70"/>
   </sortState>
@@ -3360,7 +3516,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U369"/>
+  <dimension ref="A1:U375"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="3" customWidth="1"/>
@@ -3374,14 +3530,14 @@
     <col min="9" max="9" width="19.140625" style="2" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" style="24" customWidth="1"/>
     <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="5.28515625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.42578125" style="2" customWidth="1"/>
-    <col min="14" max="14" width="5.140625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" style="2" customWidth="1"/>
     <col min="15" max="15" width="13.42578125" customWidth="1"/>
     <col min="16" max="17" width="10.5703125" customWidth="1"/>
     <col min="18" max="18" width="11.140625" customWidth="1"/>
-    <col min="19" max="19" width="11.140625" style="65" customWidth="1"/>
-    <col min="20" max="20" width="12.5703125" style="45" customWidth="1"/>
+    <col min="19" max="19" width="11.140625" style="64" customWidth="1"/>
+    <col min="20" max="20" width="12.5703125" style="44" customWidth="1"/>
     <col min="21" max="21" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3440,10 +3596,10 @@
       <c r="R1" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="S1" s="54" t="s">
+      <c r="S1" s="53" t="s">
         <v>260</v>
       </c>
-      <c r="T1" s="42" t="s">
+      <c r="T1" s="41" t="s">
         <v>199</v>
       </c>
       <c r="U1" s="13" t="s">
@@ -3483,10 +3639,10 @@
       <c r="R2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="S2" s="55" t="s">
+      <c r="S2" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="T2" s="94">
+      <c r="T2" s="93">
         <v>46583</v>
       </c>
       <c r="U2" s="6">
@@ -3515,16 +3671,16 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="S3" s="56" t="s">
+      <c r="R3" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3" s="55" t="s">
         <v>265</v>
       </c>
-      <c r="T3" s="165">
+      <c r="T3" s="159">
         <v>46327</v>
       </c>
-      <c r="U3" s="166"/>
+      <c r="U3" s="160"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="29">
@@ -3558,16 +3714,16 @@
       <c r="Q4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="R4" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="S4" s="56" t="s">
+      <c r="R4" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="S4" s="55" t="s">
         <v>263</v>
       </c>
-      <c r="T4" s="165">
+      <c r="T4" s="159">
         <v>46719</v>
       </c>
-      <c r="U4" s="166">
+      <c r="U4" s="160">
         <v>150</v>
       </c>
     </row>
@@ -3601,16 +3757,16 @@
       <c r="Q5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="S5" s="56" t="s">
+      <c r="R5" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="S5" s="55" t="s">
         <v>261</v>
       </c>
-      <c r="T5" s="165">
+      <c r="T5" s="159">
         <v>46663</v>
       </c>
-      <c r="U5" s="166">
+      <c r="U5" s="160">
         <v>150</v>
       </c>
     </row>
@@ -3644,16 +3800,16 @@
       <c r="Q6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="R6" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="S6" s="56" t="s">
+      <c r="R6" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="S6" s="55" t="s">
         <v>261</v>
       </c>
-      <c r="T6" s="167">
+      <c r="T6" s="161">
         <v>46607</v>
       </c>
-      <c r="U6" s="166">
+      <c r="U6" s="160">
         <v>150</v>
       </c>
     </row>
@@ -3690,10 +3846,10 @@
       <c r="R7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="S7" s="55" t="s">
+      <c r="S7" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="T7" s="94">
+      <c r="T7" s="93">
         <v>46607</v>
       </c>
       <c r="U7" s="6">
@@ -3713,7 +3869,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="30"/>
-      <c r="I8" s="36" t="s">
+      <c r="I8" s="35" t="s">
         <v>138</v>
       </c>
       <c r="J8" s="31"/>
@@ -3732,16 +3888,16 @@
       <c r="Q8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="R8" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="S8" s="56" t="s">
+      <c r="R8" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="S8" s="55" t="s">
         <v>278</v>
       </c>
-      <c r="T8" s="165">
+      <c r="T8" s="159">
         <v>46638</v>
       </c>
-      <c r="U8" s="166">
+      <c r="U8" s="160">
         <v>50</v>
       </c>
     </row>
@@ -3774,9 +3930,9 @@
       <c r="R9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S9" s="99"/>
-      <c r="T9" s="103"/>
-      <c r="U9" s="101"/>
+      <c r="S9" s="98"/>
+      <c r="T9" s="102"/>
+      <c r="U9" s="100"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="29">
@@ -3808,16 +3964,16 @@
       <c r="Q10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="R10" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="S10" s="57" t="s">
+      <c r="R10" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="S10" s="56" t="s">
         <v>273</v>
       </c>
-      <c r="T10" s="168">
+      <c r="T10" s="162">
         <v>46648</v>
       </c>
-      <c r="U10" s="166">
+      <c r="U10" s="160">
         <v>300</v>
       </c>
     </row>
@@ -3828,7 +3984,7 @@
       <c r="B11" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="96" t="s">
+      <c r="C11" s="95" t="s">
         <v>288</v>
       </c>
       <c r="D11" s="9"/>
@@ -3857,19 +4013,19 @@
       <c r="Q11" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="R11" s="34" t="s">
+      <c r="R11" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="S11" s="93"/>
-      <c r="T11" s="44"/>
-      <c r="U11" s="162"/>
+      <c r="S11" s="92"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="157"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="25">
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -3890,14 +4046,14 @@
         <v>8</v>
       </c>
       <c r="Q12" s="9"/>
-      <c r="R12" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S12" s="61" t="s">
+      <c r="R12" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S12" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="T12" s="160"/>
-      <c r="U12" s="164"/>
+      <c r="T12" s="155"/>
+      <c r="U12" s="158"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
@@ -3923,16 +4079,16 @@
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
-      <c r="R13" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S13" s="61" t="s">
+      <c r="R13" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S13" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="T13" s="160">
+      <c r="T13" s="155">
         <v>46631</v>
       </c>
-      <c r="U13" s="164"/>
+      <c r="U13" s="158"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
@@ -3957,9 +4113,9 @@
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="99"/>
-      <c r="T14" s="103"/>
-      <c r="U14" s="101"/>
+      <c r="S14" s="98"/>
+      <c r="T14" s="102"/>
+      <c r="U14" s="100"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="29">
@@ -4010,10 +4166,10 @@
       <c r="R15" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="S15" s="60" t="s">
+      <c r="S15" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="T15" s="43">
+      <c r="T15" s="42">
         <v>46740</v>
       </c>
       <c r="U15" s="10">
@@ -4068,16 +4224,16 @@
       <c r="Q16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R16" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S16" s="61" t="s">
+      <c r="R16" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S16" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="T16" s="160">
+      <c r="T16" s="155">
         <v>46654</v>
       </c>
-      <c r="U16" s="164">
+      <c r="U16" s="158">
         <v>150</v>
       </c>
     </row>
@@ -4129,12 +4285,12 @@
       <c r="Q17" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="R17" s="34" t="s">
+      <c r="R17" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="S17" s="169"/>
-      <c r="T17" s="44"/>
-      <c r="U17" s="162"/>
+      <c r="S17" s="163"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="157"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="29">
@@ -4184,16 +4340,16 @@
       <c r="Q18" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R18" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S18" s="61" t="s">
+      <c r="R18" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S18" s="60" t="s">
         <v>276</v>
       </c>
-      <c r="T18" s="160">
+      <c r="T18" s="155">
         <v>46730</v>
       </c>
-      <c r="U18" s="164">
+      <c r="U18" s="158">
         <v>150</v>
       </c>
     </row>
@@ -4244,10 +4400,10 @@
       <c r="R19" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S19" s="59" t="s">
-        <v>312</v>
-      </c>
-      <c r="T19" s="43">
+      <c r="S19" s="58" t="s">
+        <v>311</v>
+      </c>
+      <c r="T19" s="42">
         <v>46808</v>
       </c>
       <c r="U19" s="10"/>
@@ -4298,16 +4454,16 @@
       <c r="Q20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R20" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S20" s="61" t="s">
+      <c r="R20" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S20" s="60" t="s">
         <v>274</v>
       </c>
-      <c r="T20" s="160">
+      <c r="T20" s="155">
         <v>46703</v>
       </c>
-      <c r="U20" s="164">
+      <c r="U20" s="158">
         <v>150</v>
       </c>
     </row>
@@ -4318,7 +4474,7 @@
       <c r="B21" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="39" t="s">
+      <c r="C21" s="38" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="9" t="s">
@@ -4330,7 +4486,7 @@
       <c r="F21" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="G21" s="39" t="s">
+      <c r="G21" s="38" t="s">
         <v>42</v>
       </c>
       <c r="H21" s="18" t="s">
@@ -4355,16 +4511,16 @@
       <c r="Q21" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R21" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S21" s="61" t="s">
+      <c r="R21" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S21" s="60" t="s">
         <v>279</v>
       </c>
-      <c r="T21" s="160">
+      <c r="T21" s="155">
         <v>46718</v>
       </c>
-      <c r="U21" s="164"/>
+      <c r="U21" s="158"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="25">
@@ -4410,16 +4566,16 @@
       <c r="Q22" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R22" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S22" s="61" t="s">
+      <c r="R22" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S22" s="60" t="s">
         <v>277</v>
       </c>
-      <c r="T22" s="160">
+      <c r="T22" s="155">
         <v>46768</v>
       </c>
-      <c r="U22" s="164"/>
+      <c r="U22" s="158"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="25">
@@ -4458,8 +4614,8 @@
       <c r="R23" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S23" s="59"/>
-      <c r="T23" s="43"/>
+      <c r="S23" s="58"/>
+      <c r="T23" s="42"/>
       <c r="U23" s="10"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -4503,16 +4659,16 @@
         <v>7</v>
       </c>
       <c r="P24" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q24" s="9" t="s">
         <v>96</v>
       </c>
       <c r="R24" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="S24" s="59"/>
-      <c r="T24" s="43"/>
+        <v>335</v>
+      </c>
+      <c r="S24" s="58"/>
+      <c r="T24" s="42"/>
       <c r="U24" s="10"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -4549,16 +4705,16 @@
         <v>126</v>
       </c>
       <c r="Q25" s="9"/>
-      <c r="R25" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S25" s="61" t="s">
+      <c r="R25" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S25" s="60" t="s">
         <v>262</v>
       </c>
-      <c r="T25" s="160">
+      <c r="T25" s="155">
         <v>46661</v>
       </c>
-      <c r="U25" s="164"/>
+      <c r="U25" s="158"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="25">
@@ -4608,16 +4764,16 @@
       <c r="Q26" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R26" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S26" s="61" t="s">
+      <c r="R26" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S26" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="T26" s="160">
+      <c r="T26" s="155">
         <v>46661</v>
       </c>
-      <c r="U26" s="164"/>
+      <c r="U26" s="158"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="25">
@@ -4626,7 +4782,7 @@
       <c r="B27" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="76" t="s">
+      <c r="C27" s="75" t="s">
         <v>71</v>
       </c>
       <c r="D27" s="9" t="s">
@@ -4638,13 +4794,13 @@
       <c r="F27" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G27" s="39" t="s">
+      <c r="G27" s="38" t="s">
         <v>71</v>
       </c>
-      <c r="H27" s="85">
+      <c r="H27" s="84">
         <v>36202622522</v>
       </c>
-      <c r="I27" s="85" t="s">
+      <c r="I27" s="84" t="s">
         <v>190</v>
       </c>
       <c r="J27" s="31"/>
@@ -4663,16 +4819,16 @@
       <c r="Q27" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R27" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S27" s="61" t="s">
+      <c r="R27" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S27" s="60" t="s">
         <v>268</v>
       </c>
-      <c r="T27" s="160">
+      <c r="T27" s="155">
         <v>46631</v>
       </c>
-      <c r="U27" s="164"/>
+      <c r="U27" s="158"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="25">
@@ -4718,16 +4874,16 @@
       <c r="Q28" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R28" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S28" s="61" t="s">
+      <c r="R28" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S28" s="60" t="s">
         <v>282</v>
       </c>
-      <c r="T28" s="160">
+      <c r="T28" s="155">
         <v>46692</v>
       </c>
-      <c r="U28" s="164"/>
+      <c r="U28" s="158"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="25">
@@ -4775,16 +4931,16 @@
       <c r="Q29" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R29" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="S29" s="62" t="s">
+      <c r="R29" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="S29" s="61" t="s">
         <v>277</v>
       </c>
-      <c r="T29" s="160">
+      <c r="T29" s="155">
         <v>46768</v>
       </c>
-      <c r="U29" s="164"/>
+      <c r="U29" s="158"/>
     </row>
     <row r="30" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="25">
@@ -4830,16 +4986,16 @@
       <c r="Q30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R30" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S30" s="61" t="s">
+      <c r="R30" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S30" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="T30" s="160">
+      <c r="T30" s="155">
         <v>46668</v>
       </c>
-      <c r="U30" s="164"/>
+      <c r="U30" s="158"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="25">
@@ -4863,10 +5019,10 @@
       <c r="G31" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="H31" s="35" t="s">
+      <c r="H31" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="I31" s="36" t="s">
+      <c r="I31" s="35" t="s">
         <v>83</v>
       </c>
       <c r="J31" s="23"/>
@@ -4885,16 +5041,16 @@
       <c r="Q31" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R31" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S31" s="61" t="s">
+      <c r="R31" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S31" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="T31" s="160">
+      <c r="T31" s="155">
         <v>46668</v>
       </c>
-      <c r="U31" s="164"/>
+      <c r="U31" s="158"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="25">
@@ -4915,13 +5071,13 @@
       <c r="F32" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G32" s="39" t="s">
+      <c r="G32" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="H32" s="40" t="s">
+      <c r="H32" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="I32" s="41" t="s">
+      <c r="I32" s="40" t="s">
         <v>93</v>
       </c>
       <c r="J32" s="23"/>
@@ -4940,16 +5096,16 @@
       <c r="Q32" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R32" s="97" t="s">
-        <v>7</v>
-      </c>
-      <c r="S32" s="61" t="s">
+      <c r="R32" s="96" t="s">
+        <v>7</v>
+      </c>
+      <c r="S32" s="60" t="s">
         <v>273</v>
       </c>
-      <c r="T32" s="160">
+      <c r="T32" s="155">
         <v>46732</v>
       </c>
-      <c r="U32" s="160">
+      <c r="U32" s="155">
         <v>45918</v>
       </c>
     </row>
@@ -4972,13 +5128,13 @@
       <c r="F33" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G33" s="39" t="s">
+      <c r="G33" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="H33" s="83" t="s">
+      <c r="H33" s="82" t="s">
         <v>205</v>
       </c>
-      <c r="I33" s="50" t="s">
+      <c r="I33" s="49" t="s">
         <v>233</v>
       </c>
       <c r="J33" s="23"/>
@@ -4997,16 +5153,16 @@
       <c r="Q33" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R33" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S33" s="61" t="s">
+      <c r="R33" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S33" s="60" t="s">
         <v>272</v>
       </c>
-      <c r="T33" s="160">
+      <c r="T33" s="155">
         <v>46764</v>
       </c>
-      <c r="U33" s="164"/>
+      <c r="U33" s="158"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="25">
@@ -5030,10 +5186,10 @@
       <c r="G34" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H34" s="40" t="s">
+      <c r="H34" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="I34" s="41" t="s">
+      <c r="I34" s="40" t="s">
         <v>107</v>
       </c>
       <c r="J34" s="23"/>
@@ -5052,16 +5208,16 @@
       <c r="Q34" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R34" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S34" s="61" t="s">
+      <c r="R34" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S34" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="T34" s="160">
+      <c r="T34" s="155">
         <v>46676</v>
       </c>
-      <c r="U34" s="164"/>
+      <c r="U34" s="158"/>
     </row>
     <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="25">
@@ -5070,7 +5226,7 @@
       <c r="B35" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="38" t="s">
         <v>184</v>
       </c>
       <c r="D35" s="9" t="s">
@@ -5082,13 +5238,13 @@
       <c r="F35" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G35" s="39" t="s">
+      <c r="G35" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="H35" s="84" t="s">
+      <c r="H35" s="83" t="s">
         <v>229</v>
       </c>
-      <c r="I35" s="90" t="s">
+      <c r="I35" s="89" t="s">
         <v>208</v>
       </c>
       <c r="J35" s="23"/>
@@ -5107,16 +5263,16 @@
       <c r="Q35" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="R35" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S35" s="61" t="s">
-        <v>321</v>
-      </c>
-      <c r="T35" s="160">
+      <c r="R35" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S35" s="60" t="s">
+        <v>320</v>
+      </c>
+      <c r="T35" s="155">
         <v>46802</v>
       </c>
-      <c r="U35" s="164"/>
+      <c r="U35" s="158"/>
     </row>
     <row r="36" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="25">
@@ -5137,13 +5293,13 @@
       <c r="F36" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G36" s="39" t="s">
+      <c r="G36" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="H36" s="86" t="s">
+      <c r="H36" s="85" t="s">
         <v>132</v>
       </c>
-      <c r="I36" s="86" t="s">
+      <c r="I36" s="85" t="s">
         <v>131</v>
       </c>
       <c r="J36" s="23"/>
@@ -5162,16 +5318,16 @@
       <c r="Q36" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R36" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="S36" s="61" t="s">
+      <c r="R36" s="48" t="s">
+        <v>7</v>
+      </c>
+      <c r="S36" s="60" t="s">
         <v>270</v>
       </c>
-      <c r="T36" s="160">
+      <c r="T36" s="155">
         <v>46702</v>
       </c>
-      <c r="U36" s="164"/>
+      <c r="U36" s="158"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7">
@@ -5180,7 +5336,7 @@
       <c r="B37" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="74" t="s">
+      <c r="C37" s="73" t="s">
         <v>240</v>
       </c>
       <c r="D37" s="8" t="s">
@@ -5193,8 +5349,8 @@
         <v>8</v>
       </c>
       <c r="G37" s="8"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="38"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="37"/>
       <c r="J37" s="22"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
@@ -5204,9 +5360,9 @@
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
-      <c r="S37" s="64"/>
-      <c r="T37" s="53"/>
-      <c r="U37" s="107"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="52"/>
+      <c r="U37" s="106"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="25">
@@ -5215,7 +5371,7 @@
       <c r="B38" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C38" s="75" t="s">
+      <c r="C38" s="74" t="s">
         <v>144</v>
       </c>
       <c r="D38" s="9" t="s">
@@ -5228,8 +5384,8 @@
         <v>7</v>
       </c>
       <c r="G38" s="9"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35" t="s">
+      <c r="H38" s="34"/>
+      <c r="I38" s="34" t="s">
         <v>120</v>
       </c>
       <c r="J38" s="23"/>
@@ -5249,10 +5405,10 @@
       <c r="R38" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="S38" s="60" t="s">
+      <c r="S38" s="59" t="s">
         <v>235</v>
       </c>
-      <c r="T38" s="43"/>
+      <c r="T38" s="42"/>
       <c r="U38" s="10"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -5260,7 +5416,7 @@
         <v>40</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
@@ -5273,8 +5429,8 @@
         <v>7</v>
       </c>
       <c r="G39" s="9"/>
-      <c r="H39" s="35"/>
-      <c r="I39" s="36"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="35"/>
       <c r="J39" s="23"/>
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
@@ -5289,16 +5445,16 @@
       <c r="Q39" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R39" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S39" s="61" t="s">
+      <c r="R39" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S39" s="60" t="s">
         <v>271</v>
       </c>
-      <c r="T39" s="160">
+      <c r="T39" s="155">
         <v>46661</v>
       </c>
-      <c r="U39" s="164"/>
+      <c r="U39" s="158"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="25">
@@ -5307,7 +5463,7 @@
       <c r="B40" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C40" s="77" t="s">
+      <c r="C40" s="76" t="s">
         <v>119</v>
       </c>
       <c r="D40" s="9" t="s">
@@ -5319,13 +5475,13 @@
       <c r="F40" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G40" s="79" t="s">
+      <c r="G40" s="78" t="s">
         <v>119</v>
       </c>
-      <c r="H40" s="40" t="s">
+      <c r="H40" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="I40" s="41" t="s">
+      <c r="I40" s="40" t="s">
         <v>168</v>
       </c>
       <c r="J40" s="23"/>
@@ -5344,16 +5500,16 @@
       <c r="Q40" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R40" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S40" s="61" t="s">
+      <c r="R40" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S40" s="60" t="s">
         <v>285</v>
       </c>
-      <c r="T40" s="160">
+      <c r="T40" s="155">
         <v>46789</v>
       </c>
-      <c r="U40" s="164"/>
+      <c r="U40" s="158"/>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="25">
@@ -5377,10 +5533,10 @@
       <c r="G41" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="H41" s="89" t="s">
+      <c r="H41" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="I41" s="92" t="s">
+      <c r="I41" s="91" t="s">
         <v>124</v>
       </c>
       <c r="J41" s="23"/>
@@ -5397,16 +5553,16 @@
       <c r="Q41" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R41" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S41" s="61" t="s">
+      <c r="R41" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S41" s="60" t="s">
         <v>280</v>
       </c>
-      <c r="T41" s="160">
+      <c r="T41" s="155">
         <v>46716</v>
       </c>
-      <c r="U41" s="164"/>
+      <c r="U41" s="158"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="25">
@@ -5430,10 +5586,10 @@
       <c r="G42" s="26" t="s">
         <v>128</v>
       </c>
-      <c r="H42" s="35" t="s">
+      <c r="H42" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="I42" s="36" t="s">
+      <c r="I42" s="35" t="s">
         <v>130</v>
       </c>
       <c r="J42" s="23"/>
@@ -5455,10 +5611,10 @@
       <c r="R42" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S42" s="59" t="s">
-        <v>318</v>
-      </c>
-      <c r="T42" s="43">
+      <c r="S42" s="58" t="s">
+        <v>317</v>
+      </c>
+      <c r="T42" s="42">
         <v>46814</v>
       </c>
       <c r="U42" s="10"/>
@@ -5481,8 +5637,8 @@
         <v>141</v>
       </c>
       <c r="G43" s="9"/>
-      <c r="H43" s="35"/>
-      <c r="I43" s="36"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="35"/>
       <c r="J43" s="23"/>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
@@ -5500,8 +5656,8 @@
       <c r="R43" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S43" s="59"/>
-      <c r="T43" s="43"/>
+      <c r="S43" s="58"/>
+      <c r="T43" s="42"/>
       <c r="U43" s="10"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -5522,8 +5678,8 @@
         <v>125</v>
       </c>
       <c r="G44" s="9"/>
-      <c r="H44" s="35"/>
-      <c r="I44" s="36"/>
+      <c r="H44" s="34"/>
+      <c r="I44" s="35"/>
       <c r="J44" s="23"/>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
@@ -5533,8 +5689,8 @@
       <c r="P44" s="9"/>
       <c r="Q44" s="9"/>
       <c r="R44" s="28"/>
-      <c r="S44" s="60"/>
-      <c r="T44" s="43"/>
+      <c r="S44" s="59"/>
+      <c r="T44" s="42"/>
       <c r="U44" s="10"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -5559,10 +5715,10 @@
       <c r="G45" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="H45" s="35" t="s">
+      <c r="H45" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="I45" s="36" t="s">
+      <c r="I45" s="35" t="s">
         <v>186</v>
       </c>
       <c r="J45" s="23"/>
@@ -5581,16 +5737,16 @@
       <c r="Q45" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R45" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S45" s="63" t="s">
+      <c r="R45" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S45" s="62" t="s">
         <v>264</v>
       </c>
-      <c r="T45" s="97">
+      <c r="T45" s="96">
         <v>46732</v>
       </c>
-      <c r="U45" s="164"/>
+      <c r="U45" s="158"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="25">
@@ -5611,13 +5767,13 @@
       <c r="F46" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G46" s="80" t="s">
+      <c r="G46" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="H46" s="87" t="s">
+      <c r="H46" s="86" t="s">
         <v>182</v>
       </c>
-      <c r="I46" s="36" t="s">
+      <c r="I46" s="35" t="s">
         <v>181</v>
       </c>
       <c r="J46" s="23"/>
@@ -5639,8 +5795,8 @@
       <c r="R46" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S46" s="59"/>
-      <c r="T46" s="43">
+      <c r="S46" s="58"/>
+      <c r="T46" s="42">
         <v>46799</v>
       </c>
       <c r="U46" s="10"/>
@@ -5667,10 +5823,10 @@
       <c r="G47" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="H47" s="35" t="s">
+      <c r="H47" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="I47" s="36" t="s">
+      <c r="I47" s="35" t="s">
         <v>154</v>
       </c>
       <c r="J47" s="23">
@@ -5694,8 +5850,8 @@
       <c r="R47" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S47" s="59"/>
-      <c r="T47" s="43"/>
+      <c r="S47" s="58"/>
+      <c r="T47" s="42"/>
       <c r="U47" s="10"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -5720,10 +5876,10 @@
       <c r="G48" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="H48" s="35" t="s">
+      <c r="H48" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="I48" s="35" t="s">
+      <c r="I48" s="34" t="s">
         <v>249</v>
       </c>
       <c r="J48" s="23">
@@ -5744,16 +5900,16 @@
       <c r="Q48" s="32">
         <v>46058</v>
       </c>
-      <c r="R48" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S48" s="61" t="s">
-        <v>320</v>
-      </c>
-      <c r="T48" s="160">
+      <c r="R48" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S48" s="60" t="s">
+        <v>319</v>
+      </c>
+      <c r="T48" s="155">
         <v>46821</v>
       </c>
-      <c r="U48" s="172"/>
+      <c r="U48" s="166"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="29">
@@ -5777,15 +5933,15 @@
       <c r="G49" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="H49" s="35" t="s">
+      <c r="H49" s="34" t="s">
         <v>252</v>
       </c>
-      <c r="I49" s="36" t="s">
+      <c r="I49" s="35" t="s">
         <v>253</v>
       </c>
       <c r="J49" s="23"/>
       <c r="K49" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L49" s="9"/>
       <c r="M49" s="9"/>
@@ -5793,7 +5949,7 @@
       <c r="O49" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="P49" s="155">
+      <c r="P49" s="154">
         <v>46098</v>
       </c>
       <c r="Q49" s="32">
@@ -5802,10 +5958,10 @@
       <c r="R49" s="32">
         <v>46107</v>
       </c>
-      <c r="S49" s="194" t="s">
+      <c r="S49" s="183" t="s">
         <v>261</v>
       </c>
-      <c r="T49" s="43">
+      <c r="T49" s="42">
         <v>46837</v>
       </c>
       <c r="U49" s="10"/>
@@ -5832,10 +5988,10 @@
       <c r="G50" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="H50" s="35" t="s">
+      <c r="H50" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="I50" s="36" t="s">
+      <c r="I50" s="35" t="s">
         <v>210</v>
       </c>
       <c r="J50" s="23" t="s">
@@ -5862,7 +6018,7 @@
       <c r="S50" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="T50" s="43">
+      <c r="T50" s="42">
         <v>46373</v>
       </c>
       <c r="U50" s="10"/>
@@ -5889,10 +6045,10 @@
       <c r="G51" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="H51" s="35" t="s">
+      <c r="H51" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="I51" s="36" t="s">
+      <c r="I51" s="35" t="s">
         <v>160</v>
       </c>
       <c r="J51" s="23">
@@ -5913,22 +6069,22 @@
       <c r="Q51" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R51" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S51" s="61" t="s">
+      <c r="R51" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S51" s="60" t="s">
         <v>269</v>
       </c>
-      <c r="T51" s="160">
+      <c r="T51" s="155">
         <v>45988</v>
       </c>
-      <c r="U51" s="164"/>
+      <c r="U51" s="158"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="25">
         <v>53</v>
       </c>
-      <c r="B52" s="73" t="s">
+      <c r="B52" s="72" t="s">
         <v>178</v>
       </c>
       <c r="C52" s="9" t="s">
@@ -5943,10 +6099,10 @@
       <c r="F52" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G52" s="81" t="s">
+      <c r="G52" s="80" t="s">
         <v>236</v>
       </c>
-      <c r="H52" s="88" t="s">
+      <c r="H52" s="87" t="s">
         <v>237</v>
       </c>
       <c r="I52" s="9" t="s">
@@ -5971,10 +6127,10 @@
       <c r="R52" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S52" s="59" t="s">
-        <v>346</v>
-      </c>
-      <c r="T52" s="43">
+      <c r="S52" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="T52" s="42">
         <v>46167</v>
       </c>
       <c r="U52" s="10"/>
@@ -5986,7 +6142,7 @@
       <c r="B53" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="C53" s="39" t="s">
+      <c r="C53" s="38" t="s">
         <v>149</v>
       </c>
       <c r="D53" s="9" t="s">
@@ -5998,13 +6154,13 @@
       <c r="F53" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="G53" s="39" t="s">
+      <c r="G53" s="38" t="s">
         <v>161</v>
       </c>
-      <c r="H53" s="35" t="s">
+      <c r="H53" s="34" t="s">
         <v>162</v>
       </c>
-      <c r="I53" s="36" t="s">
+      <c r="I53" s="35" t="s">
         <v>163</v>
       </c>
       <c r="J53" s="23"/>
@@ -6023,12 +6179,12 @@
       <c r="Q53" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="R53" s="34" t="s">
+      <c r="R53" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="S53" s="70"/>
-      <c r="T53" s="44"/>
-      <c r="U53" s="162"/>
+      <c r="S53" s="69"/>
+      <c r="T53" s="43"/>
+      <c r="U53" s="157"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="25">
@@ -6037,7 +6193,7 @@
       <c r="B54" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C54" s="39" t="s">
+      <c r="C54" s="38" t="s">
         <v>145</v>
       </c>
       <c r="D54" s="9" t="s">
@@ -6074,16 +6230,16 @@
       <c r="Q54" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R54" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S54" s="170">
+      <c r="R54" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S54" s="164">
         <v>975897</v>
       </c>
-      <c r="T54" s="160">
+      <c r="T54" s="155">
         <v>46793</v>
       </c>
-      <c r="U54" s="164"/>
+      <c r="U54" s="158"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="25">
@@ -6098,27 +6254,27 @@
       <c r="D55" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" s="46" t="s">
-        <v>7</v>
-      </c>
-      <c r="G55" s="67" t="s">
+      <c r="E55" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="45" t="s">
+        <v>7</v>
+      </c>
+      <c r="G55" s="66" t="s">
         <v>183</v>
       </c>
-      <c r="H55" s="68" t="s">
+      <c r="H55" s="67" t="s">
         <v>192</v>
       </c>
-      <c r="I55" s="46" t="s">
+      <c r="I55" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="J55" s="69"/>
-      <c r="K55" s="46" t="s">
+      <c r="J55" s="68"/>
+      <c r="K55" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="L55" s="46"/>
-      <c r="M55" s="46"/>
+      <c r="L55" s="45"/>
+      <c r="M55" s="45"/>
       <c r="N55" s="9"/>
       <c r="O55" s="9" t="s">
         <v>7</v>
@@ -6129,16 +6285,16 @@
       <c r="Q55" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="R55" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S55" s="63" t="s">
+      <c r="R55" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S55" s="62" t="s">
         <v>261</v>
       </c>
-      <c r="T55" s="160">
+      <c r="T55" s="155">
         <v>46806</v>
       </c>
-      <c r="U55" s="164"/>
+      <c r="U55" s="158"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="25">
@@ -6147,7 +6303,7 @@
       <c r="B56" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="C56" s="39"/>
+      <c r="C56" s="38"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9" t="s">
@@ -6170,16 +6326,16 @@
       <c r="Q56" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R56" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S56" s="61" t="s">
+      <c r="R56" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S56" s="60" t="s">
         <v>275</v>
       </c>
-      <c r="T56" s="160">
+      <c r="T56" s="155">
         <v>46711</v>
       </c>
-      <c r="U56" s="164"/>
+      <c r="U56" s="158"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="25">
@@ -6225,16 +6381,16 @@
       <c r="Q57" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R57" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S57" s="63" t="s">
+      <c r="R57" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S57" s="62" t="s">
         <v>267</v>
       </c>
-      <c r="T57" s="97">
+      <c r="T57" s="96">
         <v>46692</v>
       </c>
-      <c r="U57" s="164"/>
+      <c r="U57" s="158"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="25">
@@ -6264,22 +6420,22 @@
       <c r="Q58" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R58" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S58" s="61" t="s">
+      <c r="R58" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S58" s="60" t="s">
         <v>284</v>
       </c>
-      <c r="T58" s="160">
+      <c r="T58" s="155">
         <v>46764</v>
       </c>
-      <c r="U58" s="164"/>
+      <c r="U58" s="158"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="25">
         <v>60</v>
       </c>
-      <c r="B59" s="73" t="s">
+      <c r="B59" s="72" t="s">
         <v>191</v>
       </c>
       <c r="C59" s="4"/>
@@ -6301,25 +6457,25 @@
       <c r="Q59" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="R59" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S59" s="61" t="s">
-        <v>311</v>
-      </c>
-      <c r="T59" s="160">
+      <c r="R59" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S59" s="60" t="s">
+        <v>310</v>
+      </c>
+      <c r="T59" s="155">
         <v>46801</v>
       </c>
-      <c r="U59" s="164"/>
+      <c r="U59" s="158"/>
     </row>
     <row r="60" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="25">
         <v>61</v>
       </c>
-      <c r="B60" s="72" t="s">
+      <c r="B60" s="71" t="s">
         <v>195</v>
       </c>
-      <c r="C60" s="39" t="s">
+      <c r="C60" s="38" t="s">
         <v>196</v>
       </c>
       <c r="D60" s="9" t="s">
@@ -6337,7 +6493,7 @@
       <c r="H60" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="I60" s="90" t="s">
+      <c r="I60" s="89" t="s">
         <v>202</v>
       </c>
       <c r="J60" s="23"/>
@@ -6359,10 +6515,10 @@
       <c r="R60" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="S60" s="171">
+      <c r="S60" s="165">
         <v>198208</v>
       </c>
-      <c r="T60" s="43">
+      <c r="T60" s="42">
         <v>46800</v>
       </c>
       <c r="U60" s="10"/>
@@ -6393,16 +6549,16 @@
       <c r="Q61" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R61" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S61" s="61" t="s">
+      <c r="R61" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S61" s="60" t="s">
         <v>281</v>
       </c>
-      <c r="T61" s="160">
+      <c r="T61" s="155">
         <v>46676</v>
       </c>
-      <c r="U61" s="164"/>
+      <c r="U61" s="158"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="25">
@@ -6429,7 +6585,7 @@
       <c r="H62" s="18" t="s">
         <v>213</v>
       </c>
-      <c r="I62" s="91" t="s">
+      <c r="I62" s="90" t="s">
         <v>214</v>
       </c>
       <c r="J62" s="23"/>
@@ -6448,16 +6604,16 @@
       <c r="Q62" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="R62" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S62" s="170">
+      <c r="R62" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S62" s="164">
         <v>780616</v>
       </c>
-      <c r="T62" s="160">
+      <c r="T62" s="155">
         <v>46803</v>
       </c>
-      <c r="U62" s="164"/>
+      <c r="U62" s="158"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="25">
@@ -6497,12 +6653,12 @@
       <c r="Q63" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R63" s="34" t="s">
+      <c r="R63" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="S63" s="58"/>
-      <c r="T63" s="44"/>
-      <c r="U63" s="162"/>
+      <c r="S63" s="57"/>
+      <c r="T63" s="43"/>
+      <c r="U63" s="157"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="25">
@@ -6542,12 +6698,12 @@
       <c r="Q64" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="R64" s="34" t="s">
+      <c r="R64" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="S64" s="58"/>
-      <c r="T64" s="44"/>
-      <c r="U64" s="162"/>
+      <c r="S64" s="57"/>
+      <c r="T64" s="43"/>
+      <c r="U64" s="157"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="25">
@@ -6587,15 +6743,15 @@
       <c r="Q65" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="R65" s="34" t="s">
+      <c r="R65" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="S65" s="58"/>
-      <c r="T65" s="44"/>
-      <c r="U65" s="162"/>
+      <c r="S65" s="57"/>
+      <c r="T65" s="43"/>
+      <c r="U65" s="157"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A66" s="52">
+      <c r="A66" s="51">
         <v>67</v>
       </c>
       <c r="B66" s="8" t="s">
@@ -6610,7 +6766,9 @@
       <c r="E66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F66" s="1"/>
+      <c r="F66" s="1" t="s">
+        <v>8</v>
+      </c>
       <c r="G66" s="1"/>
       <c r="H66" s="16"/>
       <c r="I66" s="8"/>
@@ -6623,9 +6781,9 @@
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
       <c r="R66" s="8"/>
-      <c r="S66" s="64"/>
-      <c r="T66" s="53"/>
-      <c r="U66" s="107"/>
+      <c r="S66" s="63"/>
+      <c r="T66" s="52"/>
+      <c r="U66" s="106"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="25">
@@ -6634,22 +6792,22 @@
       <c r="B67" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C67" s="66" t="s">
+      <c r="C67" s="65" t="s">
         <v>239</v>
       </c>
-      <c r="D67" s="145" t="s">
-        <v>7</v>
-      </c>
-      <c r="E67" s="145" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" s="145" t="s">
+      <c r="D67" s="144" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" s="144" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="G67" s="78" t="s">
+      <c r="G67" s="77" t="s">
         <v>239</v>
       </c>
-      <c r="H67" s="146" t="s">
+      <c r="H67" s="145" t="s">
         <v>245</v>
       </c>
       <c r="I67" s="9" t="s">
@@ -6671,12 +6829,12 @@
       <c r="Q67" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="R67" s="34" t="s">
+      <c r="R67" s="33" t="s">
         <v>283</v>
       </c>
-      <c r="S67" s="58"/>
-      <c r="T67" s="44"/>
-      <c r="U67" s="162"/>
+      <c r="S67" s="57"/>
+      <c r="T67" s="43"/>
+      <c r="U67" s="157"/>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="25">
@@ -6700,7 +6858,7 @@
       <c r="G68" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="H68" s="82">
+      <c r="H68" s="81">
         <v>19736537052</v>
       </c>
       <c r="I68" s="9" t="s">
@@ -6722,16 +6880,16 @@
       <c r="Q68" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="R68" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S68" s="63" t="s">
+      <c r="R68" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S68" s="62" t="s">
         <v>263</v>
       </c>
-      <c r="T68" s="97">
+      <c r="T68" s="96">
         <v>46779</v>
       </c>
-      <c r="U68" s="164"/>
+      <c r="U68" s="158"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="25">
@@ -6740,7 +6898,7 @@
       <c r="B69" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="C69" s="66" t="s">
+      <c r="C69" s="65" t="s">
         <v>257</v>
       </c>
       <c r="D69" s="9" t="s">
@@ -6752,10 +6910,10 @@
       <c r="F69" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G69" s="78" t="s">
+      <c r="G69" s="77" t="s">
         <v>257</v>
       </c>
-      <c r="H69" s="95" t="s">
+      <c r="H69" s="94" t="s">
         <v>258</v>
       </c>
       <c r="I69" s="9" t="s">
@@ -6775,16 +6933,16 @@
       <c r="Q69" s="32">
         <v>46065</v>
       </c>
-      <c r="R69" s="179" t="s">
-        <v>7</v>
-      </c>
-      <c r="S69" s="178" t="s">
-        <v>328</v>
-      </c>
-      <c r="T69" s="177">
+      <c r="R69" s="173" t="s">
+        <v>7</v>
+      </c>
+      <c r="S69" s="172" t="s">
+        <v>327</v>
+      </c>
+      <c r="T69" s="171">
         <v>46832</v>
       </c>
-      <c r="U69" s="176"/>
+      <c r="U69" s="170"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4">
@@ -6830,61 +6988,67 @@
       <c r="Q70" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="R70" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S70" s="63" t="s">
+      <c r="R70" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S70" s="62" t="s">
         <v>261</v>
       </c>
-      <c r="T70" s="97">
+      <c r="T70" s="96">
         <v>46815</v>
       </c>
-      <c r="U70" s="172"/>
+      <c r="U70" s="166"/>
     </row>
     <row r="71" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A71" s="33">
+      <c r="A71" s="4">
         <v>72</v>
       </c>
-      <c r="B71" s="33" t="s">
+      <c r="B71" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C71" s="33"/>
-      <c r="D71" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E71" s="33" t="s">
+      <c r="C71" s="4"/>
+      <c r="D71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E71" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F71" s="33" t="s">
+      <c r="F71" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G71" s="156" t="s">
+      <c r="G71" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="H71" s="157" t="s">
+      <c r="H71" s="85" t="s">
         <v>132</v>
       </c>
-      <c r="I71" s="157" t="s">
+      <c r="I71" s="85" t="s">
         <v>131</v>
       </c>
-      <c r="J71" s="158"/>
-      <c r="K71" s="33" t="s">
+      <c r="J71" s="31"/>
+      <c r="K71" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="L71" s="33"/>
-      <c r="M71" s="33"/>
-      <c r="N71" s="33"/>
-      <c r="O71" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="P71" s="33"/>
-      <c r="Q71" s="33"/>
-      <c r="R71" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="S71" s="159"/>
-      <c r="T71" s="158"/>
-      <c r="U71" s="163"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="R71" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="S71" s="191" t="s">
+        <v>356</v>
+      </c>
+      <c r="T71" s="31"/>
+      <c r="U71" s="192"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4">
@@ -6893,8 +7057,8 @@
       <c r="B72" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C72" s="39" t="s">
-        <v>329</v>
+      <c r="C72" s="38" t="s">
+        <v>328</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>7</v>
@@ -6905,14 +7069,14 @@
       <c r="F72" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G72" s="39" t="s">
+      <c r="G72" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="H72" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="H72" s="30" t="s">
+      <c r="I72" s="4" t="s">
         <v>330</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="J72" s="31"/>
       <c r="K72" s="4" t="s">
@@ -6924,22 +7088,22 @@
       <c r="O72" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="P72" s="155">
+      <c r="P72" s="154">
         <v>46112</v>
       </c>
-      <c r="Q72" s="155">
+      <c r="Q72" s="154">
         <v>46114</v>
       </c>
-      <c r="R72" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S72" s="63" t="s">
+      <c r="R72" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S72" s="62" t="s">
         <v>263</v>
       </c>
-      <c r="T72" s="97">
+      <c r="T72" s="96">
         <v>46845</v>
       </c>
-      <c r="U72" s="162"/>
+      <c r="U72" s="157"/>
     </row>
     <row r="73" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
@@ -6958,18 +7122,18 @@
       <c r="F73" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G73" s="152" t="s">
-        <v>306</v>
-      </c>
-      <c r="H73" s="153" t="s">
+      <c r="G73" s="151" t="s">
+        <v>305</v>
+      </c>
+      <c r="H73" s="152" t="s">
         <v>296</v>
       </c>
-      <c r="I73" s="154" t="s">
-        <v>304</v>
+      <c r="I73" s="153" t="s">
+        <v>303</v>
       </c>
       <c r="J73" s="31"/>
       <c r="K73" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -6980,25 +7144,25 @@
       <c r="P73" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="Q73" s="155">
+      <c r="Q73" s="154">
         <v>46073</v>
       </c>
-      <c r="R73" s="49">
+      <c r="R73" s="48">
         <v>46128</v>
       </c>
-      <c r="S73" s="61" t="s">
+      <c r="S73" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="T73" s="160">
+      <c r="T73" s="155">
         <v>46859</v>
       </c>
-      <c r="U73" s="172"/>
+      <c r="U73" s="166"/>
     </row>
     <row r="74" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="4">
         <v>75</v>
       </c>
-      <c r="B74" s="174" t="s">
+      <c r="B74" s="168" t="s">
         <v>294</v>
       </c>
       <c r="C74" s="4"/>
@@ -7009,14 +7173,14 @@
         <v>8</v>
       </c>
       <c r="F74" s="4"/>
-      <c r="G74" s="39" t="s">
-        <v>325</v>
+      <c r="G74" s="38" t="s">
+        <v>324</v>
       </c>
       <c r="H74" s="30" t="s">
+        <v>322</v>
+      </c>
+      <c r="I74" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="J74" s="31"/>
       <c r="K74" s="4" t="s">
@@ -7028,29 +7192,29 @@
       <c r="O74" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="P74" s="155">
+      <c r="P74" s="154">
         <v>46106</v>
       </c>
-      <c r="Q74" s="155">
+      <c r="Q74" s="154">
         <v>46107</v>
       </c>
-      <c r="R74" s="175" t="s">
-        <v>7</v>
-      </c>
-      <c r="S74" s="178" t="s">
-        <v>327</v>
-      </c>
-      <c r="T74" s="177">
+      <c r="R74" s="169" t="s">
+        <v>7</v>
+      </c>
+      <c r="S74" s="172" t="s">
+        <v>326</v>
+      </c>
+      <c r="T74" s="171">
         <v>46838</v>
       </c>
-      <c r="U74" s="176"/>
+      <c r="U74" s="170"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="4">
         <v>76</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C75" s="4"/>
       <c r="D75" s="4" t="s">
@@ -7062,7 +7226,7 @@
       <c r="F75" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G75" s="39" t="s">
+      <c r="G75" s="38" t="s">
         <v>300</v>
       </c>
       <c r="H75" s="30" t="s">
@@ -7084,74 +7248,92 @@
       <c r="P75" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="Q75" s="155">
+      <c r="Q75" s="154">
         <v>46073</v>
       </c>
-      <c r="R75" s="47" t="s">
-        <v>7</v>
-      </c>
-      <c r="S75" s="61" t="s">
-        <v>319</v>
-      </c>
-      <c r="T75" s="97">
+      <c r="R75" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="S75" s="60" t="s">
+        <v>318</v>
+      </c>
+      <c r="T75" s="96">
         <v>46815</v>
       </c>
-      <c r="U75" s="172"/>
+      <c r="U75" s="166"/>
     </row>
     <row r="76" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>77</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="C76" s="113"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
+        <v>304</v>
+      </c>
+      <c r="C76" s="184" t="s">
+        <v>353</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="F76" s="1"/>
-      <c r="G76" s="113"/>
-      <c r="H76" s="122"/>
-      <c r="I76" s="122"/>
+      <c r="G76" s="184" t="s">
+        <v>357</v>
+      </c>
+      <c r="H76" s="185" t="s">
+        <v>355</v>
+      </c>
+      <c r="I76" s="186" t="s">
+        <v>354</v>
+      </c>
       <c r="J76" s="21"/>
-      <c r="K76" s="1"/>
+      <c r="K76" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
+      <c r="O76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P76" s="174">
+        <v>46199</v>
+      </c>
       <c r="Q76" s="1"/>
       <c r="R76" s="1"/>
-      <c r="S76" s="105"/>
+      <c r="S76" s="104"/>
       <c r="T76" s="21"/>
-      <c r="U76" s="161"/>
+      <c r="U76" s="156"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="4">
         <v>78</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C77" s="38" t="s">
         <v>313</v>
       </c>
-      <c r="C77" s="39" t="s">
+      <c r="D77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G77" s="38" t="s">
+        <v>313</v>
+      </c>
+      <c r="H77" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="G77" s="39" t="s">
-        <v>314</v>
-      </c>
-      <c r="H77" s="30" t="s">
+      <c r="I77" s="4" t="s">
         <v>315</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>316</v>
       </c>
       <c r="J77" s="31"/>
       <c r="K77" s="4" t="s">
@@ -7163,48 +7345,48 @@
       <c r="O77" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="P77" s="155">
+      <c r="P77" s="154">
         <v>46091</v>
       </c>
-      <c r="Q77" s="155">
+      <c r="Q77" s="154">
         <v>46093</v>
       </c>
-      <c r="R77" s="48" t="s">
-        <v>7</v>
-      </c>
-      <c r="S77" s="57" t="s">
+      <c r="R77" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="S77" s="56" t="s">
         <v>261</v>
       </c>
-      <c r="T77" s="168">
+      <c r="T77" s="162">
         <v>46824</v>
       </c>
-      <c r="U77" s="172"/>
+      <c r="U77" s="166"/>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>79</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C78" s="8"/>
       <c r="D78" s="8" t="s">
         <v>7</v>
       </c>
       <c r="E78" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" s="107" t="s">
         <v>338</v>
       </c>
-      <c r="F78" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G78" s="108" t="s">
+      <c r="H78" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="H78" s="17" t="s">
+      <c r="I78" s="8" t="s">
         <v>340</v>
-      </c>
-      <c r="I78" s="8" t="s">
-        <v>341</v>
       </c>
       <c r="J78" s="22"/>
       <c r="K78" s="8" t="s">
@@ -7214,38 +7396,38 @@
       <c r="M78" s="8"/>
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
-      <c r="P78" s="183">
+      <c r="P78" s="174">
         <v>46129</v>
       </c>
-      <c r="Q78" s="187" t="s">
-        <v>342</v>
-      </c>
-      <c r="R78" s="187"/>
-      <c r="S78" s="188"/>
-      <c r="T78" s="189"/>
-      <c r="U78" s="190"/>
+      <c r="Q78" s="178" t="s">
+        <v>341</v>
+      </c>
+      <c r="R78" s="178"/>
+      <c r="S78" s="179"/>
+      <c r="T78" s="180"/>
+      <c r="U78" s="181"/>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>80</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C79" s="9" t="s">
         <v>332</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>333</v>
       </c>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
       <c r="F79" s="9"/>
       <c r="G79" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="H79" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="H79" s="18" t="s">
+      <c r="I79" s="9" t="s">
         <v>334</v>
-      </c>
-      <c r="I79" s="9" t="s">
-        <v>335</v>
       </c>
       <c r="J79" s="23"/>
       <c r="K79" s="9" t="s">
@@ -7257,89 +7439,97 @@
       <c r="O79" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="P79" s="155">
+      <c r="P79" s="154">
         <v>46128</v>
       </c>
-      <c r="Q79" s="155">
+      <c r="Q79" s="154">
         <v>46132</v>
       </c>
-      <c r="R79" s="184" t="s">
+      <c r="R79" s="175" t="s">
         <v>283</v>
       </c>
-      <c r="S79" s="93"/>
-      <c r="T79" s="185"/>
-      <c r="U79" s="186"/>
+      <c r="S79" s="92"/>
+      <c r="T79" s="176"/>
+      <c r="U79" s="177"/>
     </row>
     <row r="80" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="1">
+      <c r="A80" s="4">
         <v>81</v>
       </c>
-      <c r="B80" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="C80" s="1" t="s">
+      <c r="B80" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D80" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G80" s="192" t="s">
+      <c r="D80" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="G80" s="194" t="s">
+        <v>342</v>
+      </c>
+      <c r="H80" s="195" t="s">
+        <v>344</v>
+      </c>
+      <c r="I80" s="153" t="s">
         <v>343</v>
       </c>
-      <c r="H80" s="193" t="s">
-        <v>345</v>
-      </c>
-      <c r="I80" s="191" t="s">
-        <v>344</v>
-      </c>
-      <c r="J80" s="22"/>
-      <c r="K80" s="8" t="s">
+      <c r="J80" s="23"/>
+      <c r="K80" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="L80" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="M80" s="8"/>
-      <c r="N80" s="1"/>
-      <c r="O80" s="1"/>
-      <c r="P80" s="183">
+      <c r="L80" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="M80" s="9"/>
+      <c r="N80" s="4"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="154">
         <v>46175</v>
       </c>
-      <c r="Q80" s="1"/>
-      <c r="R80" s="1"/>
-      <c r="S80" s="105"/>
-      <c r="T80" s="21"/>
-      <c r="U80" s="161"/>
+      <c r="Q80" s="154">
+        <v>46203</v>
+      </c>
+      <c r="R80" s="154">
+        <v>46203</v>
+      </c>
+      <c r="S80" s="193" t="s">
+        <v>365</v>
+      </c>
+      <c r="T80" s="31">
+        <v>46934</v>
+      </c>
+      <c r="U80" s="192"/>
     </row>
     <row r="81" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>82</v>
       </c>
-      <c r="B81" s="191" t="s">
+      <c r="B81" s="182" t="s">
+        <v>348</v>
+      </c>
+      <c r="C81" s="184" t="s">
         <v>349</v>
-      </c>
-      <c r="C81" s="192" t="s">
-        <v>350</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>7</v>
       </c>
       <c r="E81" s="8"/>
       <c r="F81" s="8"/>
-      <c r="G81" s="192" t="s">
+      <c r="G81" s="184" t="s">
+        <v>349</v>
+      </c>
+      <c r="H81" s="187">
+        <v>36706061827</v>
+      </c>
+      <c r="I81" s="187" t="s">
         <v>350</v>
-      </c>
-      <c r="H81" s="191">
-        <v>36706061827</v>
-      </c>
-      <c r="I81" s="191" t="s">
-        <v>351</v>
       </c>
       <c r="J81" s="22"/>
       <c r="K81" s="8" t="s">
@@ -7348,63 +7538,115 @@
       <c r="L81" s="8"/>
       <c r="M81" s="8"/>
       <c r="N81" s="8"/>
-      <c r="O81" s="4"/>
-      <c r="P81" s="180"/>
-      <c r="Q81" s="9"/>
-      <c r="R81" s="180"/>
-      <c r="S81" s="144"/>
-      <c r="T81" s="181"/>
-      <c r="U81" s="182"/>
+      <c r="O81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P81" s="174">
+        <v>46199</v>
+      </c>
+      <c r="Q81" s="188"/>
+      <c r="R81" s="178"/>
+      <c r="S81" s="179"/>
+      <c r="T81" s="189"/>
+      <c r="U81" s="190"/>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A82" s="5"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="17"/>
-      <c r="I82" s="8"/>
-      <c r="J82" s="22"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
-      <c r="M82" s="8"/>
-      <c r="N82" s="8"/>
+      <c r="A82" s="29">
+        <v>83</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9"/>
+      <c r="G82" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="H82" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J82" s="23"/>
+      <c r="K82" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L82" s="9"/>
+      <c r="M82" s="9"/>
+      <c r="N82" s="9"/>
       <c r="O82" s="4"/>
-      <c r="P82" s="180"/>
-      <c r="Q82" s="9"/>
-      <c r="R82" s="180"/>
-      <c r="S82" s="144"/>
-      <c r="T82" s="181"/>
-      <c r="U82" s="182"/>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" s="5"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
+      <c r="P82" s="154">
+        <v>46199</v>
+      </c>
+      <c r="Q82" s="32">
+        <v>46203</v>
+      </c>
+      <c r="R82" s="154">
+        <v>46203</v>
+      </c>
+      <c r="S82" s="193" t="s">
+        <v>366</v>
+      </c>
+      <c r="T82" s="42">
+        <v>46936</v>
+      </c>
+      <c r="U82" s="6"/>
+    </row>
+    <row r="83" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
+        <v>84</v>
+      </c>
+      <c r="B83" s="182" t="s">
+        <v>352</v>
+      </c>
+      <c r="C83" s="184" t="s">
+        <v>359</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>7</v>
+      </c>
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="17"/>
-      <c r="I83" s="8"/>
+      <c r="G83" s="184" t="s">
+        <v>359</v>
+      </c>
+      <c r="H83" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>360</v>
+      </c>
       <c r="J83" s="22"/>
-      <c r="K83" s="8"/>
+      <c r="K83" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="L83" s="8"/>
       <c r="M83" s="8"/>
       <c r="N83" s="8"/>
-      <c r="O83" s="4"/>
-      <c r="P83" s="180"/>
-      <c r="Q83" s="9"/>
-      <c r="R83" s="180"/>
-      <c r="S83" s="144"/>
-      <c r="T83" s="181"/>
-      <c r="U83" s="182"/>
+      <c r="O83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="P83" s="174">
+        <v>46199</v>
+      </c>
+      <c r="Q83" s="188"/>
+      <c r="R83" s="178"/>
+      <c r="S83" s="179"/>
+      <c r="T83" s="189"/>
+      <c r="U83" s="190"/>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A84" s="5"/>
-      <c r="B84" s="1"/>
+      <c r="A84" s="5">
+        <v>85</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>361</v>
+      </c>
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
       <c r="E84" s="8"/>
@@ -7417,148 +7659,238 @@
       <c r="L84" s="8"/>
       <c r="M84" s="8"/>
       <c r="N84" s="8"/>
-      <c r="O84" s="4"/>
-      <c r="P84" s="180"/>
-      <c r="Q84" s="9"/>
-      <c r="R84" s="180"/>
-      <c r="S84" s="144"/>
-      <c r="T84" s="181"/>
-      <c r="U84" s="182"/>
+      <c r="O84" s="1"/>
+      <c r="P84" s="174">
+        <v>46199</v>
+      </c>
+      <c r="Q84" s="8"/>
+      <c r="R84" s="1"/>
+      <c r="S84" s="104"/>
+      <c r="T84" s="52"/>
+      <c r="U84" s="100"/>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A85" s="5"/>
-      <c r="B85" s="1"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
+      <c r="A85" s="5">
+        <v>86</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>7</v>
+      </c>
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="17"/>
-      <c r="I85" s="8"/>
+      <c r="G85" s="107" t="s">
+        <v>371</v>
+      </c>
+      <c r="H85" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>370</v>
+      </c>
       <c r="J85" s="22"/>
-      <c r="K85" s="8"/>
+      <c r="K85" s="8" t="s">
+        <v>45</v>
+      </c>
       <c r="L85" s="8"/>
       <c r="M85" s="8"/>
       <c r="N85" s="8"/>
-      <c r="O85" s="4"/>
-      <c r="P85" s="180"/>
-      <c r="Q85" s="9"/>
-      <c r="R85" s="180"/>
-      <c r="S85" s="144"/>
-      <c r="T85" s="181"/>
-      <c r="U85" s="182"/>
+      <c r="O85" s="197"/>
+      <c r="P85" s="197"/>
+      <c r="Q85" s="108"/>
+      <c r="R85" s="197"/>
+      <c r="S85" s="200"/>
+      <c r="T85" s="198"/>
+      <c r="U85" s="199"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A86"/>
-      <c r="B86" t="s">
-        <v>287</v>
-      </c>
-      <c r="C86"/>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86" s="173"/>
-      <c r="I86"/>
-      <c r="J86" s="45"/>
-      <c r="K86"/>
-      <c r="L86"/>
-      <c r="M86"/>
-      <c r="N86"/>
+      <c r="A86" s="5">
+        <v>87</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="E86" s="8"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="H86" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>375</v>
+      </c>
+      <c r="J86" s="22"/>
+      <c r="K86" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L86" s="8"/>
+      <c r="M86" s="8"/>
+      <c r="N86" s="8"/>
+      <c r="O86" s="197" t="s">
+        <v>7</v>
+      </c>
+      <c r="P86" s="201">
+        <v>46233</v>
+      </c>
+      <c r="Q86" s="202">
+        <v>46242</v>
+      </c>
+      <c r="R86" s="33" t="s">
+        <v>283</v>
+      </c>
+      <c r="S86" s="57"/>
+      <c r="T86" s="43"/>
+      <c r="U86" s="157"/>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A87"/>
-      <c r="B87" t="s">
-        <v>286</v>
-      </c>
-      <c r="C87"/>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87" s="173"/>
-      <c r="I87"/>
-      <c r="J87" s="45"/>
-      <c r="K87"/>
-      <c r="L87"/>
-      <c r="M87"/>
-      <c r="N87"/>
+      <c r="A87" s="5">
+        <v>88</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" s="8"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="17"/>
+      <c r="I87" s="8"/>
+      <c r="J87" s="22"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="M87" s="8"/>
+      <c r="N87" s="8"/>
+      <c r="O87" s="204"/>
+      <c r="P87" s="205"/>
+      <c r="Q87" s="206"/>
+      <c r="R87" s="207"/>
+      <c r="S87" s="203"/>
+      <c r="T87" s="208"/>
+      <c r="U87" s="209"/>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A88"/>
-      <c r="B88"/>
-      <c r="C88"/>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88" s="173"/>
-      <c r="I88"/>
-      <c r="J88" s="45"/>
-      <c r="K88"/>
-      <c r="L88"/>
-      <c r="M88"/>
-      <c r="N88"/>
+      <c r="A88" s="5"/>
+      <c r="B88" s="1"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="17"/>
+      <c r="I88" s="8"/>
+      <c r="J88" s="22"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="M88" s="8"/>
+      <c r="N88" s="8"/>
+      <c r="O88" s="204"/>
+      <c r="P88" s="205"/>
+      <c r="Q88" s="206"/>
+      <c r="R88" s="207"/>
+      <c r="S88" s="203"/>
+      <c r="T88" s="208"/>
+      <c r="U88" s="209"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89"/>
-      <c r="B89"/>
-      <c r="C89"/>
-      <c r="D89"/>
-      <c r="E89"/>
-      <c r="F89"/>
-      <c r="G89"/>
-      <c r="H89" s="173"/>
-      <c r="I89"/>
-      <c r="J89" s="45"/>
-      <c r="K89"/>
-      <c r="L89"/>
-      <c r="M89"/>
-      <c r="N89"/>
+      <c r="A89" s="5"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="17"/>
+      <c r="I89" s="8"/>
+      <c r="J89" s="22"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="M89" s="8"/>
+      <c r="N89" s="8"/>
+      <c r="O89" s="204"/>
+      <c r="P89" s="205"/>
+      <c r="Q89" s="206"/>
+      <c r="R89" s="207"/>
+      <c r="S89" s="203"/>
+      <c r="T89" s="208"/>
+      <c r="U89" s="209"/>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A90"/>
-      <c r="B90"/>
-      <c r="C90"/>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
-      <c r="G90"/>
-      <c r="H90" s="173"/>
-      <c r="I90"/>
-      <c r="J90" s="45"/>
-      <c r="K90"/>
-      <c r="L90"/>
-      <c r="M90"/>
-      <c r="N90"/>
+      <c r="A90" s="5"/>
+      <c r="B90" s="1"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="17"/>
+      <c r="I90" s="8"/>
+      <c r="J90" s="22"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="M90" s="8"/>
+      <c r="N90" s="8"/>
+      <c r="O90" s="204"/>
+      <c r="P90" s="205"/>
+      <c r="Q90" s="206"/>
+      <c r="R90" s="207"/>
+      <c r="S90" s="203"/>
+      <c r="T90" s="208"/>
+      <c r="U90" s="209"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91"/>
-      <c r="B91"/>
-      <c r="C91"/>
-      <c r="D91"/>
-      <c r="E91"/>
-      <c r="F91"/>
-      <c r="G91"/>
-      <c r="H91" s="173"/>
-      <c r="I91"/>
-      <c r="J91" s="45"/>
-      <c r="K91"/>
-      <c r="L91"/>
-      <c r="M91"/>
-      <c r="N91"/>
+      <c r="A91" s="5"/>
+      <c r="B91" s="1"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="17"/>
+      <c r="I91" s="8"/>
+      <c r="J91" s="22"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="M91" s="8"/>
+      <c r="N91" s="8"/>
+      <c r="O91" s="197"/>
+      <c r="P91" s="197"/>
+      <c r="Q91" s="108"/>
+      <c r="R91" s="197"/>
+      <c r="S91" s="196"/>
+      <c r="T91" s="198"/>
+      <c r="U91" s="199"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92"/>
-      <c r="B92"/>
+      <c r="B92" t="s">
+        <v>287</v>
+      </c>
       <c r="C92"/>
       <c r="D92"/>
       <c r="E92"/>
       <c r="F92"/>
       <c r="G92"/>
-      <c r="H92" s="173"/>
+      <c r="H92" s="167"/>
       <c r="I92"/>
-      <c r="J92" s="45"/>
+      <c r="J92" s="44"/>
       <c r="K92"/>
       <c r="L92"/>
       <c r="M92"/>
@@ -7566,15 +7898,17 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93"/>
-      <c r="B93"/>
+      <c r="B93" t="s">
+        <v>286</v>
+      </c>
       <c r="C93"/>
       <c r="D93"/>
       <c r="E93"/>
       <c r="F93"/>
       <c r="G93"/>
-      <c r="H93" s="173"/>
+      <c r="H93" s="167"/>
       <c r="I93"/>
-      <c r="J93" s="45"/>
+      <c r="J93" s="44"/>
       <c r="K93"/>
       <c r="L93"/>
       <c r="M93"/>
@@ -7588,9 +7922,9 @@
       <c r="E94"/>
       <c r="F94"/>
       <c r="G94"/>
-      <c r="H94" s="173"/>
+      <c r="H94" s="167"/>
       <c r="I94"/>
-      <c r="J94" s="45"/>
+      <c r="J94" s="44"/>
       <c r="K94"/>
       <c r="L94"/>
       <c r="M94"/>
@@ -7604,9 +7938,9 @@
       <c r="E95"/>
       <c r="F95"/>
       <c r="G95"/>
-      <c r="H95" s="173"/>
+      <c r="H95" s="167"/>
       <c r="I95"/>
-      <c r="J95" s="45"/>
+      <c r="J95" s="44"/>
       <c r="K95"/>
       <c r="L95"/>
       <c r="M95"/>
@@ -7620,9 +7954,9 @@
       <c r="E96"/>
       <c r="F96"/>
       <c r="G96"/>
-      <c r="H96" s="173"/>
+      <c r="H96" s="167"/>
       <c r="I96"/>
-      <c r="J96" s="45"/>
+      <c r="J96" s="44"/>
       <c r="K96"/>
       <c r="L96"/>
       <c r="M96"/>
@@ -7636,9 +7970,9 @@
       <c r="E97"/>
       <c r="F97"/>
       <c r="G97"/>
-      <c r="H97" s="173"/>
+      <c r="H97" s="167"/>
       <c r="I97"/>
-      <c r="J97" s="45"/>
+      <c r="J97" s="44"/>
       <c r="K97"/>
       <c r="L97"/>
       <c r="M97"/>
@@ -7652,9 +7986,9 @@
       <c r="E98"/>
       <c r="F98"/>
       <c r="G98"/>
-      <c r="H98" s="173"/>
+      <c r="H98" s="167"/>
       <c r="I98"/>
-      <c r="J98" s="45"/>
+      <c r="J98" s="44"/>
       <c r="K98"/>
       <c r="L98"/>
       <c r="M98"/>
@@ -7668,9 +8002,9 @@
       <c r="E99"/>
       <c r="F99"/>
       <c r="G99"/>
-      <c r="H99" s="173"/>
+      <c r="H99" s="167"/>
       <c r="I99"/>
-      <c r="J99" s="45"/>
+      <c r="J99" s="44"/>
       <c r="K99"/>
       <c r="L99"/>
       <c r="M99"/>
@@ -7684,9 +8018,9 @@
       <c r="E100"/>
       <c r="F100"/>
       <c r="G100"/>
-      <c r="H100" s="173"/>
+      <c r="H100" s="167"/>
       <c r="I100"/>
-      <c r="J100" s="45"/>
+      <c r="J100" s="44"/>
       <c r="K100"/>
       <c r="L100"/>
       <c r="M100"/>
@@ -7700,9 +8034,9 @@
       <c r="E101"/>
       <c r="F101"/>
       <c r="G101"/>
-      <c r="H101" s="173"/>
+      <c r="H101" s="167"/>
       <c r="I101"/>
-      <c r="J101" s="45"/>
+      <c r="J101" s="44"/>
       <c r="K101"/>
       <c r="L101"/>
       <c r="M101"/>
@@ -7716,9 +8050,9 @@
       <c r="E102"/>
       <c r="F102"/>
       <c r="G102"/>
-      <c r="H102" s="173"/>
+      <c r="H102" s="167"/>
       <c r="I102"/>
-      <c r="J102" s="45"/>
+      <c r="J102" s="44"/>
       <c r="K102"/>
       <c r="L102"/>
       <c r="M102"/>
@@ -7732,9 +8066,9 @@
       <c r="E103"/>
       <c r="F103"/>
       <c r="G103"/>
-      <c r="H103" s="173"/>
+      <c r="H103" s="167"/>
       <c r="I103"/>
-      <c r="J103" s="45"/>
+      <c r="J103" s="44"/>
       <c r="K103"/>
       <c r="L103"/>
       <c r="M103"/>
@@ -7748,9 +8082,9 @@
       <c r="E104"/>
       <c r="F104"/>
       <c r="G104"/>
-      <c r="H104" s="173"/>
+      <c r="H104" s="167"/>
       <c r="I104"/>
-      <c r="J104" s="45"/>
+      <c r="J104" s="44"/>
       <c r="K104"/>
       <c r="L104"/>
       <c r="M104"/>
@@ -7764,9 +8098,9 @@
       <c r="E105"/>
       <c r="F105"/>
       <c r="G105"/>
-      <c r="H105" s="173"/>
+      <c r="H105" s="167"/>
       <c r="I105"/>
-      <c r="J105" s="45"/>
+      <c r="J105" s="44"/>
       <c r="K105"/>
       <c r="L105"/>
       <c r="M105"/>
@@ -7780,9 +8114,9 @@
       <c r="E106"/>
       <c r="F106"/>
       <c r="G106"/>
-      <c r="H106" s="173"/>
+      <c r="H106" s="167"/>
       <c r="I106"/>
-      <c r="J106" s="45"/>
+      <c r="J106" s="44"/>
       <c r="K106"/>
       <c r="L106"/>
       <c r="M106"/>
@@ -7796,9 +8130,9 @@
       <c r="E107"/>
       <c r="F107"/>
       <c r="G107"/>
-      <c r="H107" s="173"/>
+      <c r="H107" s="167"/>
       <c r="I107"/>
-      <c r="J107" s="45"/>
+      <c r="J107" s="44"/>
       <c r="K107"/>
       <c r="L107"/>
       <c r="M107"/>
@@ -7812,9 +8146,9 @@
       <c r="E108"/>
       <c r="F108"/>
       <c r="G108"/>
-      <c r="H108" s="173"/>
+      <c r="H108" s="167"/>
       <c r="I108"/>
-      <c r="J108" s="45"/>
+      <c r="J108" s="44"/>
       <c r="K108"/>
       <c r="L108"/>
       <c r="M108"/>
@@ -7828,9 +8162,9 @@
       <c r="E109"/>
       <c r="F109"/>
       <c r="G109"/>
-      <c r="H109" s="173"/>
+      <c r="H109" s="167"/>
       <c r="I109"/>
-      <c r="J109" s="45"/>
+      <c r="J109" s="44"/>
       <c r="K109"/>
       <c r="L109"/>
       <c r="M109"/>
@@ -7844,9 +8178,9 @@
       <c r="E110"/>
       <c r="F110"/>
       <c r="G110"/>
-      <c r="H110" s="173"/>
+      <c r="H110" s="167"/>
       <c r="I110"/>
-      <c r="J110" s="45"/>
+      <c r="J110" s="44"/>
       <c r="K110"/>
       <c r="L110"/>
       <c r="M110"/>
@@ -7860,9 +8194,9 @@
       <c r="E111"/>
       <c r="F111"/>
       <c r="G111"/>
-      <c r="H111" s="173"/>
+      <c r="H111" s="167"/>
       <c r="I111"/>
-      <c r="J111" s="45"/>
+      <c r="J111" s="44"/>
       <c r="K111"/>
       <c r="L111"/>
       <c r="M111"/>
@@ -7876,9 +8210,9 @@
       <c r="E112"/>
       <c r="F112"/>
       <c r="G112"/>
-      <c r="H112" s="173"/>
+      <c r="H112" s="167"/>
       <c r="I112"/>
-      <c r="J112" s="45"/>
+      <c r="J112" s="44"/>
       <c r="K112"/>
       <c r="L112"/>
       <c r="M112"/>
@@ -7892,9 +8226,9 @@
       <c r="E113"/>
       <c r="F113"/>
       <c r="G113"/>
-      <c r="H113" s="173"/>
+      <c r="H113" s="167"/>
       <c r="I113"/>
-      <c r="J113" s="45"/>
+      <c r="J113" s="44"/>
       <c r="K113"/>
       <c r="L113"/>
       <c r="M113"/>
@@ -7908,9 +8242,9 @@
       <c r="E114"/>
       <c r="F114"/>
       <c r="G114"/>
-      <c r="H114" s="173"/>
+      <c r="H114" s="167"/>
       <c r="I114"/>
-      <c r="J114" s="45"/>
+      <c r="J114" s="44"/>
       <c r="K114"/>
       <c r="L114"/>
       <c r="M114"/>
@@ -7924,9 +8258,9 @@
       <c r="E115"/>
       <c r="F115"/>
       <c r="G115"/>
-      <c r="H115" s="173"/>
+      <c r="H115" s="167"/>
       <c r="I115"/>
-      <c r="J115" s="45"/>
+      <c r="J115" s="44"/>
       <c r="K115"/>
       <c r="L115"/>
       <c r="M115"/>
@@ -7940,9 +8274,9 @@
       <c r="E116"/>
       <c r="F116"/>
       <c r="G116"/>
-      <c r="H116" s="173"/>
+      <c r="H116" s="167"/>
       <c r="I116"/>
-      <c r="J116" s="45"/>
+      <c r="J116" s="44"/>
       <c r="K116"/>
       <c r="L116"/>
       <c r="M116"/>
@@ -7956,9 +8290,9 @@
       <c r="E117"/>
       <c r="F117"/>
       <c r="G117"/>
-      <c r="H117" s="173"/>
+      <c r="H117" s="167"/>
       <c r="I117"/>
-      <c r="J117" s="45"/>
+      <c r="J117" s="44"/>
       <c r="K117"/>
       <c r="L117"/>
       <c r="M117"/>
@@ -7972,9 +8306,9 @@
       <c r="E118"/>
       <c r="F118"/>
       <c r="G118"/>
-      <c r="H118" s="173"/>
+      <c r="H118" s="167"/>
       <c r="I118"/>
-      <c r="J118" s="45"/>
+      <c r="J118" s="44"/>
       <c r="K118"/>
       <c r="L118"/>
       <c r="M118"/>
@@ -7988,9 +8322,9 @@
       <c r="E119"/>
       <c r="F119"/>
       <c r="G119"/>
-      <c r="H119" s="173"/>
+      <c r="H119" s="167"/>
       <c r="I119"/>
-      <c r="J119" s="45"/>
+      <c r="J119" s="44"/>
       <c r="K119"/>
       <c r="L119"/>
       <c r="M119"/>
@@ -8004,9 +8338,9 @@
       <c r="E120"/>
       <c r="F120"/>
       <c r="G120"/>
-      <c r="H120" s="173"/>
+      <c r="H120" s="167"/>
       <c r="I120"/>
-      <c r="J120" s="45"/>
+      <c r="J120" s="44"/>
       <c r="K120"/>
       <c r="L120"/>
       <c r="M120"/>
@@ -8020,9 +8354,9 @@
       <c r="E121"/>
       <c r="F121"/>
       <c r="G121"/>
-      <c r="H121" s="173"/>
+      <c r="H121" s="167"/>
       <c r="I121"/>
-      <c r="J121" s="45"/>
+      <c r="J121" s="44"/>
       <c r="K121"/>
       <c r="L121"/>
       <c r="M121"/>
@@ -8036,9 +8370,9 @@
       <c r="E122"/>
       <c r="F122"/>
       <c r="G122"/>
-      <c r="H122" s="173"/>
+      <c r="H122" s="167"/>
       <c r="I122"/>
-      <c r="J122" s="45"/>
+      <c r="J122" s="44"/>
       <c r="K122"/>
       <c r="L122"/>
       <c r="M122"/>
@@ -8052,9 +8386,9 @@
       <c r="E123"/>
       <c r="F123"/>
       <c r="G123"/>
-      <c r="H123" s="173"/>
+      <c r="H123" s="167"/>
       <c r="I123"/>
-      <c r="J123" s="45"/>
+      <c r="J123" s="44"/>
       <c r="K123"/>
       <c r="L123"/>
       <c r="M123"/>
@@ -8068,9 +8402,9 @@
       <c r="E124"/>
       <c r="F124"/>
       <c r="G124"/>
-      <c r="H124" s="173"/>
+      <c r="H124" s="167"/>
       <c r="I124"/>
-      <c r="J124" s="45"/>
+      <c r="J124" s="44"/>
       <c r="K124"/>
       <c r="L124"/>
       <c r="M124"/>
@@ -8084,9 +8418,9 @@
       <c r="E125"/>
       <c r="F125"/>
       <c r="G125"/>
-      <c r="H125" s="173"/>
+      <c r="H125" s="167"/>
       <c r="I125"/>
-      <c r="J125" s="45"/>
+      <c r="J125" s="44"/>
       <c r="K125"/>
       <c r="L125"/>
       <c r="M125"/>
@@ -8100,9 +8434,9 @@
       <c r="E126"/>
       <c r="F126"/>
       <c r="G126"/>
-      <c r="H126" s="173"/>
+      <c r="H126" s="167"/>
       <c r="I126"/>
-      <c r="J126" s="45"/>
+      <c r="J126" s="44"/>
       <c r="K126"/>
       <c r="L126"/>
       <c r="M126"/>
@@ -8116,9 +8450,9 @@
       <c r="E127"/>
       <c r="F127"/>
       <c r="G127"/>
-      <c r="H127" s="173"/>
+      <c r="H127" s="167"/>
       <c r="I127"/>
-      <c r="J127" s="45"/>
+      <c r="J127" s="44"/>
       <c r="K127"/>
       <c r="L127"/>
       <c r="M127"/>
@@ -8132,9 +8466,9 @@
       <c r="E128"/>
       <c r="F128"/>
       <c r="G128"/>
-      <c r="H128" s="173"/>
+      <c r="H128" s="167"/>
       <c r="I128"/>
-      <c r="J128" s="45"/>
+      <c r="J128" s="44"/>
       <c r="K128"/>
       <c r="L128"/>
       <c r="M128"/>
@@ -8148,9 +8482,9 @@
       <c r="E129"/>
       <c r="F129"/>
       <c r="G129"/>
-      <c r="H129" s="173"/>
+      <c r="H129" s="167"/>
       <c r="I129"/>
-      <c r="J129" s="45"/>
+      <c r="J129" s="44"/>
       <c r="K129"/>
       <c r="L129"/>
       <c r="M129"/>
@@ -8164,9 +8498,9 @@
       <c r="E130"/>
       <c r="F130"/>
       <c r="G130"/>
-      <c r="H130" s="173"/>
+      <c r="H130" s="167"/>
       <c r="I130"/>
-      <c r="J130" s="45"/>
+      <c r="J130" s="44"/>
       <c r="K130"/>
       <c r="L130"/>
       <c r="M130"/>
@@ -8180,9 +8514,9 @@
       <c r="E131"/>
       <c r="F131"/>
       <c r="G131"/>
-      <c r="H131" s="173"/>
+      <c r="H131" s="167"/>
       <c r="I131"/>
-      <c r="J131" s="45"/>
+      <c r="J131" s="44"/>
       <c r="K131"/>
       <c r="L131"/>
       <c r="M131"/>
@@ -8196,9 +8530,9 @@
       <c r="E132"/>
       <c r="F132"/>
       <c r="G132"/>
-      <c r="H132" s="173"/>
+      <c r="H132" s="167"/>
       <c r="I132"/>
-      <c r="J132" s="45"/>
+      <c r="J132" s="44"/>
       <c r="K132"/>
       <c r="L132"/>
       <c r="M132"/>
@@ -8212,9 +8546,9 @@
       <c r="E133"/>
       <c r="F133"/>
       <c r="G133"/>
-      <c r="H133" s="173"/>
+      <c r="H133" s="167"/>
       <c r="I133"/>
-      <c r="J133" s="45"/>
+      <c r="J133" s="44"/>
       <c r="K133"/>
       <c r="L133"/>
       <c r="M133"/>
@@ -8228,9 +8562,9 @@
       <c r="E134"/>
       <c r="F134"/>
       <c r="G134"/>
-      <c r="H134" s="173"/>
+      <c r="H134" s="167"/>
       <c r="I134"/>
-      <c r="J134" s="45"/>
+      <c r="J134" s="44"/>
       <c r="K134"/>
       <c r="L134"/>
       <c r="M134"/>
@@ -8244,9 +8578,9 @@
       <c r="E135"/>
       <c r="F135"/>
       <c r="G135"/>
-      <c r="H135" s="173"/>
+      <c r="H135" s="167"/>
       <c r="I135"/>
-      <c r="J135" s="45"/>
+      <c r="J135" s="44"/>
       <c r="K135"/>
       <c r="L135"/>
       <c r="M135"/>
@@ -8260,9 +8594,9 @@
       <c r="E136"/>
       <c r="F136"/>
       <c r="G136"/>
-      <c r="H136" s="173"/>
+      <c r="H136" s="167"/>
       <c r="I136"/>
-      <c r="J136" s="45"/>
+      <c r="J136" s="44"/>
       <c r="K136"/>
       <c r="L136"/>
       <c r="M136"/>
@@ -8276,9 +8610,9 @@
       <c r="E137"/>
       <c r="F137"/>
       <c r="G137"/>
-      <c r="H137" s="173"/>
+      <c r="H137" s="167"/>
       <c r="I137"/>
-      <c r="J137" s="45"/>
+      <c r="J137" s="44"/>
       <c r="K137"/>
       <c r="L137"/>
       <c r="M137"/>
@@ -8292,9 +8626,9 @@
       <c r="E138"/>
       <c r="F138"/>
       <c r="G138"/>
-      <c r="H138" s="173"/>
+      <c r="H138" s="167"/>
       <c r="I138"/>
-      <c r="J138" s="45"/>
+      <c r="J138" s="44"/>
       <c r="K138"/>
       <c r="L138"/>
       <c r="M138"/>
@@ -8308,9 +8642,9 @@
       <c r="E139"/>
       <c r="F139"/>
       <c r="G139"/>
-      <c r="H139" s="173"/>
+      <c r="H139" s="167"/>
       <c r="I139"/>
-      <c r="J139" s="45"/>
+      <c r="J139" s="44"/>
       <c r="K139"/>
       <c r="L139"/>
       <c r="M139"/>
@@ -8324,9 +8658,9 @@
       <c r="E140"/>
       <c r="F140"/>
       <c r="G140"/>
-      <c r="H140" s="173"/>
+      <c r="H140" s="167"/>
       <c r="I140"/>
-      <c r="J140" s="45"/>
+      <c r="J140" s="44"/>
       <c r="K140"/>
       <c r="L140"/>
       <c r="M140"/>
@@ -8340,9 +8674,9 @@
       <c r="E141"/>
       <c r="F141"/>
       <c r="G141"/>
-      <c r="H141" s="173"/>
+      <c r="H141" s="167"/>
       <c r="I141"/>
-      <c r="J141" s="45"/>
+      <c r="J141" s="44"/>
       <c r="K141"/>
       <c r="L141"/>
       <c r="M141"/>
@@ -8356,9 +8690,9 @@
       <c r="E142"/>
       <c r="F142"/>
       <c r="G142"/>
-      <c r="H142" s="173"/>
+      <c r="H142" s="167"/>
       <c r="I142"/>
-      <c r="J142" s="45"/>
+      <c r="J142" s="44"/>
       <c r="K142"/>
       <c r="L142"/>
       <c r="M142"/>
@@ -8372,9 +8706,9 @@
       <c r="E143"/>
       <c r="F143"/>
       <c r="G143"/>
-      <c r="H143" s="173"/>
+      <c r="H143" s="167"/>
       <c r="I143"/>
-      <c r="J143" s="45"/>
+      <c r="J143" s="44"/>
       <c r="K143"/>
       <c r="L143"/>
       <c r="M143"/>
@@ -8388,9 +8722,9 @@
       <c r="E144"/>
       <c r="F144"/>
       <c r="G144"/>
-      <c r="H144" s="173"/>
+      <c r="H144" s="167"/>
       <c r="I144"/>
-      <c r="J144" s="45"/>
+      <c r="J144" s="44"/>
       <c r="K144"/>
       <c r="L144"/>
       <c r="M144"/>
@@ -8404,9 +8738,9 @@
       <c r="E145"/>
       <c r="F145"/>
       <c r="G145"/>
-      <c r="H145" s="173"/>
+      <c r="H145" s="167"/>
       <c r="I145"/>
-      <c r="J145" s="45"/>
+      <c r="J145" s="44"/>
       <c r="K145"/>
       <c r="L145"/>
       <c r="M145"/>
@@ -8420,9 +8754,9 @@
       <c r="E146"/>
       <c r="F146"/>
       <c r="G146"/>
-      <c r="H146" s="173"/>
+      <c r="H146" s="167"/>
       <c r="I146"/>
-      <c r="J146" s="45"/>
+      <c r="J146" s="44"/>
       <c r="K146"/>
       <c r="L146"/>
       <c r="M146"/>
@@ -8436,9 +8770,9 @@
       <c r="E147"/>
       <c r="F147"/>
       <c r="G147"/>
-      <c r="H147" s="173"/>
+      <c r="H147" s="167"/>
       <c r="I147"/>
-      <c r="J147" s="45"/>
+      <c r="J147" s="44"/>
       <c r="K147"/>
       <c r="L147"/>
       <c r="M147"/>
@@ -8452,9 +8786,9 @@
       <c r="E148"/>
       <c r="F148"/>
       <c r="G148"/>
-      <c r="H148" s="173"/>
+      <c r="H148" s="167"/>
       <c r="I148"/>
-      <c r="J148" s="45"/>
+      <c r="J148" s="44"/>
       <c r="K148"/>
       <c r="L148"/>
       <c r="M148"/>
@@ -8468,9 +8802,9 @@
       <c r="E149"/>
       <c r="F149"/>
       <c r="G149"/>
-      <c r="H149" s="173"/>
+      <c r="H149" s="167"/>
       <c r="I149"/>
-      <c r="J149" s="45"/>
+      <c r="J149" s="44"/>
       <c r="K149"/>
       <c r="L149"/>
       <c r="M149"/>
@@ -8484,9 +8818,9 @@
       <c r="E150"/>
       <c r="F150"/>
       <c r="G150"/>
-      <c r="H150" s="173"/>
+      <c r="H150" s="167"/>
       <c r="I150"/>
-      <c r="J150" s="45"/>
+      <c r="J150" s="44"/>
       <c r="K150"/>
       <c r="L150"/>
       <c r="M150"/>
@@ -8500,9 +8834,9 @@
       <c r="E151"/>
       <c r="F151"/>
       <c r="G151"/>
-      <c r="H151" s="173"/>
+      <c r="H151" s="167"/>
       <c r="I151"/>
-      <c r="J151" s="45"/>
+      <c r="J151" s="44"/>
       <c r="K151"/>
       <c r="L151"/>
       <c r="M151"/>
@@ -8516,9 +8850,9 @@
       <c r="E152"/>
       <c r="F152"/>
       <c r="G152"/>
-      <c r="H152" s="173"/>
+      <c r="H152" s="167"/>
       <c r="I152"/>
-      <c r="J152" s="45"/>
+      <c r="J152" s="44"/>
       <c r="K152"/>
       <c r="L152"/>
       <c r="M152"/>
@@ -8532,9 +8866,9 @@
       <c r="E153"/>
       <c r="F153"/>
       <c r="G153"/>
-      <c r="H153" s="173"/>
+      <c r="H153" s="167"/>
       <c r="I153"/>
-      <c r="J153" s="45"/>
+      <c r="J153" s="44"/>
       <c r="K153"/>
       <c r="L153"/>
       <c r="M153"/>
@@ -8548,9 +8882,9 @@
       <c r="E154"/>
       <c r="F154"/>
       <c r="G154"/>
-      <c r="H154" s="173"/>
+      <c r="H154" s="167"/>
       <c r="I154"/>
-      <c r="J154" s="45"/>
+      <c r="J154" s="44"/>
       <c r="K154"/>
       <c r="L154"/>
       <c r="M154"/>
@@ -8564,9 +8898,9 @@
       <c r="E155"/>
       <c r="F155"/>
       <c r="G155"/>
-      <c r="H155" s="173"/>
+      <c r="H155" s="167"/>
       <c r="I155"/>
-      <c r="J155" s="45"/>
+      <c r="J155" s="44"/>
       <c r="K155"/>
       <c r="L155"/>
       <c r="M155"/>
@@ -8580,9 +8914,9 @@
       <c r="E156"/>
       <c r="F156"/>
       <c r="G156"/>
-      <c r="H156" s="173"/>
+      <c r="H156" s="167"/>
       <c r="I156"/>
-      <c r="J156" s="45"/>
+      <c r="J156" s="44"/>
       <c r="K156"/>
       <c r="L156"/>
       <c r="M156"/>
@@ -8596,9 +8930,9 @@
       <c r="E157"/>
       <c r="F157"/>
       <c r="G157"/>
-      <c r="H157" s="173"/>
+      <c r="H157" s="167"/>
       <c r="I157"/>
-      <c r="J157" s="45"/>
+      <c r="J157" s="44"/>
       <c r="K157"/>
       <c r="L157"/>
       <c r="M157"/>
@@ -8612,9 +8946,9 @@
       <c r="E158"/>
       <c r="F158"/>
       <c r="G158"/>
-      <c r="H158" s="173"/>
+      <c r="H158" s="167"/>
       <c r="I158"/>
-      <c r="J158" s="45"/>
+      <c r="J158" s="44"/>
       <c r="K158"/>
       <c r="L158"/>
       <c r="M158"/>
@@ -8628,9 +8962,9 @@
       <c r="E159"/>
       <c r="F159"/>
       <c r="G159"/>
-      <c r="H159" s="173"/>
+      <c r="H159" s="167"/>
       <c r="I159"/>
-      <c r="J159" s="45"/>
+      <c r="J159" s="44"/>
       <c r="K159"/>
       <c r="L159"/>
       <c r="M159"/>
@@ -8644,9 +8978,9 @@
       <c r="E160"/>
       <c r="F160"/>
       <c r="G160"/>
-      <c r="H160" s="173"/>
+      <c r="H160" s="167"/>
       <c r="I160"/>
-      <c r="J160" s="45"/>
+      <c r="J160" s="44"/>
       <c r="K160"/>
       <c r="L160"/>
       <c r="M160"/>
@@ -8660,9 +8994,9 @@
       <c r="E161"/>
       <c r="F161"/>
       <c r="G161"/>
-      <c r="H161" s="173"/>
+      <c r="H161" s="167"/>
       <c r="I161"/>
-      <c r="J161" s="45"/>
+      <c r="J161" s="44"/>
       <c r="K161"/>
       <c r="L161"/>
       <c r="M161"/>
@@ -8676,9 +9010,9 @@
       <c r="E162"/>
       <c r="F162"/>
       <c r="G162"/>
-      <c r="H162" s="173"/>
+      <c r="H162" s="167"/>
       <c r="I162"/>
-      <c r="J162" s="45"/>
+      <c r="J162" s="44"/>
       <c r="K162"/>
       <c r="L162"/>
       <c r="M162"/>
@@ -8692,9 +9026,9 @@
       <c r="E163"/>
       <c r="F163"/>
       <c r="G163"/>
-      <c r="H163" s="173"/>
+      <c r="H163" s="167"/>
       <c r="I163"/>
-      <c r="J163" s="45"/>
+      <c r="J163" s="44"/>
       <c r="K163"/>
       <c r="L163"/>
       <c r="M163"/>
@@ -8708,9 +9042,9 @@
       <c r="E164"/>
       <c r="F164"/>
       <c r="G164"/>
-      <c r="H164" s="173"/>
+      <c r="H164" s="167"/>
       <c r="I164"/>
-      <c r="J164" s="45"/>
+      <c r="J164" s="44"/>
       <c r="K164"/>
       <c r="L164"/>
       <c r="M164"/>
@@ -8724,9 +9058,9 @@
       <c r="E165"/>
       <c r="F165"/>
       <c r="G165"/>
-      <c r="H165" s="173"/>
+      <c r="H165" s="167"/>
       <c r="I165"/>
-      <c r="J165" s="45"/>
+      <c r="J165" s="44"/>
       <c r="K165"/>
       <c r="L165"/>
       <c r="M165"/>
@@ -8740,9 +9074,9 @@
       <c r="E166"/>
       <c r="F166"/>
       <c r="G166"/>
-      <c r="H166" s="173"/>
+      <c r="H166" s="167"/>
       <c r="I166"/>
-      <c r="J166" s="45"/>
+      <c r="J166" s="44"/>
       <c r="K166"/>
       <c r="L166"/>
       <c r="M166"/>
@@ -8756,9 +9090,9 @@
       <c r="E167"/>
       <c r="F167"/>
       <c r="G167"/>
-      <c r="H167" s="173"/>
+      <c r="H167" s="167"/>
       <c r="I167"/>
-      <c r="J167" s="45"/>
+      <c r="J167" s="44"/>
       <c r="K167"/>
       <c r="L167"/>
       <c r="M167"/>
@@ -8772,9 +9106,9 @@
       <c r="E168"/>
       <c r="F168"/>
       <c r="G168"/>
-      <c r="H168" s="173"/>
+      <c r="H168" s="167"/>
       <c r="I168"/>
-      <c r="J168" s="45"/>
+      <c r="J168" s="44"/>
       <c r="K168"/>
       <c r="L168"/>
       <c r="M168"/>
@@ -8788,9 +9122,9 @@
       <c r="E169"/>
       <c r="F169"/>
       <c r="G169"/>
-      <c r="H169" s="173"/>
+      <c r="H169" s="167"/>
       <c r="I169"/>
-      <c r="J169" s="45"/>
+      <c r="J169" s="44"/>
       <c r="K169"/>
       <c r="L169"/>
       <c r="M169"/>
@@ -8804,9 +9138,9 @@
       <c r="E170"/>
       <c r="F170"/>
       <c r="G170"/>
-      <c r="H170" s="173"/>
+      <c r="H170" s="167"/>
       <c r="I170"/>
-      <c r="J170" s="45"/>
+      <c r="J170" s="44"/>
       <c r="K170"/>
       <c r="L170"/>
       <c r="M170"/>
@@ -8820,9 +9154,9 @@
       <c r="E171"/>
       <c r="F171"/>
       <c r="G171"/>
-      <c r="H171" s="173"/>
+      <c r="H171" s="167"/>
       <c r="I171"/>
-      <c r="J171" s="45"/>
+      <c r="J171" s="44"/>
       <c r="K171"/>
       <c r="L171"/>
       <c r="M171"/>
@@ -8836,9 +9170,9 @@
       <c r="E172"/>
       <c r="F172"/>
       <c r="G172"/>
-      <c r="H172" s="173"/>
+      <c r="H172" s="167"/>
       <c r="I172"/>
-      <c r="J172" s="45"/>
+      <c r="J172" s="44"/>
       <c r="K172"/>
       <c r="L172"/>
       <c r="M172"/>
@@ -8852,9 +9186,9 @@
       <c r="E173"/>
       <c r="F173"/>
       <c r="G173"/>
-      <c r="H173" s="173"/>
+      <c r="H173" s="167"/>
       <c r="I173"/>
-      <c r="J173" s="45"/>
+      <c r="J173" s="44"/>
       <c r="K173"/>
       <c r="L173"/>
       <c r="M173"/>
@@ -8868,9 +9202,9 @@
       <c r="E174"/>
       <c r="F174"/>
       <c r="G174"/>
-      <c r="H174" s="173"/>
+      <c r="H174" s="167"/>
       <c r="I174"/>
-      <c r="J174" s="45"/>
+      <c r="J174" s="44"/>
       <c r="K174"/>
       <c r="L174"/>
       <c r="M174"/>
@@ -8884,9 +9218,9 @@
       <c r="E175"/>
       <c r="F175"/>
       <c r="G175"/>
-      <c r="H175" s="173"/>
+      <c r="H175" s="167"/>
       <c r="I175"/>
-      <c r="J175" s="45"/>
+      <c r="J175" s="44"/>
       <c r="K175"/>
       <c r="L175"/>
       <c r="M175"/>
@@ -8900,9 +9234,9 @@
       <c r="E176"/>
       <c r="F176"/>
       <c r="G176"/>
-      <c r="H176" s="173"/>
+      <c r="H176" s="167"/>
       <c r="I176"/>
-      <c r="J176" s="45"/>
+      <c r="J176" s="44"/>
       <c r="K176"/>
       <c r="L176"/>
       <c r="M176"/>
@@ -8916,9 +9250,9 @@
       <c r="E177"/>
       <c r="F177"/>
       <c r="G177"/>
-      <c r="H177" s="173"/>
+      <c r="H177" s="167"/>
       <c r="I177"/>
-      <c r="J177" s="45"/>
+      <c r="J177" s="44"/>
       <c r="K177"/>
       <c r="L177"/>
       <c r="M177"/>
@@ -8932,9 +9266,9 @@
       <c r="E178"/>
       <c r="F178"/>
       <c r="G178"/>
-      <c r="H178" s="173"/>
+      <c r="H178" s="167"/>
       <c r="I178"/>
-      <c r="J178" s="45"/>
+      <c r="J178" s="44"/>
       <c r="K178"/>
       <c r="L178"/>
       <c r="M178"/>
@@ -8948,9 +9282,9 @@
       <c r="E179"/>
       <c r="F179"/>
       <c r="G179"/>
-      <c r="H179" s="173"/>
+      <c r="H179" s="167"/>
       <c r="I179"/>
-      <c r="J179" s="45"/>
+      <c r="J179" s="44"/>
       <c r="K179"/>
       <c r="L179"/>
       <c r="M179"/>
@@ -8964,9 +9298,9 @@
       <c r="E180"/>
       <c r="F180"/>
       <c r="G180"/>
-      <c r="H180" s="173"/>
+      <c r="H180" s="167"/>
       <c r="I180"/>
-      <c r="J180" s="45"/>
+      <c r="J180" s="44"/>
       <c r="K180"/>
       <c r="L180"/>
       <c r="M180"/>
@@ -8980,9 +9314,9 @@
       <c r="E181"/>
       <c r="F181"/>
       <c r="G181"/>
-      <c r="H181" s="173"/>
+      <c r="H181" s="167"/>
       <c r="I181"/>
-      <c r="J181" s="45"/>
+      <c r="J181" s="44"/>
       <c r="K181"/>
       <c r="L181"/>
       <c r="M181"/>
@@ -8996,9 +9330,9 @@
       <c r="E182"/>
       <c r="F182"/>
       <c r="G182"/>
-      <c r="H182" s="173"/>
+      <c r="H182" s="167"/>
       <c r="I182"/>
-      <c r="J182" s="45"/>
+      <c r="J182" s="44"/>
       <c r="K182"/>
       <c r="L182"/>
       <c r="M182"/>
@@ -9012,9 +9346,9 @@
       <c r="E183"/>
       <c r="F183"/>
       <c r="G183"/>
-      <c r="H183" s="173"/>
+      <c r="H183" s="167"/>
       <c r="I183"/>
-      <c r="J183" s="45"/>
+      <c r="J183" s="44"/>
       <c r="K183"/>
       <c r="L183"/>
       <c r="M183"/>
@@ -9028,9 +9362,9 @@
       <c r="E184"/>
       <c r="F184"/>
       <c r="G184"/>
-      <c r="H184" s="173"/>
+      <c r="H184" s="167"/>
       <c r="I184"/>
-      <c r="J184" s="45"/>
+      <c r="J184" s="44"/>
       <c r="K184"/>
       <c r="L184"/>
       <c r="M184"/>
@@ -9044,9 +9378,9 @@
       <c r="E185"/>
       <c r="F185"/>
       <c r="G185"/>
-      <c r="H185" s="173"/>
+      <c r="H185" s="167"/>
       <c r="I185"/>
-      <c r="J185" s="45"/>
+      <c r="J185" s="44"/>
       <c r="K185"/>
       <c r="L185"/>
       <c r="M185"/>
@@ -9060,9 +9394,9 @@
       <c r="E186"/>
       <c r="F186"/>
       <c r="G186"/>
-      <c r="H186" s="173"/>
+      <c r="H186" s="167"/>
       <c r="I186"/>
-      <c r="J186" s="45"/>
+      <c r="J186" s="44"/>
       <c r="K186"/>
       <c r="L186"/>
       <c r="M186"/>
@@ -9076,9 +9410,9 @@
       <c r="E187"/>
       <c r="F187"/>
       <c r="G187"/>
-      <c r="H187" s="173"/>
+      <c r="H187" s="167"/>
       <c r="I187"/>
-      <c r="J187" s="45"/>
+      <c r="J187" s="44"/>
       <c r="K187"/>
       <c r="L187"/>
       <c r="M187"/>
@@ -9092,9 +9426,9 @@
       <c r="E188"/>
       <c r="F188"/>
       <c r="G188"/>
-      <c r="H188" s="173"/>
+      <c r="H188" s="167"/>
       <c r="I188"/>
-      <c r="J188" s="45"/>
+      <c r="J188" s="44"/>
       <c r="K188"/>
       <c r="L188"/>
       <c r="M188"/>
@@ -9108,9 +9442,9 @@
       <c r="E189"/>
       <c r="F189"/>
       <c r="G189"/>
-      <c r="H189" s="173"/>
+      <c r="H189" s="167"/>
       <c r="I189"/>
-      <c r="J189" s="45"/>
+      <c r="J189" s="44"/>
       <c r="K189"/>
       <c r="L189"/>
       <c r="M189"/>
@@ -9124,9 +9458,9 @@
       <c r="E190"/>
       <c r="F190"/>
       <c r="G190"/>
-      <c r="H190" s="173"/>
+      <c r="H190" s="167"/>
       <c r="I190"/>
-      <c r="J190" s="45"/>
+      <c r="J190" s="44"/>
       <c r="K190"/>
       <c r="L190"/>
       <c r="M190"/>
@@ -9140,9 +9474,9 @@
       <c r="E191"/>
       <c r="F191"/>
       <c r="G191"/>
-      <c r="H191" s="173"/>
+      <c r="H191" s="167"/>
       <c r="I191"/>
-      <c r="J191" s="45"/>
+      <c r="J191" s="44"/>
       <c r="K191"/>
       <c r="L191"/>
       <c r="M191"/>
@@ -9156,9 +9490,9 @@
       <c r="E192"/>
       <c r="F192"/>
       <c r="G192"/>
-      <c r="H192" s="173"/>
+      <c r="H192" s="167"/>
       <c r="I192"/>
-      <c r="J192" s="45"/>
+      <c r="J192" s="44"/>
       <c r="K192"/>
       <c r="L192"/>
       <c r="M192"/>
@@ -9172,9 +9506,9 @@
       <c r="E193"/>
       <c r="F193"/>
       <c r="G193"/>
-      <c r="H193" s="173"/>
+      <c r="H193" s="167"/>
       <c r="I193"/>
-      <c r="J193" s="45"/>
+      <c r="J193" s="44"/>
       <c r="K193"/>
       <c r="L193"/>
       <c r="M193"/>
@@ -9188,9 +9522,9 @@
       <c r="E194"/>
       <c r="F194"/>
       <c r="G194"/>
-      <c r="H194" s="173"/>
+      <c r="H194" s="167"/>
       <c r="I194"/>
-      <c r="J194" s="45"/>
+      <c r="J194" s="44"/>
       <c r="K194"/>
       <c r="L194"/>
       <c r="M194"/>
@@ -9204,9 +9538,9 @@
       <c r="E195"/>
       <c r="F195"/>
       <c r="G195"/>
-      <c r="H195" s="173"/>
+      <c r="H195" s="167"/>
       <c r="I195"/>
-      <c r="J195" s="45"/>
+      <c r="J195" s="44"/>
       <c r="K195"/>
       <c r="L195"/>
       <c r="M195"/>
@@ -9220,9 +9554,9 @@
       <c r="E196"/>
       <c r="F196"/>
       <c r="G196"/>
-      <c r="H196" s="173"/>
+      <c r="H196" s="167"/>
       <c r="I196"/>
-      <c r="J196" s="45"/>
+      <c r="J196" s="44"/>
       <c r="K196"/>
       <c r="L196"/>
       <c r="M196"/>
@@ -9236,9 +9570,9 @@
       <c r="E197"/>
       <c r="F197"/>
       <c r="G197"/>
-      <c r="H197" s="173"/>
+      <c r="H197" s="167"/>
       <c r="I197"/>
-      <c r="J197" s="45"/>
+      <c r="J197" s="44"/>
       <c r="K197"/>
       <c r="L197"/>
       <c r="M197"/>
@@ -9252,9 +9586,9 @@
       <c r="E198"/>
       <c r="F198"/>
       <c r="G198"/>
-      <c r="H198" s="173"/>
+      <c r="H198" s="167"/>
       <c r="I198"/>
-      <c r="J198" s="45"/>
+      <c r="J198" s="44"/>
       <c r="K198"/>
       <c r="L198"/>
       <c r="M198"/>
@@ -9268,9 +9602,9 @@
       <c r="E199"/>
       <c r="F199"/>
       <c r="G199"/>
-      <c r="H199" s="173"/>
+      <c r="H199" s="167"/>
       <c r="I199"/>
-      <c r="J199" s="45"/>
+      <c r="J199" s="44"/>
       <c r="K199"/>
       <c r="L199"/>
       <c r="M199"/>
@@ -9284,9 +9618,9 @@
       <c r="E200"/>
       <c r="F200"/>
       <c r="G200"/>
-      <c r="H200" s="173"/>
+      <c r="H200" s="167"/>
       <c r="I200"/>
-      <c r="J200" s="45"/>
+      <c r="J200" s="44"/>
       <c r="K200"/>
       <c r="L200"/>
       <c r="M200"/>
@@ -9300,9 +9634,9 @@
       <c r="E201"/>
       <c r="F201"/>
       <c r="G201"/>
-      <c r="H201" s="173"/>
+      <c r="H201" s="167"/>
       <c r="I201"/>
-      <c r="J201" s="45"/>
+      <c r="J201" s="44"/>
       <c r="K201"/>
       <c r="L201"/>
       <c r="M201"/>
@@ -9316,9 +9650,9 @@
       <c r="E202"/>
       <c r="F202"/>
       <c r="G202"/>
-      <c r="H202" s="173"/>
+      <c r="H202" s="167"/>
       <c r="I202"/>
-      <c r="J202" s="45"/>
+      <c r="J202" s="44"/>
       <c r="K202"/>
       <c r="L202"/>
       <c r="M202"/>
@@ -9332,9 +9666,9 @@
       <c r="E203"/>
       <c r="F203"/>
       <c r="G203"/>
-      <c r="H203" s="173"/>
+      <c r="H203" s="167"/>
       <c r="I203"/>
-      <c r="J203" s="45"/>
+      <c r="J203" s="44"/>
       <c r="K203"/>
       <c r="L203"/>
       <c r="M203"/>
@@ -9348,9 +9682,9 @@
       <c r="E204"/>
       <c r="F204"/>
       <c r="G204"/>
-      <c r="H204" s="173"/>
+      <c r="H204" s="167"/>
       <c r="I204"/>
-      <c r="J204" s="45"/>
+      <c r="J204" s="44"/>
       <c r="K204"/>
       <c r="L204"/>
       <c r="M204"/>
@@ -9364,9 +9698,9 @@
       <c r="E205"/>
       <c r="F205"/>
       <c r="G205"/>
-      <c r="H205" s="173"/>
+      <c r="H205" s="167"/>
       <c r="I205"/>
-      <c r="J205" s="45"/>
+      <c r="J205" s="44"/>
       <c r="K205"/>
       <c r="L205"/>
       <c r="M205"/>
@@ -9380,9 +9714,9 @@
       <c r="E206"/>
       <c r="F206"/>
       <c r="G206"/>
-      <c r="H206" s="173"/>
+      <c r="H206" s="167"/>
       <c r="I206"/>
-      <c r="J206" s="45"/>
+      <c r="J206" s="44"/>
       <c r="K206"/>
       <c r="L206"/>
       <c r="M206"/>
@@ -9396,9 +9730,9 @@
       <c r="E207"/>
       <c r="F207"/>
       <c r="G207"/>
-      <c r="H207" s="173"/>
+      <c r="H207" s="167"/>
       <c r="I207"/>
-      <c r="J207" s="45"/>
+      <c r="J207" s="44"/>
       <c r="K207"/>
       <c r="L207"/>
       <c r="M207"/>
@@ -9412,9 +9746,9 @@
       <c r="E208"/>
       <c r="F208"/>
       <c r="G208"/>
-      <c r="H208" s="173"/>
+      <c r="H208" s="167"/>
       <c r="I208"/>
-      <c r="J208" s="45"/>
+      <c r="J208" s="44"/>
       <c r="K208"/>
       <c r="L208"/>
       <c r="M208"/>
@@ -9428,9 +9762,9 @@
       <c r="E209"/>
       <c r="F209"/>
       <c r="G209"/>
-      <c r="H209" s="173"/>
+      <c r="H209" s="167"/>
       <c r="I209"/>
-      <c r="J209" s="45"/>
+      <c r="J209" s="44"/>
       <c r="K209"/>
       <c r="L209"/>
       <c r="M209"/>
@@ -9444,9 +9778,9 @@
       <c r="E210"/>
       <c r="F210"/>
       <c r="G210"/>
-      <c r="H210" s="173"/>
+      <c r="H210" s="167"/>
       <c r="I210"/>
-      <c r="J210" s="45"/>
+      <c r="J210" s="44"/>
       <c r="K210"/>
       <c r="L210"/>
       <c r="M210"/>
@@ -9460,9 +9794,9 @@
       <c r="E211"/>
       <c r="F211"/>
       <c r="G211"/>
-      <c r="H211" s="173"/>
+      <c r="H211" s="167"/>
       <c r="I211"/>
-      <c r="J211" s="45"/>
+      <c r="J211" s="44"/>
       <c r="K211"/>
       <c r="L211"/>
       <c r="M211"/>
@@ -9476,9 +9810,9 @@
       <c r="E212"/>
       <c r="F212"/>
       <c r="G212"/>
-      <c r="H212" s="173"/>
+      <c r="H212" s="167"/>
       <c r="I212"/>
-      <c r="J212" s="45"/>
+      <c r="J212" s="44"/>
       <c r="K212"/>
       <c r="L212"/>
       <c r="M212"/>
@@ -9492,9 +9826,9 @@
       <c r="E213"/>
       <c r="F213"/>
       <c r="G213"/>
-      <c r="H213" s="173"/>
+      <c r="H213" s="167"/>
       <c r="I213"/>
-      <c r="J213" s="45"/>
+      <c r="J213" s="44"/>
       <c r="K213"/>
       <c r="L213"/>
       <c r="M213"/>
@@ -9508,9 +9842,9 @@
       <c r="E214"/>
       <c r="F214"/>
       <c r="G214"/>
-      <c r="H214" s="173"/>
+      <c r="H214" s="167"/>
       <c r="I214"/>
-      <c r="J214" s="45"/>
+      <c r="J214" s="44"/>
       <c r="K214"/>
       <c r="L214"/>
       <c r="M214"/>
@@ -9524,9 +9858,9 @@
       <c r="E215"/>
       <c r="F215"/>
       <c r="G215"/>
-      <c r="H215" s="173"/>
+      <c r="H215" s="167"/>
       <c r="I215"/>
-      <c r="J215" s="45"/>
+      <c r="J215" s="44"/>
       <c r="K215"/>
       <c r="L215"/>
       <c r="M215"/>
@@ -9540,9 +9874,9 @@
       <c r="E216"/>
       <c r="F216"/>
       <c r="G216"/>
-      <c r="H216" s="173"/>
+      <c r="H216" s="167"/>
       <c r="I216"/>
-      <c r="J216" s="45"/>
+      <c r="J216" s="44"/>
       <c r="K216"/>
       <c r="L216"/>
       <c r="M216"/>
@@ -9556,9 +9890,9 @@
       <c r="E217"/>
       <c r="F217"/>
       <c r="G217"/>
-      <c r="H217" s="173"/>
+      <c r="H217" s="167"/>
       <c r="I217"/>
-      <c r="J217" s="45"/>
+      <c r="J217" s="44"/>
       <c r="K217"/>
       <c r="L217"/>
       <c r="M217"/>
@@ -9572,9 +9906,9 @@
       <c r="E218"/>
       <c r="F218"/>
       <c r="G218"/>
-      <c r="H218" s="173"/>
+      <c r="H218" s="167"/>
       <c r="I218"/>
-      <c r="J218" s="45"/>
+      <c r="J218" s="44"/>
       <c r="K218"/>
       <c r="L218"/>
       <c r="M218"/>
@@ -9588,9 +9922,9 @@
       <c r="E219"/>
       <c r="F219"/>
       <c r="G219"/>
-      <c r="H219" s="173"/>
+      <c r="H219" s="167"/>
       <c r="I219"/>
-      <c r="J219" s="45"/>
+      <c r="J219" s="44"/>
       <c r="K219"/>
       <c r="L219"/>
       <c r="M219"/>
@@ -9604,9 +9938,9 @@
       <c r="E220"/>
       <c r="F220"/>
       <c r="G220"/>
-      <c r="H220" s="173"/>
+      <c r="H220" s="167"/>
       <c r="I220"/>
-      <c r="J220" s="45"/>
+      <c r="J220" s="44"/>
       <c r="K220"/>
       <c r="L220"/>
       <c r="M220"/>
@@ -9620,9 +9954,9 @@
       <c r="E221"/>
       <c r="F221"/>
       <c r="G221"/>
-      <c r="H221" s="173"/>
+      <c r="H221" s="167"/>
       <c r="I221"/>
-      <c r="J221" s="45"/>
+      <c r="J221" s="44"/>
       <c r="K221"/>
       <c r="L221"/>
       <c r="M221"/>
@@ -9636,9 +9970,9 @@
       <c r="E222"/>
       <c r="F222"/>
       <c r="G222"/>
-      <c r="H222" s="173"/>
+      <c r="H222" s="167"/>
       <c r="I222"/>
-      <c r="J222" s="45"/>
+      <c r="J222" s="44"/>
       <c r="K222"/>
       <c r="L222"/>
       <c r="M222"/>
@@ -9652,9 +9986,9 @@
       <c r="E223"/>
       <c r="F223"/>
       <c r="G223"/>
-      <c r="H223" s="173"/>
+      <c r="H223" s="167"/>
       <c r="I223"/>
-      <c r="J223" s="45"/>
+      <c r="J223" s="44"/>
       <c r="K223"/>
       <c r="L223"/>
       <c r="M223"/>
@@ -9668,9 +10002,9 @@
       <c r="E224"/>
       <c r="F224"/>
       <c r="G224"/>
-      <c r="H224" s="173"/>
+      <c r="H224" s="167"/>
       <c r="I224"/>
-      <c r="J224" s="45"/>
+      <c r="J224" s="44"/>
       <c r="K224"/>
       <c r="L224"/>
       <c r="M224"/>
@@ -9684,9 +10018,9 @@
       <c r="E225"/>
       <c r="F225"/>
       <c r="G225"/>
-      <c r="H225" s="173"/>
+      <c r="H225" s="167"/>
       <c r="I225"/>
-      <c r="J225" s="45"/>
+      <c r="J225" s="44"/>
       <c r="K225"/>
       <c r="L225"/>
       <c r="M225"/>
@@ -9700,9 +10034,9 @@
       <c r="E226"/>
       <c r="F226"/>
       <c r="G226"/>
-      <c r="H226" s="173"/>
+      <c r="H226" s="167"/>
       <c r="I226"/>
-      <c r="J226" s="45"/>
+      <c r="J226" s="44"/>
       <c r="K226"/>
       <c r="L226"/>
       <c r="M226"/>
@@ -9716,9 +10050,9 @@
       <c r="E227"/>
       <c r="F227"/>
       <c r="G227"/>
-      <c r="H227" s="173"/>
+      <c r="H227" s="167"/>
       <c r="I227"/>
-      <c r="J227" s="45"/>
+      <c r="J227" s="44"/>
       <c r="K227"/>
       <c r="L227"/>
       <c r="M227"/>
@@ -9732,9 +10066,9 @@
       <c r="E228"/>
       <c r="F228"/>
       <c r="G228"/>
-      <c r="H228" s="173"/>
+      <c r="H228" s="167"/>
       <c r="I228"/>
-      <c r="J228" s="45"/>
+      <c r="J228" s="44"/>
       <c r="K228"/>
       <c r="L228"/>
       <c r="M228"/>
@@ -9748,9 +10082,9 @@
       <c r="E229"/>
       <c r="F229"/>
       <c r="G229"/>
-      <c r="H229" s="173"/>
+      <c r="H229" s="167"/>
       <c r="I229"/>
-      <c r="J229" s="45"/>
+      <c r="J229" s="44"/>
       <c r="K229"/>
       <c r="L229"/>
       <c r="M229"/>
@@ -9764,9 +10098,9 @@
       <c r="E230"/>
       <c r="F230"/>
       <c r="G230"/>
-      <c r="H230" s="173"/>
+      <c r="H230" s="167"/>
       <c r="I230"/>
-      <c r="J230" s="45"/>
+      <c r="J230" s="44"/>
       <c r="K230"/>
       <c r="L230"/>
       <c r="M230"/>
@@ -9780,9 +10114,9 @@
       <c r="E231"/>
       <c r="F231"/>
       <c r="G231"/>
-      <c r="H231" s="173"/>
+      <c r="H231" s="167"/>
       <c r="I231"/>
-      <c r="J231" s="45"/>
+      <c r="J231" s="44"/>
       <c r="K231"/>
       <c r="L231"/>
       <c r="M231"/>
@@ -9796,9 +10130,9 @@
       <c r="E232"/>
       <c r="F232"/>
       <c r="G232"/>
-      <c r="H232" s="173"/>
+      <c r="H232" s="167"/>
       <c r="I232"/>
-      <c r="J232" s="45"/>
+      <c r="J232" s="44"/>
       <c r="K232"/>
       <c r="L232"/>
       <c r="M232"/>
@@ -9812,9 +10146,9 @@
       <c r="E233"/>
       <c r="F233"/>
       <c r="G233"/>
-      <c r="H233" s="173"/>
+      <c r="H233" s="167"/>
       <c r="I233"/>
-      <c r="J233" s="45"/>
+      <c r="J233" s="44"/>
       <c r="K233"/>
       <c r="L233"/>
       <c r="M233"/>
@@ -9828,9 +10162,9 @@
       <c r="E234"/>
       <c r="F234"/>
       <c r="G234"/>
-      <c r="H234" s="173"/>
+      <c r="H234" s="167"/>
       <c r="I234"/>
-      <c r="J234" s="45"/>
+      <c r="J234" s="44"/>
       <c r="K234"/>
       <c r="L234"/>
       <c r="M234"/>
@@ -9844,9 +10178,9 @@
       <c r="E235"/>
       <c r="F235"/>
       <c r="G235"/>
-      <c r="H235" s="173"/>
+      <c r="H235" s="167"/>
       <c r="I235"/>
-      <c r="J235" s="45"/>
+      <c r="J235" s="44"/>
       <c r="K235"/>
       <c r="L235"/>
       <c r="M235"/>
@@ -9860,9 +10194,9 @@
       <c r="E236"/>
       <c r="F236"/>
       <c r="G236"/>
-      <c r="H236" s="173"/>
+      <c r="H236" s="167"/>
       <c r="I236"/>
-      <c r="J236" s="45"/>
+      <c r="J236" s="44"/>
       <c r="K236"/>
       <c r="L236"/>
       <c r="M236"/>
@@ -9876,9 +10210,9 @@
       <c r="E237"/>
       <c r="F237"/>
       <c r="G237"/>
-      <c r="H237" s="173"/>
+      <c r="H237" s="167"/>
       <c r="I237"/>
-      <c r="J237" s="45"/>
+      <c r="J237" s="44"/>
       <c r="K237"/>
       <c r="L237"/>
       <c r="M237"/>
@@ -9892,9 +10226,9 @@
       <c r="E238"/>
       <c r="F238"/>
       <c r="G238"/>
-      <c r="H238" s="173"/>
+      <c r="H238" s="167"/>
       <c r="I238"/>
-      <c r="J238" s="45"/>
+      <c r="J238" s="44"/>
       <c r="K238"/>
       <c r="L238"/>
       <c r="M238"/>
@@ -9908,9 +10242,9 @@
       <c r="E239"/>
       <c r="F239"/>
       <c r="G239"/>
-      <c r="H239" s="173"/>
+      <c r="H239" s="167"/>
       <c r="I239"/>
-      <c r="J239" s="45"/>
+      <c r="J239" s="44"/>
       <c r="K239"/>
       <c r="L239"/>
       <c r="M239"/>
@@ -9924,9 +10258,9 @@
       <c r="E240"/>
       <c r="F240"/>
       <c r="G240"/>
-      <c r="H240" s="173"/>
+      <c r="H240" s="167"/>
       <c r="I240"/>
-      <c r="J240" s="45"/>
+      <c r="J240" s="44"/>
       <c r="K240"/>
       <c r="L240"/>
       <c r="M240"/>
@@ -9940,9 +10274,9 @@
       <c r="E241"/>
       <c r="F241"/>
       <c r="G241"/>
-      <c r="H241" s="173"/>
+      <c r="H241" s="167"/>
       <c r="I241"/>
-      <c r="J241" s="45"/>
+      <c r="J241" s="44"/>
       <c r="K241"/>
       <c r="L241"/>
       <c r="M241"/>
@@ -9956,9 +10290,9 @@
       <c r="E242"/>
       <c r="F242"/>
       <c r="G242"/>
-      <c r="H242" s="173"/>
+      <c r="H242" s="167"/>
       <c r="I242"/>
-      <c r="J242" s="45"/>
+      <c r="J242" s="44"/>
       <c r="K242"/>
       <c r="L242"/>
       <c r="M242"/>
@@ -9972,9 +10306,9 @@
       <c r="E243"/>
       <c r="F243"/>
       <c r="G243"/>
-      <c r="H243" s="173"/>
+      <c r="H243" s="167"/>
       <c r="I243"/>
-      <c r="J243" s="45"/>
+      <c r="J243" s="44"/>
       <c r="K243"/>
       <c r="L243"/>
       <c r="M243"/>
@@ -9988,9 +10322,9 @@
       <c r="E244"/>
       <c r="F244"/>
       <c r="G244"/>
-      <c r="H244" s="173"/>
+      <c r="H244" s="167"/>
       <c r="I244"/>
-      <c r="J244" s="45"/>
+      <c r="J244" s="44"/>
       <c r="K244"/>
       <c r="L244"/>
       <c r="M244"/>
@@ -10004,9 +10338,9 @@
       <c r="E245"/>
       <c r="F245"/>
       <c r="G245"/>
-      <c r="H245" s="173"/>
+      <c r="H245" s="167"/>
       <c r="I245"/>
-      <c r="J245" s="45"/>
+      <c r="J245" s="44"/>
       <c r="K245"/>
       <c r="L245"/>
       <c r="M245"/>
@@ -10020,9 +10354,9 @@
       <c r="E246"/>
       <c r="F246"/>
       <c r="G246"/>
-      <c r="H246" s="173"/>
+      <c r="H246" s="167"/>
       <c r="I246"/>
-      <c r="J246" s="45"/>
+      <c r="J246" s="44"/>
       <c r="K246"/>
       <c r="L246"/>
       <c r="M246"/>
@@ -10036,9 +10370,9 @@
       <c r="E247"/>
       <c r="F247"/>
       <c r="G247"/>
-      <c r="H247" s="173"/>
+      <c r="H247" s="167"/>
       <c r="I247"/>
-      <c r="J247" s="45"/>
+      <c r="J247" s="44"/>
       <c r="K247"/>
       <c r="L247"/>
       <c r="M247"/>
@@ -10052,9 +10386,9 @@
       <c r="E248"/>
       <c r="F248"/>
       <c r="G248"/>
-      <c r="H248" s="173"/>
+      <c r="H248" s="167"/>
       <c r="I248"/>
-      <c r="J248" s="45"/>
+      <c r="J248" s="44"/>
       <c r="K248"/>
       <c r="L248"/>
       <c r="M248"/>
@@ -10068,9 +10402,9 @@
       <c r="E249"/>
       <c r="F249"/>
       <c r="G249"/>
-      <c r="H249" s="173"/>
+      <c r="H249" s="167"/>
       <c r="I249"/>
-      <c r="J249" s="45"/>
+      <c r="J249" s="44"/>
       <c r="K249"/>
       <c r="L249"/>
       <c r="M249"/>
@@ -10084,9 +10418,9 @@
       <c r="E250"/>
       <c r="F250"/>
       <c r="G250"/>
-      <c r="H250" s="173"/>
+      <c r="H250" s="167"/>
       <c r="I250"/>
-      <c r="J250" s="45"/>
+      <c r="J250" s="44"/>
       <c r="K250"/>
       <c r="L250"/>
       <c r="M250"/>
@@ -10100,9 +10434,9 @@
       <c r="E251"/>
       <c r="F251"/>
       <c r="G251"/>
-      <c r="H251" s="173"/>
+      <c r="H251" s="167"/>
       <c r="I251"/>
-      <c r="J251" s="45"/>
+      <c r="J251" s="44"/>
       <c r="K251"/>
       <c r="L251"/>
       <c r="M251"/>
@@ -10116,9 +10450,9 @@
       <c r="E252"/>
       <c r="F252"/>
       <c r="G252"/>
-      <c r="H252" s="173"/>
+      <c r="H252" s="167"/>
       <c r="I252"/>
-      <c r="J252" s="45"/>
+      <c r="J252" s="44"/>
       <c r="K252"/>
       <c r="L252"/>
       <c r="M252"/>
@@ -10132,9 +10466,9 @@
       <c r="E253"/>
       <c r="F253"/>
       <c r="G253"/>
-      <c r="H253" s="173"/>
+      <c r="H253" s="167"/>
       <c r="I253"/>
-      <c r="J253" s="45"/>
+      <c r="J253" s="44"/>
       <c r="K253"/>
       <c r="L253"/>
       <c r="M253"/>
@@ -10148,9 +10482,9 @@
       <c r="E254"/>
       <c r="F254"/>
       <c r="G254"/>
-      <c r="H254" s="173"/>
+      <c r="H254" s="167"/>
       <c r="I254"/>
-      <c r="J254" s="45"/>
+      <c r="J254" s="44"/>
       <c r="K254"/>
       <c r="L254"/>
       <c r="M254"/>
@@ -10164,9 +10498,9 @@
       <c r="E255"/>
       <c r="F255"/>
       <c r="G255"/>
-      <c r="H255" s="173"/>
+      <c r="H255" s="167"/>
       <c r="I255"/>
-      <c r="J255" s="45"/>
+      <c r="J255" s="44"/>
       <c r="K255"/>
       <c r="L255"/>
       <c r="M255"/>
@@ -10180,9 +10514,9 @@
       <c r="E256"/>
       <c r="F256"/>
       <c r="G256"/>
-      <c r="H256" s="173"/>
+      <c r="H256" s="167"/>
       <c r="I256"/>
-      <c r="J256" s="45"/>
+      <c r="J256" s="44"/>
       <c r="K256"/>
       <c r="L256"/>
       <c r="M256"/>
@@ -10196,9 +10530,9 @@
       <c r="E257"/>
       <c r="F257"/>
       <c r="G257"/>
-      <c r="H257" s="173"/>
+      <c r="H257" s="167"/>
       <c r="I257"/>
-      <c r="J257" s="45"/>
+      <c r="J257" s="44"/>
       <c r="K257"/>
       <c r="L257"/>
       <c r="M257"/>
@@ -10212,9 +10546,9 @@
       <c r="E258"/>
       <c r="F258"/>
       <c r="G258"/>
-      <c r="H258" s="173"/>
+      <c r="H258" s="167"/>
       <c r="I258"/>
-      <c r="J258" s="45"/>
+      <c r="J258" s="44"/>
       <c r="K258"/>
       <c r="L258"/>
       <c r="M258"/>
@@ -10228,9 +10562,9 @@
       <c r="E259"/>
       <c r="F259"/>
       <c r="G259"/>
-      <c r="H259" s="173"/>
+      <c r="H259" s="167"/>
       <c r="I259"/>
-      <c r="J259" s="45"/>
+      <c r="J259" s="44"/>
       <c r="K259"/>
       <c r="L259"/>
       <c r="M259"/>
@@ -10244,9 +10578,9 @@
       <c r="E260"/>
       <c r="F260"/>
       <c r="G260"/>
-      <c r="H260" s="173"/>
+      <c r="H260" s="167"/>
       <c r="I260"/>
-      <c r="J260" s="45"/>
+      <c r="J260" s="44"/>
       <c r="K260"/>
       <c r="L260"/>
       <c r="M260"/>
@@ -10260,9 +10594,9 @@
       <c r="E261"/>
       <c r="F261"/>
       <c r="G261"/>
-      <c r="H261" s="173"/>
+      <c r="H261" s="167"/>
       <c r="I261"/>
-      <c r="J261" s="45"/>
+      <c r="J261" s="44"/>
       <c r="K261"/>
       <c r="L261"/>
       <c r="M261"/>
@@ -10276,9 +10610,9 @@
       <c r="E262"/>
       <c r="F262"/>
       <c r="G262"/>
-      <c r="H262" s="173"/>
+      <c r="H262" s="167"/>
       <c r="I262"/>
-      <c r="J262" s="45"/>
+      <c r="J262" s="44"/>
       <c r="K262"/>
       <c r="L262"/>
       <c r="M262"/>
@@ -10292,9 +10626,9 @@
       <c r="E263"/>
       <c r="F263"/>
       <c r="G263"/>
-      <c r="H263" s="173"/>
+      <c r="H263" s="167"/>
       <c r="I263"/>
-      <c r="J263" s="45"/>
+      <c r="J263" s="44"/>
       <c r="K263"/>
       <c r="L263"/>
       <c r="M263"/>
@@ -10308,9 +10642,9 @@
       <c r="E264"/>
       <c r="F264"/>
       <c r="G264"/>
-      <c r="H264" s="173"/>
+      <c r="H264" s="167"/>
       <c r="I264"/>
-      <c r="J264" s="45"/>
+      <c r="J264" s="44"/>
       <c r="K264"/>
       <c r="L264"/>
       <c r="M264"/>
@@ -10324,9 +10658,9 @@
       <c r="E265"/>
       <c r="F265"/>
       <c r="G265"/>
-      <c r="H265" s="173"/>
+      <c r="H265" s="167"/>
       <c r="I265"/>
-      <c r="J265" s="45"/>
+      <c r="J265" s="44"/>
       <c r="K265"/>
       <c r="L265"/>
       <c r="M265"/>
@@ -10340,9 +10674,9 @@
       <c r="E266"/>
       <c r="F266"/>
       <c r="G266"/>
-      <c r="H266" s="173"/>
+      <c r="H266" s="167"/>
       <c r="I266"/>
-      <c r="J266" s="45"/>
+      <c r="J266" s="44"/>
       <c r="K266"/>
       <c r="L266"/>
       <c r="M266"/>
@@ -10356,9 +10690,9 @@
       <c r="E267"/>
       <c r="F267"/>
       <c r="G267"/>
-      <c r="H267" s="173"/>
+      <c r="H267" s="167"/>
       <c r="I267"/>
-      <c r="J267" s="45"/>
+      <c r="J267" s="44"/>
       <c r="K267"/>
       <c r="L267"/>
       <c r="M267"/>
@@ -10372,9 +10706,9 @@
       <c r="E268"/>
       <c r="F268"/>
       <c r="G268"/>
-      <c r="H268" s="173"/>
+      <c r="H268" s="167"/>
       <c r="I268"/>
-      <c r="J268" s="45"/>
+      <c r="J268" s="44"/>
       <c r="K268"/>
       <c r="L268"/>
       <c r="M268"/>
@@ -10388,9 +10722,9 @@
       <c r="E269"/>
       <c r="F269"/>
       <c r="G269"/>
-      <c r="H269" s="173"/>
+      <c r="H269" s="167"/>
       <c r="I269"/>
-      <c r="J269" s="45"/>
+      <c r="J269" s="44"/>
       <c r="K269"/>
       <c r="L269"/>
       <c r="M269"/>
@@ -10404,9 +10738,9 @@
       <c r="E270"/>
       <c r="F270"/>
       <c r="G270"/>
-      <c r="H270" s="173"/>
+      <c r="H270" s="167"/>
       <c r="I270"/>
-      <c r="J270" s="45"/>
+      <c r="J270" s="44"/>
       <c r="K270"/>
       <c r="L270"/>
       <c r="M270"/>
@@ -10420,9 +10754,9 @@
       <c r="E271"/>
       <c r="F271"/>
       <c r="G271"/>
-      <c r="H271" s="173"/>
+      <c r="H271" s="167"/>
       <c r="I271"/>
-      <c r="J271" s="45"/>
+      <c r="J271" s="44"/>
       <c r="K271"/>
       <c r="L271"/>
       <c r="M271"/>
@@ -10436,9 +10770,9 @@
       <c r="E272"/>
       <c r="F272"/>
       <c r="G272"/>
-      <c r="H272" s="173"/>
+      <c r="H272" s="167"/>
       <c r="I272"/>
-      <c r="J272" s="45"/>
+      <c r="J272" s="44"/>
       <c r="K272"/>
       <c r="L272"/>
       <c r="M272"/>
@@ -10452,9 +10786,9 @@
       <c r="E273"/>
       <c r="F273"/>
       <c r="G273"/>
-      <c r="H273" s="173"/>
+      <c r="H273" s="167"/>
       <c r="I273"/>
-      <c r="J273" s="45"/>
+      <c r="J273" s="44"/>
       <c r="K273"/>
       <c r="L273"/>
       <c r="M273"/>
@@ -10468,9 +10802,9 @@
       <c r="E274"/>
       <c r="F274"/>
       <c r="G274"/>
-      <c r="H274" s="173"/>
+      <c r="H274" s="167"/>
       <c r="I274"/>
-      <c r="J274" s="45"/>
+      <c r="J274" s="44"/>
       <c r="K274"/>
       <c r="L274"/>
       <c r="M274"/>
@@ -10484,9 +10818,9 @@
       <c r="E275"/>
       <c r="F275"/>
       <c r="G275"/>
-      <c r="H275" s="173"/>
+      <c r="H275" s="167"/>
       <c r="I275"/>
-      <c r="J275" s="45"/>
+      <c r="J275" s="44"/>
       <c r="K275"/>
       <c r="L275"/>
       <c r="M275"/>
@@ -10500,9 +10834,9 @@
       <c r="E276"/>
       <c r="F276"/>
       <c r="G276"/>
-      <c r="H276" s="173"/>
+      <c r="H276" s="167"/>
       <c r="I276"/>
-      <c r="J276" s="45"/>
+      <c r="J276" s="44"/>
       <c r="K276"/>
       <c r="L276"/>
       <c r="M276"/>
@@ -10516,9 +10850,9 @@
       <c r="E277"/>
       <c r="F277"/>
       <c r="G277"/>
-      <c r="H277" s="173"/>
+      <c r="H277" s="167"/>
       <c r="I277"/>
-      <c r="J277" s="45"/>
+      <c r="J277" s="44"/>
       <c r="K277"/>
       <c r="L277"/>
       <c r="M277"/>
@@ -10532,9 +10866,9 @@
       <c r="E278"/>
       <c r="F278"/>
       <c r="G278"/>
-      <c r="H278" s="173"/>
+      <c r="H278" s="167"/>
       <c r="I278"/>
-      <c r="J278" s="45"/>
+      <c r="J278" s="44"/>
       <c r="K278"/>
       <c r="L278"/>
       <c r="M278"/>
@@ -10548,9 +10882,9 @@
       <c r="E279"/>
       <c r="F279"/>
       <c r="G279"/>
-      <c r="H279" s="173"/>
+      <c r="H279" s="167"/>
       <c r="I279"/>
-      <c r="J279" s="45"/>
+      <c r="J279" s="44"/>
       <c r="K279"/>
       <c r="L279"/>
       <c r="M279"/>
@@ -10564,9 +10898,9 @@
       <c r="E280"/>
       <c r="F280"/>
       <c r="G280"/>
-      <c r="H280" s="173"/>
+      <c r="H280" s="167"/>
       <c r="I280"/>
-      <c r="J280" s="45"/>
+      <c r="J280" s="44"/>
       <c r="K280"/>
       <c r="L280"/>
       <c r="M280"/>
@@ -10580,9 +10914,9 @@
       <c r="E281"/>
       <c r="F281"/>
       <c r="G281"/>
-      <c r="H281" s="173"/>
+      <c r="H281" s="167"/>
       <c r="I281"/>
-      <c r="J281" s="45"/>
+      <c r="J281" s="44"/>
       <c r="K281"/>
       <c r="L281"/>
       <c r="M281"/>
@@ -10596,9 +10930,9 @@
       <c r="E282"/>
       <c r="F282"/>
       <c r="G282"/>
-      <c r="H282" s="173"/>
+      <c r="H282" s="167"/>
       <c r="I282"/>
-      <c r="J282" s="45"/>
+      <c r="J282" s="44"/>
       <c r="K282"/>
       <c r="L282"/>
       <c r="M282"/>
@@ -10612,9 +10946,9 @@
       <c r="E283"/>
       <c r="F283"/>
       <c r="G283"/>
-      <c r="H283" s="173"/>
+      <c r="H283" s="167"/>
       <c r="I283"/>
-      <c r="J283" s="45"/>
+      <c r="J283" s="44"/>
       <c r="K283"/>
       <c r="L283"/>
       <c r="M283"/>
@@ -10628,9 +10962,9 @@
       <c r="E284"/>
       <c r="F284"/>
       <c r="G284"/>
-      <c r="H284" s="173"/>
+      <c r="H284" s="167"/>
       <c r="I284"/>
-      <c r="J284" s="45"/>
+      <c r="J284" s="44"/>
       <c r="K284"/>
       <c r="L284"/>
       <c r="M284"/>
@@ -10644,9 +10978,9 @@
       <c r="E285"/>
       <c r="F285"/>
       <c r="G285"/>
-      <c r="H285" s="173"/>
+      <c r="H285" s="167"/>
       <c r="I285"/>
-      <c r="J285" s="45"/>
+      <c r="J285" s="44"/>
       <c r="K285"/>
       <c r="L285"/>
       <c r="M285"/>
@@ -10660,9 +10994,9 @@
       <c r="E286"/>
       <c r="F286"/>
       <c r="G286"/>
-      <c r="H286" s="173"/>
+      <c r="H286" s="167"/>
       <c r="I286"/>
-      <c r="J286" s="45"/>
+      <c r="J286" s="44"/>
       <c r="K286"/>
       <c r="L286"/>
       <c r="M286"/>
@@ -10676,9 +11010,9 @@
       <c r="E287"/>
       <c r="F287"/>
       <c r="G287"/>
-      <c r="H287" s="173"/>
+      <c r="H287" s="167"/>
       <c r="I287"/>
-      <c r="J287" s="45"/>
+      <c r="J287" s="44"/>
       <c r="K287"/>
       <c r="L287"/>
       <c r="M287"/>
@@ -10692,9 +11026,9 @@
       <c r="E288"/>
       <c r="F288"/>
       <c r="G288"/>
-      <c r="H288" s="173"/>
+      <c r="H288" s="167"/>
       <c r="I288"/>
-      <c r="J288" s="45"/>
+      <c r="J288" s="44"/>
       <c r="K288"/>
       <c r="L288"/>
       <c r="M288"/>
@@ -10708,9 +11042,9 @@
       <c r="E289"/>
       <c r="F289"/>
       <c r="G289"/>
-      <c r="H289" s="173"/>
+      <c r="H289" s="167"/>
       <c r="I289"/>
-      <c r="J289" s="45"/>
+      <c r="J289" s="44"/>
       <c r="K289"/>
       <c r="L289"/>
       <c r="M289"/>
@@ -10724,9 +11058,9 @@
       <c r="E290"/>
       <c r="F290"/>
       <c r="G290"/>
-      <c r="H290" s="173"/>
+      <c r="H290" s="167"/>
       <c r="I290"/>
-      <c r="J290" s="45"/>
+      <c r="J290" s="44"/>
       <c r="K290"/>
       <c r="L290"/>
       <c r="M290"/>
@@ -10740,9 +11074,9 @@
       <c r="E291"/>
       <c r="F291"/>
       <c r="G291"/>
-      <c r="H291" s="173"/>
+      <c r="H291" s="167"/>
       <c r="I291"/>
-      <c r="J291" s="45"/>
+      <c r="J291" s="44"/>
       <c r="K291"/>
       <c r="L291"/>
       <c r="M291"/>
@@ -10756,9 +11090,9 @@
       <c r="E292"/>
       <c r="F292"/>
       <c r="G292"/>
-      <c r="H292" s="173"/>
+      <c r="H292" s="167"/>
       <c r="I292"/>
-      <c r="J292" s="45"/>
+      <c r="J292" s="44"/>
       <c r="K292"/>
       <c r="L292"/>
       <c r="M292"/>
@@ -10772,9 +11106,9 @@
       <c r="E293"/>
       <c r="F293"/>
       <c r="G293"/>
-      <c r="H293" s="173"/>
+      <c r="H293" s="167"/>
       <c r="I293"/>
-      <c r="J293" s="45"/>
+      <c r="J293" s="44"/>
       <c r="K293"/>
       <c r="L293"/>
       <c r="M293"/>
@@ -10788,9 +11122,9 @@
       <c r="E294"/>
       <c r="F294"/>
       <c r="G294"/>
-      <c r="H294" s="173"/>
+      <c r="H294" s="167"/>
       <c r="I294"/>
-      <c r="J294" s="45"/>
+      <c r="J294" s="44"/>
       <c r="K294"/>
       <c r="L294"/>
       <c r="M294"/>
@@ -10804,9 +11138,9 @@
       <c r="E295"/>
       <c r="F295"/>
       <c r="G295"/>
-      <c r="H295" s="173"/>
+      <c r="H295" s="167"/>
       <c r="I295"/>
-      <c r="J295" s="45"/>
+      <c r="J295" s="44"/>
       <c r="K295"/>
       <c r="L295"/>
       <c r="M295"/>
@@ -10820,9 +11154,9 @@
       <c r="E296"/>
       <c r="F296"/>
       <c r="G296"/>
-      <c r="H296" s="173"/>
+      <c r="H296" s="167"/>
       <c r="I296"/>
-      <c r="J296" s="45"/>
+      <c r="J296" s="44"/>
       <c r="K296"/>
       <c r="L296"/>
       <c r="M296"/>
@@ -10836,9 +11170,9 @@
       <c r="E297"/>
       <c r="F297"/>
       <c r="G297"/>
-      <c r="H297" s="173"/>
+      <c r="H297" s="167"/>
       <c r="I297"/>
-      <c r="J297" s="45"/>
+      <c r="J297" s="44"/>
       <c r="K297"/>
       <c r="L297"/>
       <c r="M297"/>
@@ -10852,9 +11186,9 @@
       <c r="E298"/>
       <c r="F298"/>
       <c r="G298"/>
-      <c r="H298" s="173"/>
+      <c r="H298" s="167"/>
       <c r="I298"/>
-      <c r="J298" s="45"/>
+      <c r="J298" s="44"/>
       <c r="K298"/>
       <c r="L298"/>
       <c r="M298"/>
@@ -10868,9 +11202,9 @@
       <c r="E299"/>
       <c r="F299"/>
       <c r="G299"/>
-      <c r="H299" s="173"/>
+      <c r="H299" s="167"/>
       <c r="I299"/>
-      <c r="J299" s="45"/>
+      <c r="J299" s="44"/>
       <c r="K299"/>
       <c r="L299"/>
       <c r="M299"/>
@@ -10884,9 +11218,9 @@
       <c r="E300"/>
       <c r="F300"/>
       <c r="G300"/>
-      <c r="H300" s="173"/>
+      <c r="H300" s="167"/>
       <c r="I300"/>
-      <c r="J300" s="45"/>
+      <c r="J300" s="44"/>
       <c r="K300"/>
       <c r="L300"/>
       <c r="M300"/>
@@ -10900,9 +11234,9 @@
       <c r="E301"/>
       <c r="F301"/>
       <c r="G301"/>
-      <c r="H301" s="173"/>
+      <c r="H301" s="167"/>
       <c r="I301"/>
-      <c r="J301" s="45"/>
+      <c r="J301" s="44"/>
       <c r="K301"/>
       <c r="L301"/>
       <c r="M301"/>
@@ -10916,9 +11250,9 @@
       <c r="E302"/>
       <c r="F302"/>
       <c r="G302"/>
-      <c r="H302" s="173"/>
+      <c r="H302" s="167"/>
       <c r="I302"/>
-      <c r="J302" s="45"/>
+      <c r="J302" s="44"/>
       <c r="K302"/>
       <c r="L302"/>
       <c r="M302"/>
@@ -10932,9 +11266,9 @@
       <c r="E303"/>
       <c r="F303"/>
       <c r="G303"/>
-      <c r="H303" s="173"/>
+      <c r="H303" s="167"/>
       <c r="I303"/>
-      <c r="J303" s="45"/>
+      <c r="J303" s="44"/>
       <c r="K303"/>
       <c r="L303"/>
       <c r="M303"/>
@@ -10948,9 +11282,9 @@
       <c r="E304"/>
       <c r="F304"/>
       <c r="G304"/>
-      <c r="H304" s="173"/>
+      <c r="H304" s="167"/>
       <c r="I304"/>
-      <c r="J304" s="45"/>
+      <c r="J304" s="44"/>
       <c r="K304"/>
       <c r="L304"/>
       <c r="M304"/>
@@ -10964,9 +11298,9 @@
       <c r="E305"/>
       <c r="F305"/>
       <c r="G305"/>
-      <c r="H305" s="173"/>
+      <c r="H305" s="167"/>
       <c r="I305"/>
-      <c r="J305" s="45"/>
+      <c r="J305" s="44"/>
       <c r="K305"/>
       <c r="L305"/>
       <c r="M305"/>
@@ -10980,9 +11314,9 @@
       <c r="E306"/>
       <c r="F306"/>
       <c r="G306"/>
-      <c r="H306" s="173"/>
+      <c r="H306" s="167"/>
       <c r="I306"/>
-      <c r="J306" s="45"/>
+      <c r="J306" s="44"/>
       <c r="K306"/>
       <c r="L306"/>
       <c r="M306"/>
@@ -10996,9 +11330,9 @@
       <c r="E307"/>
       <c r="F307"/>
       <c r="G307"/>
-      <c r="H307" s="173"/>
+      <c r="H307" s="167"/>
       <c r="I307"/>
-      <c r="J307" s="45"/>
+      <c r="J307" s="44"/>
       <c r="K307"/>
       <c r="L307"/>
       <c r="M307"/>
@@ -11012,9 +11346,9 @@
       <c r="E308"/>
       <c r="F308"/>
       <c r="G308"/>
-      <c r="H308" s="173"/>
+      <c r="H308" s="167"/>
       <c r="I308"/>
-      <c r="J308" s="45"/>
+      <c r="J308" s="44"/>
       <c r="K308"/>
       <c r="L308"/>
       <c r="M308"/>
@@ -11028,9 +11362,9 @@
       <c r="E309"/>
       <c r="F309"/>
       <c r="G309"/>
-      <c r="H309" s="173"/>
+      <c r="H309" s="167"/>
       <c r="I309"/>
-      <c r="J309" s="45"/>
+      <c r="J309" s="44"/>
       <c r="K309"/>
       <c r="L309"/>
       <c r="M309"/>
@@ -11044,9 +11378,9 @@
       <c r="E310"/>
       <c r="F310"/>
       <c r="G310"/>
-      <c r="H310" s="173"/>
+      <c r="H310" s="167"/>
       <c r="I310"/>
-      <c r="J310" s="45"/>
+      <c r="J310" s="44"/>
       <c r="K310"/>
       <c r="L310"/>
       <c r="M310"/>
@@ -11060,9 +11394,9 @@
       <c r="E311"/>
       <c r="F311"/>
       <c r="G311"/>
-      <c r="H311" s="173"/>
+      <c r="H311" s="167"/>
       <c r="I311"/>
-      <c r="J311" s="45"/>
+      <c r="J311" s="44"/>
       <c r="K311"/>
       <c r="L311"/>
       <c r="M311"/>
@@ -11076,9 +11410,9 @@
       <c r="E312"/>
       <c r="F312"/>
       <c r="G312"/>
-      <c r="H312" s="173"/>
+      <c r="H312" s="167"/>
       <c r="I312"/>
-      <c r="J312" s="45"/>
+      <c r="J312" s="44"/>
       <c r="K312"/>
       <c r="L312"/>
       <c r="M312"/>
@@ -11092,9 +11426,9 @@
       <c r="E313"/>
       <c r="F313"/>
       <c r="G313"/>
-      <c r="H313" s="173"/>
+      <c r="H313" s="167"/>
       <c r="I313"/>
-      <c r="J313" s="45"/>
+      <c r="J313" s="44"/>
       <c r="K313"/>
       <c r="L313"/>
       <c r="M313"/>
@@ -11108,9 +11442,9 @@
       <c r="E314"/>
       <c r="F314"/>
       <c r="G314"/>
-      <c r="H314" s="173"/>
+      <c r="H314" s="167"/>
       <c r="I314"/>
-      <c r="J314" s="45"/>
+      <c r="J314" s="44"/>
       <c r="K314"/>
       <c r="L314"/>
       <c r="M314"/>
@@ -11124,9 +11458,9 @@
       <c r="E315"/>
       <c r="F315"/>
       <c r="G315"/>
-      <c r="H315" s="173"/>
+      <c r="H315" s="167"/>
       <c r="I315"/>
-      <c r="J315" s="45"/>
+      <c r="J315" s="44"/>
       <c r="K315"/>
       <c r="L315"/>
       <c r="M315"/>
@@ -11140,9 +11474,9 @@
       <c r="E316"/>
       <c r="F316"/>
       <c r="G316"/>
-      <c r="H316" s="173"/>
+      <c r="H316" s="167"/>
       <c r="I316"/>
-      <c r="J316" s="45"/>
+      <c r="J316" s="44"/>
       <c r="K316"/>
       <c r="L316"/>
       <c r="M316"/>
@@ -11156,9 +11490,9 @@
       <c r="E317"/>
       <c r="F317"/>
       <c r="G317"/>
-      <c r="H317" s="173"/>
+      <c r="H317" s="167"/>
       <c r="I317"/>
-      <c r="J317" s="45"/>
+      <c r="J317" s="44"/>
       <c r="K317"/>
       <c r="L317"/>
       <c r="M317"/>
@@ -11172,9 +11506,9 @@
       <c r="E318"/>
       <c r="F318"/>
       <c r="G318"/>
-      <c r="H318" s="173"/>
+      <c r="H318" s="167"/>
       <c r="I318"/>
-      <c r="J318" s="45"/>
+      <c r="J318" s="44"/>
       <c r="K318"/>
       <c r="L318"/>
       <c r="M318"/>
@@ -11188,9 +11522,9 @@
       <c r="E319"/>
       <c r="F319"/>
       <c r="G319"/>
-      <c r="H319" s="173"/>
+      <c r="H319" s="167"/>
       <c r="I319"/>
-      <c r="J319" s="45"/>
+      <c r="J319" s="44"/>
       <c r="K319"/>
       <c r="L319"/>
       <c r="M319"/>
@@ -11204,9 +11538,9 @@
       <c r="E320"/>
       <c r="F320"/>
       <c r="G320"/>
-      <c r="H320" s="173"/>
+      <c r="H320" s="167"/>
       <c r="I320"/>
-      <c r="J320" s="45"/>
+      <c r="J320" s="44"/>
       <c r="K320"/>
       <c r="L320"/>
       <c r="M320"/>
@@ -11220,9 +11554,9 @@
       <c r="E321"/>
       <c r="F321"/>
       <c r="G321"/>
-      <c r="H321" s="173"/>
+      <c r="H321" s="167"/>
       <c r="I321"/>
-      <c r="J321" s="45"/>
+      <c r="J321" s="44"/>
       <c r="K321"/>
       <c r="L321"/>
       <c r="M321"/>
@@ -11236,9 +11570,9 @@
       <c r="E322"/>
       <c r="F322"/>
       <c r="G322"/>
-      <c r="H322" s="173"/>
+      <c r="H322" s="167"/>
       <c r="I322"/>
-      <c r="J322" s="45"/>
+      <c r="J322" s="44"/>
       <c r="K322"/>
       <c r="L322"/>
       <c r="M322"/>
@@ -11252,9 +11586,9 @@
       <c r="E323"/>
       <c r="F323"/>
       <c r="G323"/>
-      <c r="H323" s="173"/>
+      <c r="H323" s="167"/>
       <c r="I323"/>
-      <c r="J323" s="45"/>
+      <c r="J323" s="44"/>
       <c r="K323"/>
       <c r="L323"/>
       <c r="M323"/>
@@ -11268,9 +11602,9 @@
       <c r="E324"/>
       <c r="F324"/>
       <c r="G324"/>
-      <c r="H324" s="173"/>
+      <c r="H324" s="167"/>
       <c r="I324"/>
-      <c r="J324" s="45"/>
+      <c r="J324" s="44"/>
       <c r="K324"/>
       <c r="L324"/>
       <c r="M324"/>
@@ -11284,9 +11618,9 @@
       <c r="E325"/>
       <c r="F325"/>
       <c r="G325"/>
-      <c r="H325" s="173"/>
+      <c r="H325" s="167"/>
       <c r="I325"/>
-      <c r="J325" s="45"/>
+      <c r="J325" s="44"/>
       <c r="K325"/>
       <c r="L325"/>
       <c r="M325"/>
@@ -11300,9 +11634,9 @@
       <c r="E326"/>
       <c r="F326"/>
       <c r="G326"/>
-      <c r="H326" s="173"/>
+      <c r="H326" s="167"/>
       <c r="I326"/>
-      <c r="J326" s="45"/>
+      <c r="J326" s="44"/>
       <c r="K326"/>
       <c r="L326"/>
       <c r="M326"/>
@@ -11316,9 +11650,9 @@
       <c r="E327"/>
       <c r="F327"/>
       <c r="G327"/>
-      <c r="H327" s="173"/>
+      <c r="H327" s="167"/>
       <c r="I327"/>
-      <c r="J327" s="45"/>
+      <c r="J327" s="44"/>
       <c r="K327"/>
       <c r="L327"/>
       <c r="M327"/>
@@ -11332,9 +11666,9 @@
       <c r="E328"/>
       <c r="F328"/>
       <c r="G328"/>
-      <c r="H328" s="173"/>
+      <c r="H328" s="167"/>
       <c r="I328"/>
-      <c r="J328" s="45"/>
+      <c r="J328" s="44"/>
       <c r="K328"/>
       <c r="L328"/>
       <c r="M328"/>
@@ -11348,9 +11682,9 @@
       <c r="E329"/>
       <c r="F329"/>
       <c r="G329"/>
-      <c r="H329" s="173"/>
+      <c r="H329" s="167"/>
       <c r="I329"/>
-      <c r="J329" s="45"/>
+      <c r="J329" s="44"/>
       <c r="K329"/>
       <c r="L329"/>
       <c r="M329"/>
@@ -11364,9 +11698,9 @@
       <c r="E330"/>
       <c r="F330"/>
       <c r="G330"/>
-      <c r="H330" s="173"/>
+      <c r="H330" s="167"/>
       <c r="I330"/>
-      <c r="J330" s="45"/>
+      <c r="J330" s="44"/>
       <c r="K330"/>
       <c r="L330"/>
       <c r="M330"/>
@@ -11380,9 +11714,9 @@
       <c r="E331"/>
       <c r="F331"/>
       <c r="G331"/>
-      <c r="H331" s="173"/>
+      <c r="H331" s="167"/>
       <c r="I331"/>
-      <c r="J331" s="45"/>
+      <c r="J331" s="44"/>
       <c r="K331"/>
       <c r="L331"/>
       <c r="M331"/>
@@ -11396,9 +11730,9 @@
       <c r="E332"/>
       <c r="F332"/>
       <c r="G332"/>
-      <c r="H332" s="173"/>
+      <c r="H332" s="167"/>
       <c r="I332"/>
-      <c r="J332" s="45"/>
+      <c r="J332" s="44"/>
       <c r="K332"/>
       <c r="L332"/>
       <c r="M332"/>
@@ -11412,9 +11746,9 @@
       <c r="E333"/>
       <c r="F333"/>
       <c r="G333"/>
-      <c r="H333" s="173"/>
+      <c r="H333" s="167"/>
       <c r="I333"/>
-      <c r="J333" s="45"/>
+      <c r="J333" s="44"/>
       <c r="K333"/>
       <c r="L333"/>
       <c r="M333"/>
@@ -11428,9 +11762,9 @@
       <c r="E334"/>
       <c r="F334"/>
       <c r="G334"/>
-      <c r="H334" s="173"/>
+      <c r="H334" s="167"/>
       <c r="I334"/>
-      <c r="J334" s="45"/>
+      <c r="J334" s="44"/>
       <c r="K334"/>
       <c r="L334"/>
       <c r="M334"/>
@@ -11444,9 +11778,9 @@
       <c r="E335"/>
       <c r="F335"/>
       <c r="G335"/>
-      <c r="H335" s="173"/>
+      <c r="H335" s="167"/>
       <c r="I335"/>
-      <c r="J335" s="45"/>
+      <c r="J335" s="44"/>
       <c r="K335"/>
       <c r="L335"/>
       <c r="M335"/>
@@ -11460,9 +11794,9 @@
       <c r="E336"/>
       <c r="F336"/>
       <c r="G336"/>
-      <c r="H336" s="173"/>
+      <c r="H336" s="167"/>
       <c r="I336"/>
-      <c r="J336" s="45"/>
+      <c r="J336" s="44"/>
       <c r="K336"/>
       <c r="L336"/>
       <c r="M336"/>
@@ -11476,9 +11810,9 @@
       <c r="E337"/>
       <c r="F337"/>
       <c r="G337"/>
-      <c r="H337" s="173"/>
+      <c r="H337" s="167"/>
       <c r="I337"/>
-      <c r="J337" s="45"/>
+      <c r="J337" s="44"/>
       <c r="K337"/>
       <c r="L337"/>
       <c r="M337"/>
@@ -11492,9 +11826,9 @@
       <c r="E338"/>
       <c r="F338"/>
       <c r="G338"/>
-      <c r="H338" s="173"/>
+      <c r="H338" s="167"/>
       <c r="I338"/>
-      <c r="J338" s="45"/>
+      <c r="J338" s="44"/>
       <c r="K338"/>
       <c r="L338"/>
       <c r="M338"/>
@@ -11508,9 +11842,9 @@
       <c r="E339"/>
       <c r="F339"/>
       <c r="G339"/>
-      <c r="H339" s="173"/>
+      <c r="H339" s="167"/>
       <c r="I339"/>
-      <c r="J339" s="45"/>
+      <c r="J339" s="44"/>
       <c r="K339"/>
       <c r="L339"/>
       <c r="M339"/>
@@ -11524,9 +11858,9 @@
       <c r="E340"/>
       <c r="F340"/>
       <c r="G340"/>
-      <c r="H340" s="173"/>
+      <c r="H340" s="167"/>
       <c r="I340"/>
-      <c r="J340" s="45"/>
+      <c r="J340" s="44"/>
       <c r="K340"/>
       <c r="L340"/>
       <c r="M340"/>
@@ -11540,9 +11874,9 @@
       <c r="E341"/>
       <c r="F341"/>
       <c r="G341"/>
-      <c r="H341" s="173"/>
+      <c r="H341" s="167"/>
       <c r="I341"/>
-      <c r="J341" s="45"/>
+      <c r="J341" s="44"/>
       <c r="K341"/>
       <c r="L341"/>
       <c r="M341"/>
@@ -11556,9 +11890,9 @@
       <c r="E342"/>
       <c r="F342"/>
       <c r="G342"/>
-      <c r="H342" s="173"/>
+      <c r="H342" s="167"/>
       <c r="I342"/>
-      <c r="J342" s="45"/>
+      <c r="J342" s="44"/>
       <c r="K342"/>
       <c r="L342"/>
       <c r="M342"/>
@@ -11572,9 +11906,9 @@
       <c r="E343"/>
       <c r="F343"/>
       <c r="G343"/>
-      <c r="H343" s="173"/>
+      <c r="H343" s="167"/>
       <c r="I343"/>
-      <c r="J343" s="45"/>
+      <c r="J343" s="44"/>
       <c r="K343"/>
       <c r="L343"/>
       <c r="M343"/>
@@ -11588,9 +11922,9 @@
       <c r="E344"/>
       <c r="F344"/>
       <c r="G344"/>
-      <c r="H344" s="173"/>
+      <c r="H344" s="167"/>
       <c r="I344"/>
-      <c r="J344" s="45"/>
+      <c r="J344" s="44"/>
       <c r="K344"/>
       <c r="L344"/>
       <c r="M344"/>
@@ -11604,9 +11938,9 @@
       <c r="E345"/>
       <c r="F345"/>
       <c r="G345"/>
-      <c r="H345" s="173"/>
+      <c r="H345" s="167"/>
       <c r="I345"/>
-      <c r="J345" s="45"/>
+      <c r="J345" s="44"/>
       <c r="K345"/>
       <c r="L345"/>
       <c r="M345"/>
@@ -11620,9 +11954,9 @@
       <c r="E346"/>
       <c r="F346"/>
       <c r="G346"/>
-      <c r="H346" s="173"/>
+      <c r="H346" s="167"/>
       <c r="I346"/>
-      <c r="J346" s="45"/>
+      <c r="J346" s="44"/>
       <c r="K346"/>
       <c r="L346"/>
       <c r="M346"/>
@@ -11636,9 +11970,9 @@
       <c r="E347"/>
       <c r="F347"/>
       <c r="G347"/>
-      <c r="H347" s="173"/>
+      <c r="H347" s="167"/>
       <c r="I347"/>
-      <c r="J347" s="45"/>
+      <c r="J347" s="44"/>
       <c r="K347"/>
       <c r="L347"/>
       <c r="M347"/>
@@ -11652,9 +11986,9 @@
       <c r="E348"/>
       <c r="F348"/>
       <c r="G348"/>
-      <c r="H348" s="173"/>
+      <c r="H348" s="167"/>
       <c r="I348"/>
-      <c r="J348" s="45"/>
+      <c r="J348" s="44"/>
       <c r="K348"/>
       <c r="L348"/>
       <c r="M348"/>
@@ -11668,9 +12002,9 @@
       <c r="E349"/>
       <c r="F349"/>
       <c r="G349"/>
-      <c r="H349" s="173"/>
+      <c r="H349" s="167"/>
       <c r="I349"/>
-      <c r="J349" s="45"/>
+      <c r="J349" s="44"/>
       <c r="K349"/>
       <c r="L349"/>
       <c r="M349"/>
@@ -11684,9 +12018,9 @@
       <c r="E350"/>
       <c r="F350"/>
       <c r="G350"/>
-      <c r="H350" s="173"/>
+      <c r="H350" s="167"/>
       <c r="I350"/>
-      <c r="J350" s="45"/>
+      <c r="J350" s="44"/>
       <c r="K350"/>
       <c r="L350"/>
       <c r="M350"/>
@@ -11700,9 +12034,9 @@
       <c r="E351"/>
       <c r="F351"/>
       <c r="G351"/>
-      <c r="H351" s="173"/>
+      <c r="H351" s="167"/>
       <c r="I351"/>
-      <c r="J351" s="45"/>
+      <c r="J351" s="44"/>
       <c r="K351"/>
       <c r="L351"/>
       <c r="M351"/>
@@ -11716,9 +12050,9 @@
       <c r="E352"/>
       <c r="F352"/>
       <c r="G352"/>
-      <c r="H352" s="173"/>
+      <c r="H352" s="167"/>
       <c r="I352"/>
-      <c r="J352" s="45"/>
+      <c r="J352" s="44"/>
       <c r="K352"/>
       <c r="L352"/>
       <c r="M352"/>
@@ -11732,9 +12066,9 @@
       <c r="E353"/>
       <c r="F353"/>
       <c r="G353"/>
-      <c r="H353" s="173"/>
+      <c r="H353" s="167"/>
       <c r="I353"/>
-      <c r="J353" s="45"/>
+      <c r="J353" s="44"/>
       <c r="K353"/>
       <c r="L353"/>
       <c r="M353"/>
@@ -11748,9 +12082,9 @@
       <c r="E354"/>
       <c r="F354"/>
       <c r="G354"/>
-      <c r="H354" s="173"/>
+      <c r="H354" s="167"/>
       <c r="I354"/>
-      <c r="J354" s="45"/>
+      <c r="J354" s="44"/>
       <c r="K354"/>
       <c r="L354"/>
       <c r="M354"/>
@@ -11764,9 +12098,9 @@
       <c r="E355"/>
       <c r="F355"/>
       <c r="G355"/>
-      <c r="H355" s="173"/>
+      <c r="H355" s="167"/>
       <c r="I355"/>
-      <c r="J355" s="45"/>
+      <c r="J355" s="44"/>
       <c r="K355"/>
       <c r="L355"/>
       <c r="M355"/>
@@ -11780,9 +12114,9 @@
       <c r="E356"/>
       <c r="F356"/>
       <c r="G356"/>
-      <c r="H356" s="173"/>
+      <c r="H356" s="167"/>
       <c r="I356"/>
-      <c r="J356" s="45"/>
+      <c r="J356" s="44"/>
       <c r="K356"/>
       <c r="L356"/>
       <c r="M356"/>
@@ -11796,9 +12130,9 @@
       <c r="E357"/>
       <c r="F357"/>
       <c r="G357"/>
-      <c r="H357" s="173"/>
+      <c r="H357" s="167"/>
       <c r="I357"/>
-      <c r="J357" s="45"/>
+      <c r="J357" s="44"/>
       <c r="K357"/>
       <c r="L357"/>
       <c r="M357"/>
@@ -11812,9 +12146,9 @@
       <c r="E358"/>
       <c r="F358"/>
       <c r="G358"/>
-      <c r="H358" s="173"/>
+      <c r="H358" s="167"/>
       <c r="I358"/>
-      <c r="J358" s="45"/>
+      <c r="J358" s="44"/>
       <c r="K358"/>
       <c r="L358"/>
       <c r="M358"/>
@@ -11828,9 +12162,9 @@
       <c r="E359"/>
       <c r="F359"/>
       <c r="G359"/>
-      <c r="H359" s="173"/>
+      <c r="H359" s="167"/>
       <c r="I359"/>
-      <c r="J359" s="45"/>
+      <c r="J359" s="44"/>
       <c r="K359"/>
       <c r="L359"/>
       <c r="M359"/>
@@ -11844,9 +12178,9 @@
       <c r="E360"/>
       <c r="F360"/>
       <c r="G360"/>
-      <c r="H360" s="173"/>
+      <c r="H360" s="167"/>
       <c r="I360"/>
-      <c r="J360" s="45"/>
+      <c r="J360" s="44"/>
       <c r="K360"/>
       <c r="L360"/>
       <c r="M360"/>
@@ -11860,9 +12194,9 @@
       <c r="E361"/>
       <c r="F361"/>
       <c r="G361"/>
-      <c r="H361" s="173"/>
+      <c r="H361" s="167"/>
       <c r="I361"/>
-      <c r="J361" s="45"/>
+      <c r="J361" s="44"/>
       <c r="K361"/>
       <c r="L361"/>
       <c r="M361"/>
@@ -11876,9 +12210,9 @@
       <c r="E362"/>
       <c r="F362"/>
       <c r="G362"/>
-      <c r="H362" s="173"/>
+      <c r="H362" s="167"/>
       <c r="I362"/>
-      <c r="J362" s="45"/>
+      <c r="J362" s="44"/>
       <c r="K362"/>
       <c r="L362"/>
       <c r="M362"/>
@@ -11892,9 +12226,9 @@
       <c r="E363"/>
       <c r="F363"/>
       <c r="G363"/>
-      <c r="H363" s="173"/>
+      <c r="H363" s="167"/>
       <c r="I363"/>
-      <c r="J363" s="45"/>
+      <c r="J363" s="44"/>
       <c r="K363"/>
       <c r="L363"/>
       <c r="M363"/>
@@ -11908,9 +12242,9 @@
       <c r="E364"/>
       <c r="F364"/>
       <c r="G364"/>
-      <c r="H364" s="173"/>
+      <c r="H364" s="167"/>
       <c r="I364"/>
-      <c r="J364" s="45"/>
+      <c r="J364" s="44"/>
       <c r="K364"/>
       <c r="L364"/>
       <c r="M364"/>
@@ -11924,9 +12258,9 @@
       <c r="E365"/>
       <c r="F365"/>
       <c r="G365"/>
-      <c r="H365" s="173"/>
+      <c r="H365" s="167"/>
       <c r="I365"/>
-      <c r="J365" s="45"/>
+      <c r="J365" s="44"/>
       <c r="K365"/>
       <c r="L365"/>
       <c r="M365"/>
@@ -11940,9 +12274,9 @@
       <c r="E366"/>
       <c r="F366"/>
       <c r="G366"/>
-      <c r="H366" s="173"/>
+      <c r="H366" s="167"/>
       <c r="I366"/>
-      <c r="J366" s="45"/>
+      <c r="J366" s="44"/>
       <c r="K366"/>
       <c r="L366"/>
       <c r="M366"/>
@@ -11956,9 +12290,9 @@
       <c r="E367"/>
       <c r="F367"/>
       <c r="G367"/>
-      <c r="H367" s="173"/>
+      <c r="H367" s="167"/>
       <c r="I367"/>
-      <c r="J367" s="45"/>
+      <c r="J367" s="44"/>
       <c r="K367"/>
       <c r="L367"/>
       <c r="M367"/>
@@ -11972,9 +12306,9 @@
       <c r="E368"/>
       <c r="F368"/>
       <c r="G368"/>
-      <c r="H368" s="173"/>
+      <c r="H368" s="167"/>
       <c r="I368"/>
-      <c r="J368" s="45"/>
+      <c r="J368" s="44"/>
       <c r="K368"/>
       <c r="L368"/>
       <c r="M368"/>
@@ -11988,13 +12322,109 @@
       <c r="E369"/>
       <c r="F369"/>
       <c r="G369"/>
-      <c r="H369" s="173"/>
+      <c r="H369" s="167"/>
       <c r="I369"/>
-      <c r="J369" s="45"/>
+      <c r="J369" s="44"/>
       <c r="K369"/>
       <c r="L369"/>
       <c r="M369"/>
       <c r="N369"/>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A370"/>
+      <c r="B370"/>
+      <c r="C370"/>
+      <c r="D370"/>
+      <c r="E370"/>
+      <c r="F370"/>
+      <c r="G370"/>
+      <c r="H370" s="167"/>
+      <c r="I370"/>
+      <c r="J370" s="44"/>
+      <c r="K370"/>
+      <c r="L370"/>
+      <c r="M370"/>
+      <c r="N370"/>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A371"/>
+      <c r="B371"/>
+      <c r="C371"/>
+      <c r="D371"/>
+      <c r="E371"/>
+      <c r="F371"/>
+      <c r="G371"/>
+      <c r="H371" s="167"/>
+      <c r="I371"/>
+      <c r="J371" s="44"/>
+      <c r="K371"/>
+      <c r="L371"/>
+      <c r="M371"/>
+      <c r="N371"/>
+    </row>
+    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A372"/>
+      <c r="B372"/>
+      <c r="C372"/>
+      <c r="D372"/>
+      <c r="E372"/>
+      <c r="F372"/>
+      <c r="G372"/>
+      <c r="H372" s="167"/>
+      <c r="I372"/>
+      <c r="J372" s="44"/>
+      <c r="K372"/>
+      <c r="L372"/>
+      <c r="M372"/>
+      <c r="N372"/>
+    </row>
+    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A373"/>
+      <c r="B373"/>
+      <c r="C373"/>
+      <c r="D373"/>
+      <c r="E373"/>
+      <c r="F373"/>
+      <c r="G373"/>
+      <c r="H373" s="167"/>
+      <c r="I373"/>
+      <c r="J373" s="44"/>
+      <c r="K373"/>
+      <c r="L373"/>
+      <c r="M373"/>
+      <c r="N373"/>
+    </row>
+    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A374"/>
+      <c r="B374"/>
+      <c r="C374"/>
+      <c r="D374"/>
+      <c r="E374"/>
+      <c r="F374"/>
+      <c r="G374"/>
+      <c r="H374" s="167"/>
+      <c r="I374"/>
+      <c r="J374" s="44"/>
+      <c r="K374"/>
+      <c r="L374"/>
+      <c r="M374"/>
+      <c r="N374"/>
+    </row>
+    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A375"/>
+      <c r="B375"/>
+      <c r="C375"/>
+      <c r="D375"/>
+      <c r="E375"/>
+      <c r="F375"/>
+      <c r="G375"/>
+      <c r="H375" s="167"/>
+      <c r="I375"/>
+      <c r="J375" s="44"/>
+      <c r="K375"/>
+      <c r="L375"/>
+      <c r="M375"/>
+      <c r="N375"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -12074,13 +12504,17 @@
     <hyperlink ref="G78" r:id="rId73" xr:uid="{1D1C47D0-BC9D-4736-BAC0-A2036F92EB15}"/>
     <hyperlink ref="G80" r:id="rId74" display="mailto:adamgoldenbergkft@gmail.com" xr:uid="{EC282377-1B8F-4EFC-B956-3A848548A480}"/>
     <hyperlink ref="C81" r:id="rId75" display="mailto:sukizsuzsa@gmail.com" xr:uid="{C279F46B-0099-4784-8302-DD3112347FFA}"/>
-    <hyperlink ref="G81" r:id="rId76" display="mailto:sukizsuzsa@gmail.com" xr:uid="{5CE69C38-ED09-4295-8312-8504B50C69E5}"/>
+    <hyperlink ref="G81" r:id="rId76" xr:uid="{5CE69C38-ED09-4295-8312-8504B50C69E5}"/>
+    <hyperlink ref="C76" r:id="rId77" display="mailto:baumhakl@gmail.com" xr:uid="{273BF3E5-9A04-4B63-90D3-71F1088B6331}"/>
+    <hyperlink ref="G76" r:id="rId78" xr:uid="{6F7DA6ED-BAE2-4184-9913-BA3498F4C94E}"/>
+    <hyperlink ref="G83" r:id="rId79" xr:uid="{CBA03C9C-0213-4F5E-A76E-128127645C3F}"/>
+    <hyperlink ref="G85" r:id="rId80" xr:uid="{0FB0671A-AB04-40A2-91E1-2A93563D53B5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" r:id="rId77"/>
-  <legacyDrawing r:id="rId78"/>
+  <pageSetup paperSize="9" scale="76" fitToHeight="0" orientation="landscape" r:id="rId81"/>
+  <legacyDrawing r:id="rId82"/>
   <tableParts count="1">
-    <tablePart r:id="rId79"/>
+    <tablePart r:id="rId83"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12157,10 +12591,10 @@
       <c r="R1" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="S1" s="54" t="s">
+      <c r="S1" s="53" t="s">
         <v>260</v>
       </c>
-      <c r="T1" s="42" t="s">
+      <c r="T1" s="41" t="s">
         <v>199</v>
       </c>
       <c r="U1" s="13" t="s">
@@ -12168,53 +12602,53 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="98">
+      <c r="A2" s="97">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>293</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="149" t="s">
+      <c r="G2" s="148" t="s">
+        <v>305</v>
+      </c>
+      <c r="H2" s="149" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="150" t="s">
+        <v>303</v>
+      </c>
+      <c r="J2" s="147"/>
+      <c r="K2" s="146" t="s">
         <v>306</v>
       </c>
-      <c r="H2" s="150" t="s">
-        <v>296</v>
-      </c>
-      <c r="I2" s="151" t="s">
-        <v>304</v>
-      </c>
-      <c r="J2" s="148"/>
-      <c r="K2" s="147" t="s">
-        <v>307</v>
-      </c>
-      <c r="L2" s="147"/>
-      <c r="M2" s="147"/>
-      <c r="N2" s="147"/>
-      <c r="O2" s="147" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" s="147" t="s">
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" s="146" t="s">
         <v>8</v>
       </c>
       <c r="Q2" s="1"/>
       <c r="R2" s="1"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="100"/>
-      <c r="U2" s="101"/>
+      <c r="S2" s="98"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="100"/>
     </row>
     <row r="3" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="98">
+      <c r="A3" s="97">
         <v>2</v>
       </c>
-      <c r="B3" s="102" t="s">
+      <c r="B3" s="101" t="s">
         <v>294</v>
       </c>
       <c r="C3" s="1"/>
@@ -12233,12 +12667,12 @@
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
-      <c r="S3" s="99"/>
-      <c r="T3" s="103"/>
-      <c r="U3" s="101"/>
+      <c r="S3" s="98"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="100"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="98">
+      <c r="A4" s="97">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -12250,9 +12684,15 @@
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="1"/>
+      <c r="G4" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>364</v>
+      </c>
       <c r="J4" s="21"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -12262,17 +12702,21 @@
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="103"/>
-      <c r="U4" s="101"/>
+      <c r="S4" s="98"/>
+      <c r="T4" s="102"/>
+      <c r="U4" s="100"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="98">
+      <c r="A5" s="97">
         <v>4</v>
       </c>
-      <c r="B5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>351</v>
+      </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -12287,20 +12731,26 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
-      <c r="S5" s="99"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="101"/>
+      <c r="S5" s="98"/>
+      <c r="T5" s="102"/>
+      <c r="U5" s="100"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="98">
+      <c r="A6" s="97">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>377</v>
+      </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1" t="s">
+        <v>378</v>
+      </c>
       <c r="H6" s="16"/>
       <c r="I6" s="1"/>
       <c r="J6" s="21"/>
@@ -12312,12 +12762,12 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="99"/>
-      <c r="T6" s="104"/>
-      <c r="U6" s="101"/>
+      <c r="S6" s="98"/>
+      <c r="T6" s="103"/>
+      <c r="U6" s="100"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="98">
+      <c r="A7" s="97">
         <v>6</v>
       </c>
       <c r="B7" s="1"/>
@@ -12337,12 +12787,12 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="100"/>
-      <c r="U7" s="101"/>
+      <c r="S7" s="98"/>
+      <c r="T7" s="99"/>
+      <c r="U7" s="100"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="98">
+      <c r="A8" s="97">
         <v>7</v>
       </c>
       <c r="B8" s="1"/>
@@ -12352,7 +12802,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="16"/>
-      <c r="I8" s="38"/>
+      <c r="I8" s="37"/>
       <c r="J8" s="21"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -12362,12 +12812,12 @@
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
-      <c r="S8" s="99"/>
-      <c r="T8" s="103"/>
-      <c r="U8" s="101"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="102"/>
+      <c r="U8" s="100"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="98">
+      <c r="A9" s="97">
         <v>8</v>
       </c>
       <c r="B9" s="1"/>
@@ -12387,12 +12837,12 @@
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
-      <c r="S9" s="99"/>
-      <c r="T9" s="103"/>
-      <c r="U9" s="101"/>
+      <c r="S9" s="98"/>
+      <c r="T9" s="102"/>
+      <c r="U9" s="100"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="98">
+      <c r="A10" s="97">
         <v>9</v>
       </c>
       <c r="B10" s="1"/>
@@ -12412,16 +12862,16 @@
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
-      <c r="S10" s="105"/>
+      <c r="S10" s="104"/>
       <c r="T10" s="21"/>
-      <c r="U10" s="101"/>
+      <c r="U10" s="100"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="52">
+      <c r="A11" s="51">
         <v>10</v>
       </c>
       <c r="B11" s="8"/>
-      <c r="C11" s="106"/>
+      <c r="C11" s="105"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
       <c r="F11" s="8"/>
@@ -12437,12 +12887,12 @@
       <c r="P11" s="8"/>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="53"/>
-      <c r="U11" s="107"/>
+      <c r="S11" s="104"/>
+      <c r="T11" s="52"/>
+      <c r="U11" s="106"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="52">
+      <c r="A12" s="51">
         <v>11</v>
       </c>
       <c r="B12" s="8"/>
@@ -12462,12 +12912,12 @@
       <c r="P12" s="8"/>
       <c r="Q12" s="8"/>
       <c r="R12" s="8"/>
-      <c r="S12" s="64"/>
-      <c r="T12" s="53"/>
-      <c r="U12" s="107"/>
+      <c r="S12" s="63"/>
+      <c r="T12" s="52"/>
+      <c r="U12" s="106"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="52">
+      <c r="A13" s="51">
         <v>12</v>
       </c>
       <c r="B13" s="8"/>
@@ -12487,12 +12937,12 @@
       <c r="P13" s="8"/>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
-      <c r="S13" s="64"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="107"/>
+      <c r="S13" s="63"/>
+      <c r="T13" s="52"/>
+      <c r="U13" s="106"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="98">
+      <c r="A14" s="97">
         <v>13</v>
       </c>
       <c r="B14" s="1"/>
@@ -12512,12 +12962,12 @@
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
-      <c r="S14" s="99"/>
-      <c r="T14" s="103"/>
-      <c r="U14" s="101"/>
+      <c r="S14" s="98"/>
+      <c r="T14" s="102"/>
+      <c r="U14" s="100"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="98">
+      <c r="A15" s="97">
         <v>14</v>
       </c>
       <c r="B15" s="8"/>
@@ -12525,7 +12975,7 @@
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
-      <c r="G15" s="108"/>
+      <c r="G15" s="107"/>
       <c r="H15" s="17"/>
       <c r="I15" s="8"/>
       <c r="J15" s="22"/>
@@ -12536,13 +12986,13 @@
       <c r="O15" s="1"/>
       <c r="P15" s="8"/>
       <c r="Q15" s="8"/>
-      <c r="R15" s="109"/>
-      <c r="S15" s="110"/>
-      <c r="T15" s="53"/>
-      <c r="U15" s="107"/>
+      <c r="R15" s="108"/>
+      <c r="S15" s="109"/>
+      <c r="T15" s="52"/>
+      <c r="U15" s="106"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="98">
+      <c r="A16" s="97">
         <v>15</v>
       </c>
       <c r="B16" s="8"/>
@@ -12562,20 +13012,20 @@
       <c r="P16" s="8"/>
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
-      <c r="S16" s="64"/>
-      <c r="T16" s="53"/>
-      <c r="U16" s="107"/>
+      <c r="S16" s="63"/>
+      <c r="T16" s="52"/>
+      <c r="U16" s="106"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="98">
+      <c r="A17" s="97">
         <v>16</v>
       </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
-      <c r="F17" s="109"/>
-      <c r="G17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="107"/>
       <c r="H17" s="17"/>
       <c r="I17" s="8"/>
       <c r="J17" s="22"/>
@@ -12587,12 +13037,12 @@
       <c r="P17" s="8"/>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
-      <c r="S17" s="111"/>
-      <c r="T17" s="53"/>
-      <c r="U17" s="107"/>
+      <c r="S17" s="110"/>
+      <c r="T17" s="52"/>
+      <c r="U17" s="106"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="98">
+      <c r="A18" s="97">
         <v>17</v>
       </c>
       <c r="B18" s="8"/>
@@ -12600,7 +13050,7 @@
       <c r="D18" s="8"/>
       <c r="E18" s="8"/>
       <c r="F18" s="8"/>
-      <c r="G18" s="112"/>
+      <c r="G18" s="111"/>
       <c r="H18" s="17"/>
       <c r="I18" s="8"/>
       <c r="J18" s="22"/>
@@ -12612,20 +13062,20 @@
       <c r="P18" s="8"/>
       <c r="Q18" s="8"/>
       <c r="R18" s="8"/>
-      <c r="S18" s="64"/>
-      <c r="T18" s="53"/>
-      <c r="U18" s="107"/>
+      <c r="S18" s="63"/>
+      <c r="T18" s="52"/>
+      <c r="U18" s="106"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="98">
+      <c r="A19" s="97">
         <v>18</v>
       </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
-      <c r="F19" s="109"/>
-      <c r="G19" s="108"/>
+      <c r="F19" s="108"/>
+      <c r="G19" s="107"/>
       <c r="H19" s="17"/>
       <c r="I19" s="8"/>
       <c r="J19" s="22"/>
@@ -12637,12 +13087,12 @@
       <c r="P19" s="8"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
-      <c r="S19" s="64"/>
-      <c r="T19" s="53"/>
-      <c r="U19" s="107"/>
+      <c r="S19" s="63"/>
+      <c r="T19" s="52"/>
+      <c r="U19" s="106"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="98">
+      <c r="A20" s="97">
         <v>19</v>
       </c>
       <c r="B20" s="8"/>
@@ -12650,7 +13100,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="108"/>
+      <c r="G20" s="107"/>
       <c r="H20" s="17"/>
       <c r="I20" s="8"/>
       <c r="J20" s="22"/>
@@ -12662,20 +13112,20 @@
       <c r="P20" s="8"/>
       <c r="Q20" s="8"/>
       <c r="R20" s="8"/>
-      <c r="S20" s="64"/>
-      <c r="T20" s="53"/>
-      <c r="U20" s="107"/>
+      <c r="S20" s="63"/>
+      <c r="T20" s="52"/>
+      <c r="U20" s="106"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="52">
+      <c r="A21" s="51">
         <v>20</v>
       </c>
       <c r="B21" s="8"/>
-      <c r="C21" s="113"/>
+      <c r="C21" s="112"/>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
-      <c r="F21" s="109"/>
-      <c r="G21" s="113"/>
+      <c r="F21" s="108"/>
+      <c r="G21" s="112"/>
       <c r="H21" s="17"/>
       <c r="I21" s="8"/>
       <c r="J21" s="22"/>
@@ -12687,20 +13137,20 @@
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
-      <c r="S21" s="64"/>
-      <c r="T21" s="53"/>
-      <c r="U21" s="107"/>
+      <c r="S21" s="63"/>
+      <c r="T21" s="52"/>
+      <c r="U21" s="106"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="52">
+      <c r="A22" s="51">
         <v>21</v>
       </c>
       <c r="B22" s="8"/>
-      <c r="C22" s="112"/>
+      <c r="C22" s="111"/>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
-      <c r="F22" s="109"/>
-      <c r="G22" s="108"/>
+      <c r="F22" s="108"/>
+      <c r="G22" s="107"/>
       <c r="H22" s="17"/>
       <c r="I22" s="8"/>
       <c r="J22" s="22"/>
@@ -12712,12 +13162,12 @@
       <c r="P22" s="8"/>
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
-      <c r="S22" s="64"/>
-      <c r="T22" s="53"/>
-      <c r="U22" s="107"/>
+      <c r="S22" s="63"/>
+      <c r="T22" s="52"/>
+      <c r="U22" s="106"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="52">
+      <c r="A23" s="51">
         <v>22</v>
       </c>
       <c r="B23" s="8"/>
@@ -12737,20 +13187,20 @@
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
-      <c r="S23" s="64"/>
-      <c r="T23" s="53"/>
-      <c r="U23" s="107"/>
+      <c r="S23" s="63"/>
+      <c r="T23" s="52"/>
+      <c r="U23" s="106"/>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="52">
+      <c r="A24" s="51">
         <v>23</v>
       </c>
       <c r="B24" s="8"/>
-      <c r="C24" s="112"/>
+      <c r="C24" s="111"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="108"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="107"/>
       <c r="H24" s="17"/>
       <c r="I24" s="8"/>
       <c r="J24" s="22"/>
@@ -12762,19 +13212,19 @@
       <c r="P24" s="8"/>
       <c r="Q24" s="8"/>
       <c r="R24" s="8"/>
-      <c r="S24" s="64"/>
-      <c r="T24" s="53"/>
-      <c r="U24" s="107"/>
+      <c r="S24" s="63"/>
+      <c r="T24" s="52"/>
+      <c r="U24" s="106"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="52">
+      <c r="A25" s="51">
         <v>24</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
-      <c r="F25" s="109"/>
+      <c r="F25" s="108"/>
       <c r="G25" s="8"/>
       <c r="H25" s="17"/>
       <c r="I25" s="8"/>
@@ -12787,12 +13237,12 @@
       <c r="P25" s="8"/>
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
-      <c r="S25" s="64"/>
-      <c r="T25" s="53"/>
-      <c r="U25" s="107"/>
+      <c r="S25" s="63"/>
+      <c r="T25" s="52"/>
+      <c r="U25" s="106"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="52">
+      <c r="A26" s="51">
         <v>25</v>
       </c>
       <c r="B26" s="8"/>
@@ -12800,7 +13250,7 @@
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="108"/>
+      <c r="G26" s="107"/>
       <c r="H26" s="17"/>
       <c r="I26" s="8"/>
       <c r="J26" s="22"/>
@@ -12812,22 +13262,22 @@
       <c r="P26" s="8"/>
       <c r="Q26" s="8"/>
       <c r="R26" s="8"/>
-      <c r="S26" s="64"/>
-      <c r="T26" s="53"/>
-      <c r="U26" s="107"/>
+      <c r="S26" s="63"/>
+      <c r="T26" s="52"/>
+      <c r="U26" s="106"/>
     </row>
     <row r="27" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="52">
+      <c r="A27" s="51">
         <v>27</v>
       </c>
       <c r="B27" s="8"/>
-      <c r="C27" s="114"/>
+      <c r="C27" s="113"/>
       <c r="D27" s="8"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
-      <c r="G27" s="113"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
+      <c r="G27" s="112"/>
+      <c r="H27" s="114"/>
+      <c r="I27" s="114"/>
       <c r="J27" s="21"/>
       <c r="K27" s="1"/>
       <c r="L27" s="8"/>
@@ -12837,12 +13287,12 @@
       <c r="P27" s="8"/>
       <c r="Q27" s="8"/>
       <c r="R27" s="8"/>
-      <c r="S27" s="64"/>
-      <c r="T27" s="53"/>
-      <c r="U27" s="107"/>
+      <c r="S27" s="63"/>
+      <c r="T27" s="52"/>
+      <c r="U27" s="106"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="52">
+      <c r="A28" s="51">
         <v>28</v>
       </c>
       <c r="B28" s="8"/>
@@ -12850,7 +13300,7 @@
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="108"/>
+      <c r="G28" s="107"/>
       <c r="H28" s="17"/>
       <c r="I28" s="8"/>
       <c r="J28" s="22"/>
@@ -12862,12 +13312,12 @@
       <c r="P28" s="8"/>
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
-      <c r="S28" s="64"/>
-      <c r="T28" s="53"/>
-      <c r="U28" s="107"/>
+      <c r="S28" s="63"/>
+      <c r="T28" s="52"/>
+      <c r="U28" s="106"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="52">
+      <c r="A29" s="51">
         <v>29</v>
       </c>
       <c r="B29" s="8"/>
@@ -12875,10 +13325,10 @@
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
-      <c r="G29" s="108"/>
+      <c r="G29" s="107"/>
       <c r="H29" s="17"/>
       <c r="I29" s="8"/>
-      <c r="J29" s="108"/>
+      <c r="J29" s="107"/>
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
       <c r="M29" s="8"/>
@@ -12886,21 +13336,21 @@
       <c r="O29" s="8"/>
       <c r="P29" s="8"/>
       <c r="Q29" s="8"/>
-      <c r="R29" s="109"/>
-      <c r="S29" s="110"/>
-      <c r="T29" s="53"/>
-      <c r="U29" s="107"/>
+      <c r="R29" s="108"/>
+      <c r="S29" s="109"/>
+      <c r="T29" s="52"/>
+      <c r="U29" s="106"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="52">
+      <c r="A30" s="51">
         <v>30</v>
       </c>
       <c r="B30" s="8"/>
-      <c r="C30" s="108"/>
+      <c r="C30" s="107"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
-      <c r="G30" s="108"/>
+      <c r="G30" s="107"/>
       <c r="H30" s="17"/>
       <c r="I30" s="8"/>
       <c r="J30" s="22"/>
@@ -12912,22 +13362,22 @@
       <c r="P30" s="8"/>
       <c r="Q30" s="8"/>
       <c r="R30" s="8"/>
-      <c r="S30" s="64"/>
-      <c r="T30" s="53"/>
-      <c r="U30" s="107"/>
+      <c r="S30" s="63"/>
+      <c r="T30" s="52"/>
+      <c r="U30" s="106"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="52">
+      <c r="A31" s="51">
         <v>31</v>
       </c>
       <c r="B31" s="8"/>
-      <c r="C31" s="108"/>
+      <c r="C31" s="107"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
-      <c r="G31" s="108"/>
-      <c r="H31" s="37"/>
-      <c r="I31" s="38"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="37"/>
       <c r="J31" s="22"/>
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
@@ -12937,22 +13387,22 @@
       <c r="P31" s="8"/>
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
-      <c r="S31" s="64"/>
-      <c r="T31" s="53"/>
-      <c r="U31" s="107"/>
+      <c r="S31" s="63"/>
+      <c r="T31" s="52"/>
+      <c r="U31" s="106"/>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="52">
+      <c r="A32" s="51">
         <v>32</v>
       </c>
       <c r="B32" s="8"/>
-      <c r="C32" s="108"/>
+      <c r="C32" s="107"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
-      <c r="G32" s="113"/>
-      <c r="H32" s="116"/>
-      <c r="I32" s="117"/>
+      <c r="G32" s="112"/>
+      <c r="H32" s="115"/>
+      <c r="I32" s="116"/>
       <c r="J32" s="22"/>
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
@@ -12962,22 +13412,22 @@
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
       <c r="R32" s="22"/>
-      <c r="S32" s="64"/>
-      <c r="T32" s="53"/>
-      <c r="U32" s="53"/>
+      <c r="S32" s="63"/>
+      <c r="T32" s="52"/>
+      <c r="U32" s="52"/>
     </row>
     <row r="33" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="52">
+      <c r="A33" s="51">
         <v>33</v>
       </c>
       <c r="B33" s="8"/>
-      <c r="C33" s="108"/>
+      <c r="C33" s="107"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
-      <c r="G33" s="113"/>
-      <c r="H33" s="118"/>
-      <c r="I33" s="119"/>
+      <c r="G33" s="112"/>
+      <c r="H33" s="117"/>
+      <c r="I33" s="118"/>
       <c r="J33" s="22"/>
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
@@ -12987,12 +13437,12 @@
       <c r="P33" s="8"/>
       <c r="Q33" s="8"/>
       <c r="R33" s="8"/>
-      <c r="S33" s="64"/>
-      <c r="T33" s="53"/>
-      <c r="U33" s="107"/>
+      <c r="S33" s="63"/>
+      <c r="T33" s="52"/>
+      <c r="U33" s="106"/>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="52">
+      <c r="A34" s="51">
         <v>34</v>
       </c>
       <c r="B34" s="8"/>
@@ -13001,8 +13451,8 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
       <c r="G34" s="1"/>
-      <c r="H34" s="116"/>
-      <c r="I34" s="117"/>
+      <c r="H34" s="115"/>
+      <c r="I34" s="116"/>
       <c r="J34" s="22"/>
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
@@ -13012,22 +13462,22 @@
       <c r="P34" s="8"/>
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
-      <c r="S34" s="64"/>
-      <c r="T34" s="53"/>
-      <c r="U34" s="107"/>
+      <c r="S34" s="63"/>
+      <c r="T34" s="52"/>
+      <c r="U34" s="106"/>
     </row>
     <row r="35" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="52">
+      <c r="A35" s="51">
         <v>36</v>
       </c>
       <c r="B35" s="8"/>
-      <c r="C35" s="113"/>
+      <c r="C35" s="112"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
-      <c r="G35" s="113"/>
-      <c r="H35" s="120"/>
-      <c r="I35" s="121"/>
+      <c r="G35" s="112"/>
+      <c r="H35" s="119"/>
+      <c r="I35" s="120"/>
       <c r="J35" s="22"/>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
@@ -13037,22 +13487,22 @@
       <c r="P35" s="8"/>
       <c r="Q35" s="8"/>
       <c r="R35" s="8"/>
-      <c r="S35" s="64"/>
-      <c r="T35" s="53"/>
-      <c r="U35" s="107"/>
+      <c r="S35" s="63"/>
+      <c r="T35" s="52"/>
+      <c r="U35" s="106"/>
     </row>
     <row r="36" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="52">
+      <c r="A36" s="51">
         <v>37</v>
       </c>
       <c r="B36" s="8"/>
-      <c r="C36" s="112"/>
+      <c r="C36" s="111"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
-      <c r="G36" s="113"/>
-      <c r="H36" s="122"/>
-      <c r="I36" s="122"/>
+      <c r="G36" s="112"/>
+      <c r="H36" s="121"/>
+      <c r="I36" s="121"/>
       <c r="J36" s="22"/>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
@@ -13061,23 +13511,23 @@
       <c r="O36" s="8"/>
       <c r="P36" s="8"/>
       <c r="Q36" s="8"/>
-      <c r="R36" s="123"/>
-      <c r="S36" s="64"/>
-      <c r="T36" s="53"/>
-      <c r="U36" s="107"/>
+      <c r="R36" s="122"/>
+      <c r="S36" s="63"/>
+      <c r="T36" s="52"/>
+      <c r="U36" s="106"/>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="52">
+      <c r="A37" s="51">
         <v>38</v>
       </c>
       <c r="B37" s="8"/>
-      <c r="C37" s="112"/>
+      <c r="C37" s="111"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
       <c r="G37" s="8"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="38"/>
+      <c r="H37" s="36"/>
+      <c r="I37" s="37"/>
       <c r="J37" s="22"/>
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
@@ -13087,22 +13537,22 @@
       <c r="P37" s="8"/>
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
-      <c r="S37" s="64"/>
-      <c r="T37" s="53"/>
-      <c r="U37" s="107"/>
+      <c r="S37" s="63"/>
+      <c r="T37" s="52"/>
+      <c r="U37" s="106"/>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="52">
+      <c r="A38" s="51">
         <v>39</v>
       </c>
       <c r="B38" s="8"/>
-      <c r="C38" s="124"/>
+      <c r="C38" s="123"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
       <c r="J38" s="22"/>
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
@@ -13111,13 +13561,13 @@
       <c r="O38" s="8"/>
       <c r="P38" s="8"/>
       <c r="Q38" s="8"/>
-      <c r="R38" s="123"/>
-      <c r="S38" s="64"/>
-      <c r="T38" s="53"/>
-      <c r="U38" s="107"/>
+      <c r="R38" s="122"/>
+      <c r="S38" s="63"/>
+      <c r="T38" s="52"/>
+      <c r="U38" s="106"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="52">
+      <c r="A39" s="51">
         <v>40</v>
       </c>
       <c r="B39" s="8"/>
@@ -13126,8 +13576,8 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
-      <c r="H39" s="37"/>
-      <c r="I39" s="38"/>
+      <c r="H39" s="36"/>
+      <c r="I39" s="37"/>
       <c r="J39" s="22"/>
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
@@ -13137,22 +13587,22 @@
       <c r="P39" s="8"/>
       <c r="Q39" s="8"/>
       <c r="R39" s="8"/>
-      <c r="S39" s="64"/>
-      <c r="T39" s="53"/>
-      <c r="U39" s="107"/>
+      <c r="S39" s="63"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="106"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="52">
+      <c r="A40" s="51">
         <v>41</v>
       </c>
       <c r="B40" s="8"/>
-      <c r="C40" s="125"/>
+      <c r="C40" s="124"/>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
-      <c r="G40" s="126"/>
-      <c r="H40" s="116"/>
-      <c r="I40" s="117"/>
+      <c r="G40" s="125"/>
+      <c r="H40" s="115"/>
+      <c r="I40" s="116"/>
       <c r="J40" s="22"/>
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
@@ -13162,22 +13612,22 @@
       <c r="P40" s="8"/>
       <c r="Q40" s="8"/>
       <c r="R40" s="8"/>
-      <c r="S40" s="64"/>
-      <c r="T40" s="53"/>
-      <c r="U40" s="107"/>
+      <c r="S40" s="63"/>
+      <c r="T40" s="52"/>
+      <c r="U40" s="106"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="52">
+      <c r="A41" s="51">
         <v>42</v>
       </c>
       <c r="B41" s="8"/>
-      <c r="C41" s="112"/>
+      <c r="C41" s="111"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
       <c r="G41" s="1"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="128"/>
+      <c r="H41" s="126"/>
+      <c r="I41" s="127"/>
       <c r="J41" s="22"/>
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
@@ -13187,22 +13637,22 @@
       <c r="P41" s="8"/>
       <c r="Q41" s="8"/>
       <c r="R41" s="8"/>
-      <c r="S41" s="64"/>
-      <c r="T41" s="53"/>
-      <c r="U41" s="107"/>
+      <c r="S41" s="63"/>
+      <c r="T41" s="52"/>
+      <c r="U41" s="106"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="52">
+      <c r="A42" s="51">
         <v>43</v>
       </c>
       <c r="B42" s="8"/>
-      <c r="C42" s="108"/>
+      <c r="C42" s="107"/>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
-      <c r="G42" s="108"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="38"/>
+      <c r="G42" s="107"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="37"/>
       <c r="J42" s="22"/>
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
@@ -13212,12 +13662,12 @@
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
       <c r="R42" s="8"/>
-      <c r="S42" s="64"/>
-      <c r="T42" s="53"/>
-      <c r="U42" s="107"/>
+      <c r="S42" s="63"/>
+      <c r="T42" s="52"/>
+      <c r="U42" s="106"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="52">
+      <c r="A43" s="51">
         <v>44</v>
       </c>
       <c r="B43" s="8"/>
@@ -13226,8 +13676,8 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
       <c r="G43" s="8"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="38"/>
+      <c r="H43" s="36"/>
+      <c r="I43" s="37"/>
       <c r="J43" s="22"/>
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
@@ -13237,12 +13687,12 @@
       <c r="P43" s="8"/>
       <c r="Q43" s="8"/>
       <c r="R43" s="8"/>
-      <c r="S43" s="64"/>
-      <c r="T43" s="53"/>
-      <c r="U43" s="107"/>
+      <c r="S43" s="63"/>
+      <c r="T43" s="52"/>
+      <c r="U43" s="106"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="52">
+      <c r="A44" s="51">
         <v>45</v>
       </c>
       <c r="B44" s="8"/>
@@ -13251,8 +13701,8 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="38"/>
+      <c r="H44" s="36"/>
+      <c r="I44" s="37"/>
       <c r="J44" s="22"/>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
@@ -13261,23 +13711,23 @@
       <c r="O44" s="8"/>
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
-      <c r="R44" s="109"/>
-      <c r="S44" s="110"/>
-      <c r="T44" s="53"/>
-      <c r="U44" s="107"/>
+      <c r="R44" s="108"/>
+      <c r="S44" s="109"/>
+      <c r="T44" s="52"/>
+      <c r="U44" s="106"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A45" s="52">
+      <c r="A45" s="51">
         <v>46</v>
       </c>
       <c r="B45" s="8"/>
-      <c r="C45" s="112"/>
+      <c r="C45" s="111"/>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
-      <c r="G45" s="108"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="38"/>
+      <c r="G45" s="107"/>
+      <c r="H45" s="36"/>
+      <c r="I45" s="37"/>
       <c r="J45" s="22"/>
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
@@ -13287,22 +13737,22 @@
       <c r="P45" s="8"/>
       <c r="Q45" s="8"/>
       <c r="R45" s="8"/>
-      <c r="S45" s="129"/>
+      <c r="S45" s="128"/>
       <c r="T45" s="22"/>
-      <c r="U45" s="107"/>
+      <c r="U45" s="106"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A46" s="52">
+      <c r="A46" s="51">
         <v>47</v>
       </c>
       <c r="B46" s="8"/>
-      <c r="C46" s="108"/>
+      <c r="C46" s="107"/>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
       <c r="F46" s="8"/>
-      <c r="G46" s="130"/>
-      <c r="H46" s="131"/>
-      <c r="I46" s="38"/>
+      <c r="G46" s="129"/>
+      <c r="H46" s="130"/>
+      <c r="I46" s="37"/>
       <c r="J46" s="22"/>
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
@@ -13310,24 +13760,24 @@
       <c r="N46" s="8"/>
       <c r="O46" s="8"/>
       <c r="P46" s="8"/>
-      <c r="Q46" s="123"/>
+      <c r="Q46" s="122"/>
       <c r="R46" s="8"/>
-      <c r="S46" s="64"/>
-      <c r="T46" s="53"/>
-      <c r="U46" s="107"/>
+      <c r="S46" s="63"/>
+      <c r="T46" s="52"/>
+      <c r="U46" s="106"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A47" s="52">
+      <c r="A47" s="51">
         <v>48</v>
       </c>
       <c r="B47" s="8"/>
-      <c r="C47" s="108"/>
+      <c r="C47" s="107"/>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
-      <c r="G47" s="108"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="38"/>
+      <c r="G47" s="107"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="37"/>
       <c r="J47" s="22"/>
       <c r="K47" s="22"/>
       <c r="L47" s="8"/>
@@ -13337,22 +13787,22 @@
       <c r="P47" s="8"/>
       <c r="Q47" s="8"/>
       <c r="R47" s="8"/>
-      <c r="S47" s="64"/>
-      <c r="T47" s="53"/>
-      <c r="U47" s="107"/>
+      <c r="S47" s="63"/>
+      <c r="T47" s="52"/>
+      <c r="U47" s="106"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A48" s="52">
+      <c r="A48" s="51">
         <v>49</v>
       </c>
       <c r="B48" s="8"/>
-      <c r="C48" s="108"/>
+      <c r="C48" s="107"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
-      <c r="G48" s="108"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
+      <c r="G48" s="107"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
       <c r="J48" s="22"/>
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
@@ -13360,14 +13810,14 @@
       <c r="N48" s="8"/>
       <c r="O48" s="8"/>
       <c r="P48" s="8"/>
-      <c r="Q48" s="123"/>
+      <c r="Q48" s="122"/>
       <c r="R48" s="8"/>
-      <c r="S48" s="64"/>
-      <c r="T48" s="53"/>
-      <c r="U48" s="107"/>
+      <c r="S48" s="63"/>
+      <c r="T48" s="52"/>
+      <c r="U48" s="106"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A49" s="98">
+      <c r="A49" s="97">
         <v>50</v>
       </c>
       <c r="B49" s="8"/>
@@ -13375,9 +13825,9 @@
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
-      <c r="G49" s="108"/>
-      <c r="H49" s="37"/>
-      <c r="I49" s="38"/>
+      <c r="G49" s="107"/>
+      <c r="H49" s="36"/>
+      <c r="I49" s="37"/>
       <c r="J49" s="22"/>
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
@@ -13387,22 +13837,22 @@
       <c r="P49" s="1"/>
       <c r="Q49" s="8"/>
       <c r="R49" s="1"/>
-      <c r="S49" s="99"/>
-      <c r="T49" s="103"/>
-      <c r="U49" s="101"/>
+      <c r="S49" s="98"/>
+      <c r="T49" s="102"/>
+      <c r="U49" s="100"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A50" s="52">
+      <c r="A50" s="51">
         <v>51</v>
       </c>
       <c r="B50" s="8"/>
-      <c r="C50" s="108"/>
+      <c r="C50" s="107"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
-      <c r="G50" s="108"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="38"/>
+      <c r="G50" s="107"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="37"/>
       <c r="J50" s="22"/>
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
@@ -13412,22 +13862,22 @@
       <c r="P50" s="8"/>
       <c r="Q50" s="8"/>
       <c r="R50" s="8"/>
-      <c r="S50" s="64"/>
-      <c r="T50" s="53"/>
-      <c r="U50" s="107"/>
+      <c r="S50" s="63"/>
+      <c r="T50" s="52"/>
+      <c r="U50" s="106"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A51" s="52">
+      <c r="A51" s="51">
         <v>52</v>
       </c>
       <c r="B51" s="8"/>
-      <c r="C51" s="108"/>
+      <c r="C51" s="107"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
-      <c r="G51" s="108"/>
-      <c r="H51" s="37"/>
-      <c r="I51" s="38"/>
+      <c r="G51" s="107"/>
+      <c r="H51" s="36"/>
+      <c r="I51" s="37"/>
       <c r="J51" s="22"/>
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
@@ -13437,21 +13887,21 @@
       <c r="P51" s="8"/>
       <c r="Q51" s="8"/>
       <c r="R51" s="8"/>
-      <c r="S51" s="64"/>
-      <c r="T51" s="53"/>
-      <c r="U51" s="107"/>
+      <c r="S51" s="63"/>
+      <c r="T51" s="52"/>
+      <c r="U51" s="106"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A52" s="52">
+      <c r="A52" s="51">
         <v>53</v>
       </c>
-      <c r="B52" s="71"/>
+      <c r="B52" s="70"/>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
-      <c r="G52" s="132"/>
-      <c r="H52" s="133"/>
+      <c r="G52" s="131"/>
+      <c r="H52" s="132"/>
       <c r="I52" s="8"/>
       <c r="J52" s="22"/>
       <c r="K52" s="8"/>
@@ -13462,22 +13912,22 @@
       <c r="P52" s="8"/>
       <c r="Q52" s="8"/>
       <c r="R52" s="8"/>
-      <c r="S52" s="64"/>
-      <c r="T52" s="53"/>
-      <c r="U52" s="107"/>
+      <c r="S52" s="63"/>
+      <c r="T52" s="52"/>
+      <c r="U52" s="106"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A53" s="52">
+      <c r="A53" s="51">
         <v>54</v>
       </c>
       <c r="B53" s="8"/>
-      <c r="C53" s="113"/>
+      <c r="C53" s="112"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
-      <c r="G53" s="113"/>
-      <c r="H53" s="37"/>
-      <c r="I53" s="38"/>
+      <c r="G53" s="112"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="37"/>
       <c r="J53" s="22"/>
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
@@ -13487,20 +13937,20 @@
       <c r="P53" s="8"/>
       <c r="Q53" s="8"/>
       <c r="R53" s="8"/>
-      <c r="S53" s="129"/>
-      <c r="T53" s="53"/>
-      <c r="U53" s="107"/>
+      <c r="S53" s="128"/>
+      <c r="T53" s="52"/>
+      <c r="U53" s="106"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A54" s="52">
+      <c r="A54" s="51">
         <v>55</v>
       </c>
       <c r="B54" s="8"/>
-      <c r="C54" s="113"/>
+      <c r="C54" s="112"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
-      <c r="G54" s="108"/>
+      <c r="G54" s="107"/>
       <c r="H54" s="17"/>
       <c r="I54" s="8"/>
       <c r="J54" s="22"/>
@@ -13513,44 +13963,44 @@
       <c r="Q54" s="8"/>
       <c r="R54" s="8"/>
       <c r="S54" s="8"/>
-      <c r="T54" s="53"/>
-      <c r="U54" s="107"/>
+      <c r="T54" s="52"/>
+      <c r="U54" s="106"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="52">
+      <c r="A55" s="51">
         <v>56</v>
       </c>
       <c r="B55" s="1"/>
-      <c r="C55" s="108"/>
+      <c r="C55" s="107"/>
       <c r="D55" s="8"/>
-      <c r="E55" s="134"/>
-      <c r="F55" s="134"/>
-      <c r="G55" s="135"/>
-      <c r="H55" s="136"/>
-      <c r="I55" s="134"/>
-      <c r="J55" s="137"/>
-      <c r="K55" s="134"/>
-      <c r="L55" s="134"/>
-      <c r="M55" s="134"/>
+      <c r="E55" s="133"/>
+      <c r="F55" s="133"/>
+      <c r="G55" s="134"/>
+      <c r="H55" s="135"/>
+      <c r="I55" s="133"/>
+      <c r="J55" s="136"/>
+      <c r="K55" s="133"/>
+      <c r="L55" s="133"/>
+      <c r="M55" s="133"/>
       <c r="N55" s="8"/>
       <c r="O55" s="8"/>
       <c r="P55" s="8"/>
       <c r="Q55" s="8"/>
       <c r="R55" s="8"/>
-      <c r="S55" s="129"/>
-      <c r="T55" s="53"/>
-      <c r="U55" s="107"/>
+      <c r="S55" s="128"/>
+      <c r="T55" s="52"/>
+      <c r="U55" s="106"/>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A56" s="52">
+      <c r="A56" s="51">
         <v>57</v>
       </c>
       <c r="B56" s="8"/>
-      <c r="C56" s="113"/>
+      <c r="C56" s="112"/>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
       <c r="F56" s="8"/>
-      <c r="G56" s="108"/>
+      <c r="G56" s="107"/>
       <c r="H56" s="17"/>
       <c r="I56" s="8"/>
       <c r="J56" s="22"/>
@@ -13562,20 +14012,20 @@
       <c r="P56" s="8"/>
       <c r="Q56" s="8"/>
       <c r="R56" s="8"/>
-      <c r="S56" s="64"/>
-      <c r="T56" s="53"/>
-      <c r="U56" s="107"/>
+      <c r="S56" s="63"/>
+      <c r="T56" s="52"/>
+      <c r="U56" s="106"/>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A57" s="52">
+      <c r="A57" s="51">
         <v>58</v>
       </c>
       <c r="B57" s="8"/>
-      <c r="C57" s="108"/>
+      <c r="C57" s="107"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
-      <c r="G57" s="108"/>
+      <c r="G57" s="107"/>
       <c r="H57" s="17"/>
       <c r="I57" s="17"/>
       <c r="J57" s="22"/>
@@ -13587,12 +14037,12 @@
       <c r="P57" s="8"/>
       <c r="Q57" s="8"/>
       <c r="R57" s="8"/>
-      <c r="S57" s="129"/>
+      <c r="S57" s="128"/>
       <c r="T57" s="22"/>
-      <c r="U57" s="107"/>
+      <c r="U57" s="106"/>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" s="52">
+      <c r="A58" s="51">
         <v>59</v>
       </c>
       <c r="B58" s="1"/>
@@ -13612,15 +14062,15 @@
       <c r="P58" s="1"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="64"/>
-      <c r="T58" s="53"/>
-      <c r="U58" s="107"/>
+      <c r="S58" s="63"/>
+      <c r="T58" s="52"/>
+      <c r="U58" s="106"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="52">
+      <c r="A59" s="51">
         <v>60</v>
       </c>
-      <c r="B59" s="71"/>
+      <c r="B59" s="70"/>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -13637,22 +14087,22 @@
       <c r="P59" s="8"/>
       <c r="Q59" s="8"/>
       <c r="R59" s="8"/>
-      <c r="S59" s="64"/>
-      <c r="T59" s="53"/>
-      <c r="U59" s="107"/>
+      <c r="S59" s="63"/>
+      <c r="T59" s="52"/>
+      <c r="U59" s="106"/>
     </row>
     <row r="60" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="52">
+      <c r="A60" s="51">
         <v>61</v>
       </c>
       <c r="B60" s="19"/>
-      <c r="C60" s="113"/>
+      <c r="C60" s="112"/>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
       <c r="F60" s="8"/>
-      <c r="G60" s="108"/>
+      <c r="G60" s="107"/>
       <c r="H60" s="17"/>
-      <c r="I60" s="121"/>
+      <c r="I60" s="120"/>
       <c r="J60" s="22"/>
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
@@ -13662,12 +14112,12 @@
       <c r="P60" s="8"/>
       <c r="Q60" s="8"/>
       <c r="R60" s="8"/>
-      <c r="S60" s="64"/>
-      <c r="T60" s="53"/>
-      <c r="U60" s="107"/>
+      <c r="S60" s="63"/>
+      <c r="T60" s="52"/>
+      <c r="U60" s="106"/>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="52">
+      <c r="A61" s="51">
         <v>62</v>
       </c>
       <c r="B61" s="8"/>
@@ -13687,22 +14137,22 @@
       <c r="P61" s="8"/>
       <c r="Q61" s="8"/>
       <c r="R61" s="8"/>
-      <c r="S61" s="64"/>
-      <c r="T61" s="53"/>
-      <c r="U61" s="107"/>
+      <c r="S61" s="63"/>
+      <c r="T61" s="52"/>
+      <c r="U61" s="106"/>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" s="52">
+      <c r="A62" s="51">
         <v>63</v>
       </c>
       <c r="B62" s="8"/>
-      <c r="C62" s="108"/>
+      <c r="C62" s="107"/>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
-      <c r="G62" s="108"/>
+      <c r="G62" s="107"/>
       <c r="H62" s="17"/>
-      <c r="I62" s="138"/>
+      <c r="I62" s="137"/>
       <c r="J62" s="22"/>
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
@@ -13712,12 +14162,12 @@
       <c r="P62" s="8"/>
       <c r="Q62" s="8"/>
       <c r="R62" s="8"/>
-      <c r="S62" s="64"/>
-      <c r="T62" s="53"/>
-      <c r="U62" s="107"/>
+      <c r="S62" s="63"/>
+      <c r="T62" s="52"/>
+      <c r="U62" s="106"/>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="52">
+      <c r="A63" s="51">
         <v>64</v>
       </c>
       <c r="B63" s="8"/>
@@ -13725,7 +14175,7 @@
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
-      <c r="G63" s="108"/>
+      <c r="G63" s="107"/>
       <c r="H63" s="17"/>
       <c r="I63" s="8"/>
       <c r="J63" s="22"/>
@@ -13737,12 +14187,12 @@
       <c r="P63" s="8"/>
       <c r="Q63" s="8"/>
       <c r="R63" s="8"/>
-      <c r="S63" s="64"/>
-      <c r="T63" s="53"/>
-      <c r="U63" s="107"/>
+      <c r="S63" s="63"/>
+      <c r="T63" s="52"/>
+      <c r="U63" s="106"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="52">
+      <c r="A64" s="51">
         <v>65</v>
       </c>
       <c r="B64" s="8"/>
@@ -13750,7 +14200,7 @@
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
-      <c r="G64" s="108"/>
+      <c r="G64" s="107"/>
       <c r="H64" s="17"/>
       <c r="I64" s="8"/>
       <c r="J64" s="22"/>
@@ -13762,12 +14212,12 @@
       <c r="P64" s="8"/>
       <c r="Q64" s="8"/>
       <c r="R64" s="8"/>
-      <c r="S64" s="64"/>
-      <c r="T64" s="53"/>
-      <c r="U64" s="107"/>
+      <c r="S64" s="63"/>
+      <c r="T64" s="52"/>
+      <c r="U64" s="106"/>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="52">
+      <c r="A65" s="51">
         <v>66</v>
       </c>
       <c r="B65" s="8"/>
@@ -13775,7 +14225,7 @@
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
-      <c r="G65" s="108"/>
+      <c r="G65" s="107"/>
       <c r="H65" s="17"/>
       <c r="I65" s="8"/>
       <c r="J65" s="22"/>
@@ -13787,12 +14237,12 @@
       <c r="P65" s="8"/>
       <c r="Q65" s="8"/>
       <c r="R65" s="8"/>
-      <c r="S65" s="64"/>
-      <c r="T65" s="53"/>
-      <c r="U65" s="107"/>
+      <c r="S65" s="63"/>
+      <c r="T65" s="52"/>
+      <c r="U65" s="106"/>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A66" s="52">
+      <c r="A66" s="51">
         <v>67</v>
       </c>
       <c r="B66" s="8"/>
@@ -13812,21 +14262,21 @@
       <c r="P66" s="8"/>
       <c r="Q66" s="8"/>
       <c r="R66" s="8"/>
-      <c r="S66" s="64"/>
-      <c r="T66" s="53"/>
-      <c r="U66" s="107"/>
+      <c r="S66" s="63"/>
+      <c r="T66" s="52"/>
+      <c r="U66" s="106"/>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A67" s="52">
+      <c r="A67" s="51">
         <v>68</v>
       </c>
       <c r="B67" s="8"/>
-      <c r="C67" s="139"/>
+      <c r="C67" s="138"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
-      <c r="G67" s="140"/>
-      <c r="H67" s="141"/>
+      <c r="G67" s="139"/>
+      <c r="H67" s="140"/>
       <c r="I67" s="8"/>
       <c r="J67" s="22"/>
       <c r="K67" s="8"/>
@@ -13837,12 +14287,12 @@
       <c r="P67" s="8"/>
       <c r="Q67" s="8"/>
       <c r="R67" s="8"/>
-      <c r="S67" s="64"/>
-      <c r="T67" s="53"/>
-      <c r="U67" s="107"/>
+      <c r="S67" s="63"/>
+      <c r="T67" s="52"/>
+      <c r="U67" s="106"/>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A68" s="52">
+      <c r="A68" s="51">
         <v>69</v>
       </c>
       <c r="B68" s="8"/>
@@ -13851,7 +14301,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
       <c r="G68" s="8"/>
-      <c r="H68" s="142"/>
+      <c r="H68" s="141"/>
       <c r="I68" s="8"/>
       <c r="J68" s="22"/>
       <c r="K68" s="8"/>
@@ -13862,21 +14312,21 @@
       <c r="P68" s="8"/>
       <c r="Q68" s="8"/>
       <c r="R68" s="8"/>
-      <c r="S68" s="129"/>
+      <c r="S68" s="128"/>
       <c r="T68" s="22"/>
-      <c r="U68" s="107"/>
+      <c r="U68" s="106"/>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="52">
+      <c r="A69" s="51">
         <v>70</v>
       </c>
       <c r="B69" s="8"/>
-      <c r="C69" s="139"/>
+      <c r="C69" s="138"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
-      <c r="G69" s="140"/>
-      <c r="H69" s="143"/>
+      <c r="G69" s="139"/>
+      <c r="H69" s="142"/>
       <c r="I69" s="8"/>
       <c r="J69" s="22"/>
       <c r="K69" s="8"/>
@@ -13885,14 +14335,14 @@
       <c r="N69" s="8"/>
       <c r="O69" s="8"/>
       <c r="P69" s="8"/>
-      <c r="Q69" s="123"/>
+      <c r="Q69" s="122"/>
       <c r="R69" s="8"/>
-      <c r="S69" s="64"/>
-      <c r="T69" s="53"/>
-      <c r="U69" s="107"/>
+      <c r="S69" s="63"/>
+      <c r="T69" s="52"/>
+      <c r="U69" s="106"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A70" s="52">
+      <c r="A70" s="51">
         <v>71</v>
       </c>
       <c r="B70" s="8"/>
@@ -13912,12 +14362,12 @@
       <c r="P70" s="8"/>
       <c r="Q70" s="8"/>
       <c r="R70" s="8"/>
-      <c r="S70" s="64"/>
-      <c r="T70" s="53"/>
-      <c r="U70" s="107"/>
+      <c r="S70" s="63"/>
+      <c r="T70" s="52"/>
+      <c r="U70" s="106"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="52">
+      <c r="A71" s="51">
         <v>72</v>
       </c>
       <c r="B71" s="8"/>
@@ -13937,12 +14387,12 @@
       <c r="P71" s="8"/>
       <c r="Q71" s="8"/>
       <c r="R71" s="8"/>
-      <c r="S71" s="144"/>
-      <c r="T71" s="53"/>
-      <c r="U71" s="107"/>
+      <c r="S71" s="143"/>
+      <c r="T71" s="52"/>
+      <c r="U71" s="106"/>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A72" s="52">
+      <c r="A72" s="51">
         <v>73</v>
       </c>
       <c r="B72" s="8"/>
@@ -13962,12 +14412,12 @@
       <c r="P72" s="8"/>
       <c r="Q72" s="8"/>
       <c r="R72" s="8"/>
-      <c r="S72" s="144"/>
-      <c r="T72" s="53"/>
-      <c r="U72" s="107"/>
+      <c r="S72" s="143"/>
+      <c r="T72" s="52"/>
+      <c r="U72" s="106"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="52">
+      <c r="A73" s="51">
         <v>74</v>
       </c>
       <c r="B73" s="8"/>
@@ -13987,15 +14437,15 @@
       <c r="P73" s="8"/>
       <c r="Q73" s="8"/>
       <c r="R73" s="8"/>
-      <c r="S73" s="144"/>
-      <c r="T73" s="53"/>
-      <c r="U73" s="107"/>
+      <c r="S73" s="143"/>
+      <c r="T73" s="52"/>
+      <c r="U73" s="106"/>
     </row>
     <row r="74" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="98">
+      <c r="A74" s="97">
         <v>75</v>
       </c>
-      <c r="B74" s="102"/>
+      <c r="B74" s="101"/>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
@@ -14012,12 +14462,12 @@
       <c r="P74" s="1"/>
       <c r="Q74" s="8"/>
       <c r="R74" s="1"/>
-      <c r="S74" s="144"/>
-      <c r="T74" s="53"/>
-      <c r="U74" s="101"/>
+      <c r="S74" s="143"/>
+      <c r="T74" s="52"/>
+      <c r="U74" s="100"/>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="98"/>
+      <c r="A75" s="97"/>
       <c r="B75" s="1"/>
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
@@ -14035,12 +14485,12 @@
       <c r="P75" s="1"/>
       <c r="Q75" s="8"/>
       <c r="R75" s="1"/>
-      <c r="S75" s="144"/>
-      <c r="T75" s="53"/>
-      <c r="U75" s="101"/>
+      <c r="S75" s="143"/>
+      <c r="T75" s="52"/>
+      <c r="U75" s="100"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A76" s="98"/>
+      <c r="A76" s="97"/>
       <c r="B76" s="1"/>
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
@@ -14058,9 +14508,9 @@
       <c r="P76" s="1"/>
       <c r="Q76" s="8"/>
       <c r="R76" s="1"/>
-      <c r="S76" s="144"/>
-      <c r="T76" s="53"/>
-      <c r="U76" s="101"/>
+      <c r="S76" s="143"/>
+      <c r="T76" s="52"/>
+      <c r="U76" s="100"/>
     </row>
   </sheetData>
   <hyperlinks>
